--- a/downloads/BTC_Tagesbericht_2026-10-05.xlsx
+++ b/downloads/BTC_Tagesbericht_2026-10-05.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tagesanalyse" sheetId="1" r:id="R84778ee911ea499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szenarien" sheetId="2" r:id="R374621db921248c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trading Journal" sheetId="3" r:id="Rd090f11c99f44e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datenquellen" sheetId="4" r:id="R2bd606b5f6ea457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kerzen 30m" sheetId="5" r:id="Re322d3975d884237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tagesanalyse" sheetId="1" r:id="R78174454f3cb4bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szenarien" sheetId="2" r:id="R4f694ff47f914341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trading Journal" sheetId="3" r:id="R5b2499515be544ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datenquellen" sheetId="4" r:id="Rd997e44b3ca24c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kerzen 30m" sheetId="5" r:id="R333f05bd5ad84200"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -425,8 +425,8 @@
       <x:c r="I6" s="8" t="n">
         <x:v>-22.092559714571028</x:v>
       </x:c>
-      <x:c r="J6" s="7" t="d">
-        <x:v>2026-10-05T11:59:59.000Z</x:v>
+      <x:c r="J6" s="7" t="n">
+        <x:v>46300.49998842593</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
@@ -457,8 +457,8 @@
       <x:c r="I7" s="8" t="n">
         <x:v>-42.519306127415604</x:v>
       </x:c>
-      <x:c r="J7" s="7" t="d">
-        <x:v>2026-10-05T11:59:59.000Z</x:v>
+      <x:c r="J7" s="7" t="n">
+        <x:v>46300.49998842593</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
@@ -489,8 +489,8 @@
       <x:c r="I8" s="8" t="n">
         <x:v>-38.03127473597942</x:v>
       </x:c>
-      <x:c r="J8" s="7" t="d">
-        <x:v>2026-10-05T11:59:59.000Z</x:v>
+      <x:c r="J8" s="7" t="n">
+        <x:v>46300.49998842593</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -521,8 +521,8 @@
       <x:c r="I9" s="8" t="n">
         <x:v>117.99244768450524</x:v>
       </x:c>
-      <x:c r="J9" s="7" t="d">
-        <x:v>2026-10-05T09:59:59.000Z</x:v>
+      <x:c r="J9" s="7" t="n">
+        <x:v>46300.41665509259</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
@@ -553,8 +553,8 @@
       <x:c r="I10" s="8" t="n">
         <x:v>-63.60965696258063</x:v>
       </x:c>
-      <x:c r="J10" s="7" t="d">
-        <x:v>2026-10-05T01:59:59.000Z</x:v>
+      <x:c r="J10" s="7" t="n">
+        <x:v>46300.08332175926</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1060,8 +1060,8 @@
       <x:c r="B6" s="4" t="str">
         <x:v>https://data-api.binance.vision/api/v3/klines?symbol=BTCUSDT&amp;interval=15m&amp;limit=300</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="d">
-        <x:v>2026-10-05T10:12:38.733Z</x:v>
+      <x:c r="C6" s="7" t="n">
+        <x:v>46300.425448298614</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
         <x:v>300 Kerzen; laufende Kerze aus Indikatoren ausgeschlossen</x:v>
@@ -1074,8 +1074,8 @@
       <x:c r="B7" s="4" t="str">
         <x:v>https://data-api.binance.vision/api/v3/klines?symbol=BTCUSDT&amp;interval=30m&amp;limit=300</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="d">
-        <x:v>2026-10-05T10:12:38.916Z</x:v>
+      <x:c r="C7" s="7" t="n">
+        <x:v>46300.42545041667</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
         <x:v>300 Kerzen; laufende Kerze aus Indikatoren ausgeschlossen</x:v>
@@ -1088,8 +1088,8 @@
       <x:c r="B8" s="4" t="str">
         <x:v>https://data-api.binance.vision/api/v3/klines?symbol=BTCUSDT&amp;interval=1h&amp;limit=300</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="d">
-        <x:v>2026-10-05T10:12:38.959Z</x:v>
+      <x:c r="C8" s="7" t="n">
+        <x:v>46300.42545091435</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>300 Kerzen; laufende Kerze aus Indikatoren ausgeschlossen</x:v>
@@ -1102,8 +1102,8 @@
       <x:c r="B9" s="4" t="str">
         <x:v>https://data-api.binance.vision/api/v3/klines?symbol=BTCUSDT&amp;interval=4h&amp;limit=300</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="d">
-        <x:v>2026-10-05T10:12:38.815Z</x:v>
+      <x:c r="C9" s="7" t="n">
+        <x:v>46300.42544924769</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
         <x:v>300 Kerzen; laufende Kerze aus Indikatoren ausgeschlossen</x:v>
@@ -1116,8 +1116,8 @@
       <x:c r="B10" s="4" t="str">
         <x:v>https://data-api.binance.vision/api/v3/klines?symbol=BTCUSDT&amp;interval=1d&amp;limit=300</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="d">
-        <x:v>2026-10-05T10:12:39.022Z</x:v>
+      <x:c r="C10" s="7" t="n">
+        <x:v>46300.42545164352</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>300 Kerzen; laufende Kerze aus Indikatoren ausgeschlossen</x:v>
@@ -1180,8 +1180,8 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="20" t="d">
-        <x:v>2026-09-29T04:30:00.000Z</x:v>
+      <x:c r="A6" s="20" t="n">
+        <x:v>46294.1875</x:v>
       </x:c>
       <x:c r="B6" s="8" t="n">
         <x:v>83226.01</x:v>
@@ -1198,13 +1198,13 @@
       <x:c r="F6" s="8" t="n">
         <x:v>199.67459</x:v>
       </x:c>
-      <x:c r="G6" s="20" t="d">
-        <x:v>2026-09-29T04:59:59.999Z</x:v>
+      <x:c r="G6" s="20" t="n">
+        <x:v>46294.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
-      <x:c r="A7" s="20" t="d">
-        <x:v>2026-09-29T05:00:00.000Z</x:v>
+      <x:c r="A7" s="20" t="n">
+        <x:v>46294.20833333333</x:v>
       </x:c>
       <x:c r="B7" s="8" t="n">
         <x:v>83212.98</x:v>
@@ -1221,13 +1221,13 @@
       <x:c r="F7" s="8" t="n">
         <x:v>134.5961</x:v>
       </x:c>
-      <x:c r="G7" s="20" t="d">
-        <x:v>2026-09-29T05:29:59.999Z</x:v>
+      <x:c r="G7" s="20" t="n">
+        <x:v>46294.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
-      <x:c r="A8" s="20" t="d">
-        <x:v>2026-09-29T05:30:00.000Z</x:v>
+      <x:c r="A8" s="20" t="n">
+        <x:v>46294.22916666667</x:v>
       </x:c>
       <x:c r="B8" s="8" t="n">
         <x:v>83316.01</x:v>
@@ -1244,13 +1244,13 @@
       <x:c r="F8" s="8" t="n">
         <x:v>224.56199</x:v>
       </x:c>
-      <x:c r="G8" s="20" t="d">
-        <x:v>2026-09-29T05:59:59.999Z</x:v>
+      <x:c r="G8" s="20" t="n">
+        <x:v>46294.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9" s="20" t="d">
-        <x:v>2026-09-29T06:00:00.000Z</x:v>
+      <x:c r="A9" s="20" t="n">
+        <x:v>46294.25</x:v>
       </x:c>
       <x:c r="B9" s="8" t="n">
         <x:v>83431.01</x:v>
@@ -1267,13 +1267,13 @@
       <x:c r="F9" s="8" t="n">
         <x:v>385.03579</x:v>
       </x:c>
-      <x:c r="G9" s="20" t="d">
-        <x:v>2026-09-29T06:29:59.999Z</x:v>
+      <x:c r="G9" s="20" t="n">
+        <x:v>46294.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="20" t="d">
-        <x:v>2026-09-29T06:30:00.000Z</x:v>
+      <x:c r="A10" s="20" t="n">
+        <x:v>46294.27083333333</x:v>
       </x:c>
       <x:c r="B10" s="8" t="n">
         <x:v>83881.93</x:v>
@@ -1290,13 +1290,13 @@
       <x:c r="F10" s="8" t="n">
         <x:v>272.41285</x:v>
       </x:c>
-      <x:c r="G10" s="20" t="d">
-        <x:v>2026-09-29T06:59:59.999Z</x:v>
+      <x:c r="G10" s="20" t="n">
+        <x:v>46294.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="20" t="d">
-        <x:v>2026-09-29T07:00:00.000Z</x:v>
+      <x:c r="A11" s="20" t="n">
+        <x:v>46294.29166666667</x:v>
       </x:c>
       <x:c r="B11" s="8" t="n">
         <x:v>84007.07</x:v>
@@ -1313,13 +1313,13 @@
       <x:c r="F11" s="8" t="n">
         <x:v>266.5709</x:v>
       </x:c>
-      <x:c r="G11" s="20" t="d">
-        <x:v>2026-09-29T07:29:59.999Z</x:v>
+      <x:c r="G11" s="20" t="n">
+        <x:v>46294.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
-      <x:c r="A12" s="20" t="d">
-        <x:v>2026-09-29T07:30:00.000Z</x:v>
+      <x:c r="A12" s="20" t="n">
+        <x:v>46294.3125</x:v>
       </x:c>
       <x:c r="B12" s="8" t="n">
         <x:v>83996.21</x:v>
@@ -1336,13 +1336,13 @@
       <x:c r="F12" s="8" t="n">
         <x:v>347.83224</x:v>
       </x:c>
-      <x:c r="G12" s="20" t="d">
-        <x:v>2026-09-29T07:59:59.999Z</x:v>
+      <x:c r="G12" s="20" t="n">
+        <x:v>46294.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="20" t="d">
-        <x:v>2026-09-29T08:00:00.000Z</x:v>
+      <x:c r="A13" s="20" t="n">
+        <x:v>46294.33333333333</x:v>
       </x:c>
       <x:c r="B13" s="8" t="n">
         <x:v>83980.97</x:v>
@@ -1359,13 +1359,13 @@
       <x:c r="F13" s="8" t="n">
         <x:v>354.47813</x:v>
       </x:c>
-      <x:c r="G13" s="20" t="d">
-        <x:v>2026-09-29T08:29:59.999Z</x:v>
+      <x:c r="G13" s="20" t="n">
+        <x:v>46294.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
-      <x:c r="A14" s="20" t="d">
-        <x:v>2026-09-29T08:30:00.000Z</x:v>
+      <x:c r="A14" s="20" t="n">
+        <x:v>46294.35416666667</x:v>
       </x:c>
       <x:c r="B14" s="8" t="n">
         <x:v>84166.93</x:v>
@@ -1382,13 +1382,13 @@
       <x:c r="F14" s="8" t="n">
         <x:v>296.20098</x:v>
       </x:c>
-      <x:c r="G14" s="20" t="d">
-        <x:v>2026-09-29T08:59:59.999Z</x:v>
+      <x:c r="G14" s="20" t="n">
+        <x:v>46294.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
-      <x:c r="A15" s="20" t="d">
-        <x:v>2026-09-29T09:00:00.000Z</x:v>
+      <x:c r="A15" s="20" t="n">
+        <x:v>46294.375</x:v>
       </x:c>
       <x:c r="B15" s="8" t="n">
         <x:v>83874.01</x:v>
@@ -1405,13 +1405,13 @@
       <x:c r="F15" s="8" t="n">
         <x:v>286.45248</x:v>
       </x:c>
-      <x:c r="G15" s="20" t="d">
-        <x:v>2026-09-29T09:29:59.999Z</x:v>
+      <x:c r="G15" s="20" t="n">
+        <x:v>46294.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
-      <x:c r="A16" s="20" t="d">
-        <x:v>2026-09-29T09:30:00.000Z</x:v>
+      <x:c r="A16" s="20" t="n">
+        <x:v>46294.39583333333</x:v>
       </x:c>
       <x:c r="B16" s="8" t="n">
         <x:v>83849.54</x:v>
@@ -1428,13 +1428,13 @@
       <x:c r="F16" s="8" t="n">
         <x:v>596.94562</x:v>
       </x:c>
-      <x:c r="G16" s="20" t="d">
-        <x:v>2026-09-29T09:59:59.999Z</x:v>
+      <x:c r="G16" s="20" t="n">
+        <x:v>46294.41666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
-      <x:c r="A17" s="20" t="d">
-        <x:v>2026-09-29T10:00:00.000Z</x:v>
+      <x:c r="A17" s="20" t="n">
+        <x:v>46294.41666666667</x:v>
       </x:c>
       <x:c r="B17" s="8" t="n">
         <x:v>84258.01</x:v>
@@ -1451,13 +1451,13 @@
       <x:c r="F17" s="8" t="n">
         <x:v>343.55989</x:v>
       </x:c>
-      <x:c r="G17" s="20" t="d">
-        <x:v>2026-09-29T10:29:59.999Z</x:v>
+      <x:c r="G17" s="20" t="n">
+        <x:v>46294.43749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
-      <x:c r="A18" s="20" t="d">
-        <x:v>2026-09-29T10:30:00.000Z</x:v>
+      <x:c r="A18" s="20" t="n">
+        <x:v>46294.4375</x:v>
       </x:c>
       <x:c r="B18" s="8" t="n">
         <x:v>84150.01</x:v>
@@ -1474,13 +1474,13 @@
       <x:c r="F18" s="8" t="n">
         <x:v>165.94705</x:v>
       </x:c>
-      <x:c r="G18" s="20" t="d">
-        <x:v>2026-09-29T10:59:59.999Z</x:v>
+      <x:c r="G18" s="20" t="n">
+        <x:v>46294.45833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
-      <x:c r="A19" s="20" t="d">
-        <x:v>2026-09-29T11:00:00.000Z</x:v>
+      <x:c r="A19" s="20" t="n">
+        <x:v>46294.45833333333</x:v>
       </x:c>
       <x:c r="B19" s="8" t="n">
         <x:v>84030.5</x:v>
@@ -1497,13 +1497,13 @@
       <x:c r="F19" s="8" t="n">
         <x:v>191.97251</x:v>
       </x:c>
-      <x:c r="G19" s="20" t="d">
-        <x:v>2026-09-29T11:29:59.999Z</x:v>
+      <x:c r="G19" s="20" t="n">
+        <x:v>46294.47916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
-      <x:c r="A20" s="20" t="d">
-        <x:v>2026-09-29T11:30:00.000Z</x:v>
+      <x:c r="A20" s="20" t="n">
+        <x:v>46294.47916666667</x:v>
       </x:c>
       <x:c r="B20" s="8" t="n">
         <x:v>84068.29</x:v>
@@ -1520,13 +1520,13 @@
       <x:c r="F20" s="8" t="n">
         <x:v>300.08105</x:v>
       </x:c>
-      <x:c r="G20" s="20" t="d">
-        <x:v>2026-09-29T11:59:59.999Z</x:v>
+      <x:c r="G20" s="20" t="n">
+        <x:v>46294.49999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="20" t="d">
-        <x:v>2026-09-29T12:00:00.000Z</x:v>
+      <x:c r="A21" s="20" t="n">
+        <x:v>46294.5</x:v>
       </x:c>
       <x:c r="B21" s="8" t="n">
         <x:v>84358</x:v>
@@ -1543,13 +1543,13 @@
       <x:c r="F21" s="8" t="n">
         <x:v>342.68398</x:v>
       </x:c>
-      <x:c r="G21" s="20" t="d">
-        <x:v>2026-09-29T12:29:59.999Z</x:v>
+      <x:c r="G21" s="20" t="n">
+        <x:v>46294.52083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
-      <x:c r="A22" s="20" t="d">
-        <x:v>2026-09-29T12:30:00.000Z</x:v>
+      <x:c r="A22" s="20" t="n">
+        <x:v>46294.52083333333</x:v>
       </x:c>
       <x:c r="B22" s="8" t="n">
         <x:v>84203.93</x:v>
@@ -1566,13 +1566,13 @@
       <x:c r="F22" s="8" t="n">
         <x:v>247.7439</x:v>
       </x:c>
-      <x:c r="G22" s="20" t="d">
-        <x:v>2026-09-29T12:59:59.999Z</x:v>
+      <x:c r="G22" s="20" t="n">
+        <x:v>46294.54166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="20" t="d">
-        <x:v>2026-09-29T13:00:00.000Z</x:v>
+      <x:c r="A23" s="20" t="n">
+        <x:v>46294.54166666667</x:v>
       </x:c>
       <x:c r="B23" s="8" t="n">
         <x:v>84332.85</x:v>
@@ -1589,13 +1589,13 @@
       <x:c r="F23" s="8" t="n">
         <x:v>347.41169</x:v>
       </x:c>
-      <x:c r="G23" s="20" t="d">
-        <x:v>2026-09-29T13:29:59.999Z</x:v>
+      <x:c r="G23" s="20" t="n">
+        <x:v>46294.56249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
-      <x:c r="A24" s="20" t="d">
-        <x:v>2026-09-29T13:30:00.000Z</x:v>
+      <x:c r="A24" s="20" t="n">
+        <x:v>46294.5625</x:v>
       </x:c>
       <x:c r="B24" s="8" t="n">
         <x:v>84361.84</x:v>
@@ -1612,13 +1612,13 @@
       <x:c r="F24" s="8" t="n">
         <x:v>509.50332</x:v>
       </x:c>
-      <x:c r="G24" s="20" t="d">
-        <x:v>2026-09-29T13:59:59.999Z</x:v>
+      <x:c r="G24" s="20" t="n">
+        <x:v>46294.58333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
-      <x:c r="A25" s="20" t="d">
-        <x:v>2026-09-29T14:00:00.000Z</x:v>
+      <x:c r="A25" s="20" t="n">
+        <x:v>46294.58333333333</x:v>
       </x:c>
       <x:c r="B25" s="8" t="n">
         <x:v>84200.01</x:v>
@@ -1635,13 +1635,13 @@
       <x:c r="F25" s="8" t="n">
         <x:v>524.37819</x:v>
       </x:c>
-      <x:c r="G25" s="20" t="d">
-        <x:v>2026-09-29T14:29:59.999Z</x:v>
+      <x:c r="G25" s="20" t="n">
+        <x:v>46294.60416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
-      <x:c r="A26" s="20" t="d">
-        <x:v>2026-09-29T14:30:00.000Z</x:v>
+      <x:c r="A26" s="20" t="n">
+        <x:v>46294.60416666667</x:v>
       </x:c>
       <x:c r="B26" s="8" t="n">
         <x:v>83942.17</x:v>
@@ -1658,13 +1658,13 @@
       <x:c r="F26" s="8" t="n">
         <x:v>526.24502</x:v>
       </x:c>
-      <x:c r="G26" s="20" t="d">
-        <x:v>2026-09-29T14:59:59.999Z</x:v>
+      <x:c r="G26" s="20" t="n">
+        <x:v>46294.62499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
-      <x:c r="A27" s="20" t="d">
-        <x:v>2026-09-29T15:00:00.000Z</x:v>
+      <x:c r="A27" s="20" t="n">
+        <x:v>46294.625</x:v>
       </x:c>
       <x:c r="B27" s="8" t="n">
         <x:v>83752</x:v>
@@ -1681,13 +1681,13 @@
       <x:c r="F27" s="8" t="n">
         <x:v>838.52587</x:v>
       </x:c>
-      <x:c r="G27" s="20" t="d">
-        <x:v>2026-09-29T15:29:59.999Z</x:v>
+      <x:c r="G27" s="20" t="n">
+        <x:v>46294.64583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
-      <x:c r="A28" s="20" t="d">
-        <x:v>2026-09-29T15:30:00.000Z</x:v>
+      <x:c r="A28" s="20" t="n">
+        <x:v>46294.64583333333</x:v>
       </x:c>
       <x:c r="B28" s="8" t="n">
         <x:v>82994.53</x:v>
@@ -1704,13 +1704,13 @@
       <x:c r="F28" s="8" t="n">
         <x:v>653.58479</x:v>
       </x:c>
-      <x:c r="G28" s="20" t="d">
-        <x:v>2026-09-29T15:59:59.999Z</x:v>
+      <x:c r="G28" s="20" t="n">
+        <x:v>46294.66666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
-      <x:c r="A29" s="20" t="d">
-        <x:v>2026-09-29T16:00:00.000Z</x:v>
+      <x:c r="A29" s="20" t="n">
+        <x:v>46294.66666666667</x:v>
       </x:c>
       <x:c r="B29" s="8" t="n">
         <x:v>83068</x:v>
@@ -1727,13 +1727,13 @@
       <x:c r="F29" s="8" t="n">
         <x:v>401.71157</x:v>
       </x:c>
-      <x:c r="G29" s="20" t="d">
-        <x:v>2026-09-29T16:29:59.999Z</x:v>
+      <x:c r="G29" s="20" t="n">
+        <x:v>46294.68749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
-      <x:c r="A30" s="20" t="d">
-        <x:v>2026-09-29T16:30:00.000Z</x:v>
+      <x:c r="A30" s="20" t="n">
+        <x:v>46294.6875</x:v>
       </x:c>
       <x:c r="B30" s="8" t="n">
         <x:v>83258.01</x:v>
@@ -1750,13 +1750,13 @@
       <x:c r="F30" s="8" t="n">
         <x:v>282.35824</x:v>
       </x:c>
-      <x:c r="G30" s="20" t="d">
-        <x:v>2026-09-29T16:59:59.999Z</x:v>
+      <x:c r="G30" s="20" t="n">
+        <x:v>46294.70833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
-      <x:c r="A31" s="20" t="d">
-        <x:v>2026-09-29T17:00:00.000Z</x:v>
+      <x:c r="A31" s="20" t="n">
+        <x:v>46294.70833333333</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
         <x:v>83061.28</x:v>
@@ -1773,13 +1773,13 @@
       <x:c r="F31" s="8" t="n">
         <x:v>224.09034</x:v>
       </x:c>
-      <x:c r="G31" s="20" t="d">
-        <x:v>2026-09-29T17:29:59.999Z</x:v>
+      <x:c r="G31" s="20" t="n">
+        <x:v>46294.72916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
-      <x:c r="A32" s="20" t="d">
-        <x:v>2026-09-29T17:30:00.000Z</x:v>
+      <x:c r="A32" s="20" t="n">
+        <x:v>46294.72916666667</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
         <x:v>83178.01</x:v>
@@ -1796,13 +1796,13 @@
       <x:c r="F32" s="8" t="n">
         <x:v>159.20664</x:v>
       </x:c>
-      <x:c r="G32" s="20" t="d">
-        <x:v>2026-09-29T17:59:59.999Z</x:v>
+      <x:c r="G32" s="20" t="n">
+        <x:v>46294.74999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
-      <x:c r="A33" s="20" t="d">
-        <x:v>2026-09-29T18:00:00.000Z</x:v>
+      <x:c r="A33" s="20" t="n">
+        <x:v>46294.75</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
         <x:v>83078.01</x:v>
@@ -1819,13 +1819,13 @@
       <x:c r="F33" s="8" t="n">
         <x:v>210.65405</x:v>
       </x:c>
-      <x:c r="G33" s="20" t="d">
-        <x:v>2026-09-29T18:29:59.999Z</x:v>
+      <x:c r="G33" s="20" t="n">
+        <x:v>46294.77083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
-      <x:c r="A34" s="20" t="d">
-        <x:v>2026-09-29T18:30:00.000Z</x:v>
+      <x:c r="A34" s="20" t="n">
+        <x:v>46294.77083333333</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
         <x:v>83427.66</x:v>
@@ -1842,13 +1842,13 @@
       <x:c r="F34" s="8" t="n">
         <x:v>183.36628</x:v>
       </x:c>
-      <x:c r="G34" s="20" t="d">
-        <x:v>2026-09-29T18:59:59.999Z</x:v>
+      <x:c r="G34" s="20" t="n">
+        <x:v>46294.79166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
-      <x:c r="A35" s="20" t="d">
-        <x:v>2026-09-29T19:00:00.000Z</x:v>
+      <x:c r="A35" s="20" t="n">
+        <x:v>46294.79166666667</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
         <x:v>83640</x:v>
@@ -1865,13 +1865,13 @@
       <x:c r="F35" s="8" t="n">
         <x:v>133.28186</x:v>
       </x:c>
-      <x:c r="G35" s="20" t="d">
-        <x:v>2026-09-29T19:29:59.999Z</x:v>
+      <x:c r="G35" s="20" t="n">
+        <x:v>46294.81249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
-      <x:c r="A36" s="20" t="d">
-        <x:v>2026-09-29T19:30:00.000Z</x:v>
+      <x:c r="A36" s="20" t="n">
+        <x:v>46294.8125</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
         <x:v>83547.99</x:v>
@@ -1888,13 +1888,13 @@
       <x:c r="F36" s="8" t="n">
         <x:v>186.93631</x:v>
       </x:c>
-      <x:c r="G36" s="20" t="d">
-        <x:v>2026-09-29T19:59:59.999Z</x:v>
+      <x:c r="G36" s="20" t="n">
+        <x:v>46294.83333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
-      <x:c r="A37" s="20" t="d">
-        <x:v>2026-09-29T20:00:00.000Z</x:v>
+      <x:c r="A37" s="20" t="n">
+        <x:v>46294.83333333333</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
         <x:v>83594.01</x:v>
@@ -1911,13 +1911,13 @@
       <x:c r="F37" s="8" t="n">
         <x:v>121.65783</x:v>
       </x:c>
-      <x:c r="G37" s="20" t="d">
-        <x:v>2026-09-29T20:29:59.999Z</x:v>
+      <x:c r="G37" s="20" t="n">
+        <x:v>46294.85416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
-      <x:c r="A38" s="20" t="d">
-        <x:v>2026-09-29T20:30:00.000Z</x:v>
+      <x:c r="A38" s="20" t="n">
+        <x:v>46294.85416666667</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
         <x:v>83630.26</x:v>
@@ -1934,13 +1934,13 @@
       <x:c r="F38" s="8" t="n">
         <x:v>82.60417</x:v>
       </x:c>
-      <x:c r="G38" s="20" t="d">
-        <x:v>2026-09-29T20:59:59.999Z</x:v>
+      <x:c r="G38" s="20" t="n">
+        <x:v>46294.87499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
-      <x:c r="A39" s="20" t="d">
-        <x:v>2026-09-29T21:00:00.000Z</x:v>
+      <x:c r="A39" s="20" t="n">
+        <x:v>46294.875</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
         <x:v>83616.38</x:v>
@@ -1957,13 +1957,13 @@
       <x:c r="F39" s="8" t="n">
         <x:v>235.71899</x:v>
       </x:c>
-      <x:c r="G39" s="20" t="d">
-        <x:v>2026-09-29T21:29:59.999Z</x:v>
+      <x:c r="G39" s="20" t="n">
+        <x:v>46294.89583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
-      <x:c r="A40" s="20" t="d">
-        <x:v>2026-09-29T21:30:00.000Z</x:v>
+      <x:c r="A40" s="20" t="n">
+        <x:v>46294.89583333333</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
         <x:v>83422.01</x:v>
@@ -1980,13 +1980,13 @@
       <x:c r="F40" s="8" t="n">
         <x:v>108.44055</x:v>
       </x:c>
-      <x:c r="G40" s="20" t="d">
-        <x:v>2026-09-29T21:59:59.999Z</x:v>
+      <x:c r="G40" s="20" t="n">
+        <x:v>46294.91666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
-      <x:c r="A41" s="20" t="d">
-        <x:v>2026-09-30T00:00:00.000Z</x:v>
+      <x:c r="A41" s="20" t="n">
+        <x:v>46294.91666666667</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
         <x:v>83503.99</x:v>
@@ -2003,13 +2003,13 @@
       <x:c r="F41" s="8" t="n">
         <x:v>145.02974</x:v>
       </x:c>
-      <x:c r="G41" s="20" t="d">
-        <x:v>2026-09-29T22:29:59.999Z</x:v>
+      <x:c r="G41" s="20" t="n">
+        <x:v>46294.93749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
-      <x:c r="A42" s="20" t="d">
-        <x:v>2026-09-29T22:30:00.000Z</x:v>
+      <x:c r="A42" s="20" t="n">
+        <x:v>46294.9375</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
         <x:v>83598.01</x:v>
@@ -2026,13 +2026,13 @@
       <x:c r="F42" s="8" t="n">
         <x:v>129.86333</x:v>
       </x:c>
-      <x:c r="G42" s="20" t="d">
-        <x:v>2026-09-29T22:59:59.999Z</x:v>
+      <x:c r="G42" s="20" t="n">
+        <x:v>46294.95833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
-      <x:c r="A43" s="20" t="d">
-        <x:v>2026-09-29T23:00:00.000Z</x:v>
+      <x:c r="A43" s="20" t="n">
+        <x:v>46294.95833333333</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
         <x:v>83612</x:v>
@@ -2049,13 +2049,13 @@
       <x:c r="F43" s="8" t="n">
         <x:v>186.95331</x:v>
       </x:c>
-      <x:c r="G43" s="20" t="d">
-        <x:v>2026-09-29T23:29:59.999Z</x:v>
+      <x:c r="G43" s="20" t="n">
+        <x:v>46294.97916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
-      <x:c r="A44" s="20" t="d">
-        <x:v>2026-09-29T23:30:00.000Z</x:v>
+      <x:c r="A44" s="20" t="n">
+        <x:v>46294.97916666667</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
         <x:v>83759.04</x:v>
@@ -2072,13 +2072,13 @@
       <x:c r="F44" s="8" t="n">
         <x:v>104.8931</x:v>
       </x:c>
-      <x:c r="G44" s="20" t="d">
-        <x:v>2026-09-29T23:59:59.999Z</x:v>
+      <x:c r="G44" s="20" t="n">
+        <x:v>46294.99999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
-      <x:c r="A45" s="20" t="d">
-        <x:v>2026-09-30T00:00:00.000Z</x:v>
+      <x:c r="A45" s="20" t="n">
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
         <x:v>83663.66</x:v>
@@ -2095,13 +2095,13 @@
       <x:c r="F45" s="8" t="n">
         <x:v>230.9377</x:v>
       </x:c>
-      <x:c r="G45" s="20" t="d">
-        <x:v>2026-09-30T00:29:59.999Z</x:v>
+      <x:c r="G45" s="20" t="n">
+        <x:v>46295.02083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
-      <x:c r="A46" s="20" t="d">
-        <x:v>2026-09-30T00:30:00.000Z</x:v>
+      <x:c r="A46" s="20" t="n">
+        <x:v>46295.02083333333</x:v>
       </x:c>
       <x:c r="B46" s="8" t="n">
         <x:v>83578</x:v>
@@ -2118,13 +2118,13 @@
       <x:c r="F46" s="8" t="n">
         <x:v>179.92421</x:v>
       </x:c>
-      <x:c r="G46" s="20" t="d">
-        <x:v>2026-09-30T00:59:59.999Z</x:v>
+      <x:c r="G46" s="20" t="n">
+        <x:v>46295.04166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
-      <x:c r="A47" s="20" t="d">
-        <x:v>2026-09-30T01:00:00.000Z</x:v>
+      <x:c r="A47" s="20" t="n">
+        <x:v>46295.04166666667</x:v>
       </x:c>
       <x:c r="B47" s="8" t="n">
         <x:v>83453.36</x:v>
@@ -2141,13 +2141,13 @@
       <x:c r="F47" s="8" t="n">
         <x:v>273.96137</x:v>
       </x:c>
-      <x:c r="G47" s="20" t="d">
-        <x:v>2026-09-30T01:29:59.999Z</x:v>
+      <x:c r="G47" s="20" t="n">
+        <x:v>46295.06249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
-      <x:c r="A48" s="20" t="d">
-        <x:v>2026-09-30T01:30:00.000Z</x:v>
+      <x:c r="A48" s="20" t="n">
+        <x:v>46295.0625</x:v>
       </x:c>
       <x:c r="B48" s="8" t="n">
         <x:v>83429.19</x:v>
@@ -2164,13 +2164,13 @@
       <x:c r="F48" s="8" t="n">
         <x:v>134.50477</x:v>
       </x:c>
-      <x:c r="G48" s="20" t="d">
-        <x:v>2026-09-30T01:59:59.999Z</x:v>
+      <x:c r="G48" s="20" t="n">
+        <x:v>46295.08333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
-      <x:c r="A49" s="20" t="d">
-        <x:v>2026-09-30T02:00:00.000Z</x:v>
+      <x:c r="A49" s="20" t="n">
+        <x:v>46295.08333333333</x:v>
       </x:c>
       <x:c r="B49" s="8" t="n">
         <x:v>83448.01</x:v>
@@ -2187,13 +2187,13 @@
       <x:c r="F49" s="8" t="n">
         <x:v>170.11266</x:v>
       </x:c>
-      <x:c r="G49" s="20" t="d">
-        <x:v>2026-09-30T02:29:59.999Z</x:v>
+      <x:c r="G49" s="20" t="n">
+        <x:v>46295.10416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
-      <x:c r="A50" s="20" t="d">
-        <x:v>2026-09-30T02:30:00.000Z</x:v>
+      <x:c r="A50" s="20" t="n">
+        <x:v>46295.10416666667</x:v>
       </x:c>
       <x:c r="B50" s="8" t="n">
         <x:v>83420.01</x:v>
@@ -2210,13 +2210,13 @@
       <x:c r="F50" s="8" t="n">
         <x:v>172.22615</x:v>
       </x:c>
-      <x:c r="G50" s="20" t="d">
-        <x:v>2026-09-30T02:59:59.999Z</x:v>
+      <x:c r="G50" s="20" t="n">
+        <x:v>46295.12499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
-      <x:c r="A51" s="20" t="d">
-        <x:v>2026-09-30T03:00:00.000Z</x:v>
+      <x:c r="A51" s="20" t="n">
+        <x:v>46295.125</x:v>
       </x:c>
       <x:c r="B51" s="8" t="n">
         <x:v>83384.68</x:v>
@@ -2233,13 +2233,13 @@
       <x:c r="F51" s="8" t="n">
         <x:v>169.06728</x:v>
       </x:c>
-      <x:c r="G51" s="20" t="d">
-        <x:v>2026-09-30T03:29:59.999Z</x:v>
+      <x:c r="G51" s="20" t="n">
+        <x:v>46295.14583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
-      <x:c r="A52" s="20" t="d">
-        <x:v>2026-09-30T03:30:00.000Z</x:v>
+      <x:c r="A52" s="20" t="n">
+        <x:v>46295.14583333333</x:v>
       </x:c>
       <x:c r="B52" s="8" t="n">
         <x:v>83321.39</x:v>
@@ -2256,13 +2256,13 @@
       <x:c r="F52" s="8" t="n">
         <x:v>95.6884</x:v>
       </x:c>
-      <x:c r="G52" s="20" t="d">
-        <x:v>2026-09-30T03:59:59.999Z</x:v>
+      <x:c r="G52" s="20" t="n">
+        <x:v>46295.16666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
-      <x:c r="A53" s="20" t="d">
-        <x:v>2026-09-30T04:00:00.000Z</x:v>
+      <x:c r="A53" s="20" t="n">
+        <x:v>46295.16666666667</x:v>
       </x:c>
       <x:c r="B53" s="8" t="n">
         <x:v>83300.65</x:v>
@@ -2279,13 +2279,13 @@
       <x:c r="F53" s="8" t="n">
         <x:v>145.35712</x:v>
       </x:c>
-      <x:c r="G53" s="20" t="d">
-        <x:v>2026-09-30T04:29:59.999Z</x:v>
+      <x:c r="G53" s="20" t="n">
+        <x:v>46295.18749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
-      <x:c r="A54" s="20" t="d">
-        <x:v>2026-09-30T04:30:00.000Z</x:v>
+      <x:c r="A54" s="20" t="n">
+        <x:v>46295.1875</x:v>
       </x:c>
       <x:c r="B54" s="8" t="n">
         <x:v>83370.01</x:v>
@@ -2302,13 +2302,13 @@
       <x:c r="F54" s="8" t="n">
         <x:v>141.12655</x:v>
       </x:c>
-      <x:c r="G54" s="20" t="d">
-        <x:v>2026-09-30T04:59:59.999Z</x:v>
+      <x:c r="G54" s="20" t="n">
+        <x:v>46295.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
-      <x:c r="A55" s="20" t="d">
-        <x:v>2026-09-30T05:00:00.000Z</x:v>
+      <x:c r="A55" s="20" t="n">
+        <x:v>46295.20833333333</x:v>
       </x:c>
       <x:c r="B55" s="8" t="n">
         <x:v>83210.01</x:v>
@@ -2325,13 +2325,13 @@
       <x:c r="F55" s="8" t="n">
         <x:v>236.51977</x:v>
       </x:c>
-      <x:c r="G55" s="20" t="d">
-        <x:v>2026-09-30T05:29:59.999Z</x:v>
+      <x:c r="G55" s="20" t="n">
+        <x:v>46295.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
-      <x:c r="A56" s="20" t="d">
-        <x:v>2026-09-30T05:30:00.000Z</x:v>
+      <x:c r="A56" s="20" t="n">
+        <x:v>46295.22916666667</x:v>
       </x:c>
       <x:c r="B56" s="8" t="n">
         <x:v>83383.96</x:v>
@@ -2348,13 +2348,13 @@
       <x:c r="F56" s="8" t="n">
         <x:v>204.31383</x:v>
       </x:c>
-      <x:c r="G56" s="20" t="d">
-        <x:v>2026-09-30T05:59:59.999Z</x:v>
+      <x:c r="G56" s="20" t="n">
+        <x:v>46295.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
-      <x:c r="A57" s="20" t="d">
-        <x:v>2026-09-30T06:00:00.000Z</x:v>
+      <x:c r="A57" s="20" t="n">
+        <x:v>46295.25</x:v>
       </x:c>
       <x:c r="B57" s="8" t="n">
         <x:v>83384.01</x:v>
@@ -2371,13 +2371,13 @@
       <x:c r="F57" s="8" t="n">
         <x:v>281.46991</x:v>
       </x:c>
-      <x:c r="G57" s="20" t="d">
-        <x:v>2026-09-30T06:29:59.999Z</x:v>
+      <x:c r="G57" s="20" t="n">
+        <x:v>46295.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
-      <x:c r="A58" s="20" t="d">
-        <x:v>2026-09-30T06:30:00.000Z</x:v>
+      <x:c r="A58" s="20" t="n">
+        <x:v>46295.27083333333</x:v>
       </x:c>
       <x:c r="B58" s="8" t="n">
         <x:v>83160.05</x:v>
@@ -2394,13 +2394,13 @@
       <x:c r="F58" s="8" t="n">
         <x:v>248.83003</x:v>
       </x:c>
-      <x:c r="G58" s="20" t="d">
-        <x:v>2026-09-30T06:59:59.999Z</x:v>
+      <x:c r="G58" s="20" t="n">
+        <x:v>46295.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="42" customHeight="1">
-      <x:c r="A59" s="20" t="d">
-        <x:v>2026-09-30T07:00:00.000Z</x:v>
+      <x:c r="A59" s="20" t="n">
+        <x:v>46295.29166666667</x:v>
       </x:c>
       <x:c r="B59" s="8" t="n">
         <x:v>83043.14</x:v>
@@ -2417,13 +2417,13 @@
       <x:c r="F59" s="8" t="n">
         <x:v>269.04851</x:v>
       </x:c>
-      <x:c r="G59" s="20" t="d">
-        <x:v>2026-09-30T07:29:59.999Z</x:v>
+      <x:c r="G59" s="20" t="n">
+        <x:v>46295.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="42" customHeight="1">
-      <x:c r="A60" s="20" t="d">
-        <x:v>2026-09-30T07:30:00.000Z</x:v>
+      <x:c r="A60" s="20" t="n">
+        <x:v>46295.3125</x:v>
       </x:c>
       <x:c r="B60" s="8" t="n">
         <x:v>83308</x:v>
@@ -2440,13 +2440,13 @@
       <x:c r="F60" s="8" t="n">
         <x:v>419.11729</x:v>
       </x:c>
-      <x:c r="G60" s="20" t="d">
-        <x:v>2026-09-30T07:59:59.999Z</x:v>
+      <x:c r="G60" s="20" t="n">
+        <x:v>46295.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
-      <x:c r="A61" s="20" t="d">
-        <x:v>2026-09-30T08:00:00.000Z</x:v>
+      <x:c r="A61" s="20" t="n">
+        <x:v>46295.33333333333</x:v>
       </x:c>
       <x:c r="B61" s="8" t="n">
         <x:v>83304.92</x:v>
@@ -2463,13 +2463,13 @@
       <x:c r="F61" s="8" t="n">
         <x:v>327.51499</x:v>
       </x:c>
-      <x:c r="G61" s="20" t="d">
-        <x:v>2026-09-30T08:29:59.999Z</x:v>
+      <x:c r="G61" s="20" t="n">
+        <x:v>46295.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
-      <x:c r="A62" s="20" t="d">
-        <x:v>2026-09-30T08:30:00.000Z</x:v>
+      <x:c r="A62" s="20" t="n">
+        <x:v>46295.35416666667</x:v>
       </x:c>
       <x:c r="B62" s="8" t="n">
         <x:v>83134</x:v>
@@ -2486,13 +2486,13 @@
       <x:c r="F62" s="8" t="n">
         <x:v>300.75192</x:v>
       </x:c>
-      <x:c r="G62" s="20" t="d">
-        <x:v>2026-09-30T08:59:59.999Z</x:v>
+      <x:c r="G62" s="20" t="n">
+        <x:v>46295.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="42" customHeight="1">
-      <x:c r="A63" s="20" t="d">
-        <x:v>2026-09-30T09:00:00.000Z</x:v>
+      <x:c r="A63" s="20" t="n">
+        <x:v>46295.375</x:v>
       </x:c>
       <x:c r="B63" s="8" t="n">
         <x:v>83062.41</x:v>
@@ -2509,13 +2509,13 @@
       <x:c r="F63" s="8" t="n">
         <x:v>212.08709</x:v>
       </x:c>
-      <x:c r="G63" s="20" t="d">
-        <x:v>2026-09-30T09:29:59.999Z</x:v>
+      <x:c r="G63" s="20" t="n">
+        <x:v>46295.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="42" customHeight="1">
-      <x:c r="A64" s="20" t="d">
-        <x:v>2026-09-30T09:30:00.000Z</x:v>
+      <x:c r="A64" s="20" t="n">
+        <x:v>46295.39583333333</x:v>
       </x:c>
       <x:c r="B64" s="8" t="n">
         <x:v>83426.96</x:v>
@@ -2532,13 +2532,13 @@
       <x:c r="F64" s="8" t="n">
         <x:v>432.66679</x:v>
       </x:c>
-      <x:c r="G64" s="20" t="d">
-        <x:v>2026-09-30T09:59:59.999Z</x:v>
+      <x:c r="G64" s="20" t="n">
+        <x:v>46295.41666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="42" customHeight="1">
-      <x:c r="A65" s="20" t="d">
-        <x:v>2026-09-30T10:00:00.000Z</x:v>
+      <x:c r="A65" s="20" t="n">
+        <x:v>46295.41666666667</x:v>
       </x:c>
       <x:c r="B65" s="8" t="n">
         <x:v>83632.01</x:v>
@@ -2555,13 +2555,13 @@
       <x:c r="F65" s="8" t="n">
         <x:v>519.57779</x:v>
       </x:c>
-      <x:c r="G65" s="20" t="d">
-        <x:v>2026-09-30T10:29:59.999Z</x:v>
+      <x:c r="G65" s="20" t="n">
+        <x:v>46295.43749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="42" customHeight="1">
-      <x:c r="A66" s="20" t="d">
-        <x:v>2026-09-30T10:30:00.000Z</x:v>
+      <x:c r="A66" s="20" t="n">
+        <x:v>46295.4375</x:v>
       </x:c>
       <x:c r="B66" s="8" t="n">
         <x:v>83787.91</x:v>
@@ -2578,13 +2578,13 @@
       <x:c r="F66" s="8" t="n">
         <x:v>238.88448</x:v>
       </x:c>
-      <x:c r="G66" s="20" t="d">
-        <x:v>2026-09-30T10:59:59.999Z</x:v>
+      <x:c r="G66" s="20" t="n">
+        <x:v>46295.45833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="42" customHeight="1">
-      <x:c r="A67" s="20" t="d">
-        <x:v>2026-09-30T11:00:00.000Z</x:v>
+      <x:c r="A67" s="20" t="n">
+        <x:v>46295.45833333333</x:v>
       </x:c>
       <x:c r="B67" s="8" t="n">
         <x:v>83918</x:v>
@@ -2601,13 +2601,13 @@
       <x:c r="F67" s="8" t="n">
         <x:v>196.49747</x:v>
       </x:c>
-      <x:c r="G67" s="20" t="d">
-        <x:v>2026-09-30T11:29:59.999Z</x:v>
+      <x:c r="G67" s="20" t="n">
+        <x:v>46295.47916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
-      <x:c r="A68" s="20" t="d">
-        <x:v>2026-09-30T11:30:00.000Z</x:v>
+      <x:c r="A68" s="20" t="n">
+        <x:v>46295.47916666667</x:v>
       </x:c>
       <x:c r="B68" s="8" t="n">
         <x:v>83858.01</x:v>
@@ -2624,13 +2624,13 @@
       <x:c r="F68" s="8" t="n">
         <x:v>252.6715</x:v>
       </x:c>
-      <x:c r="G68" s="20" t="d">
-        <x:v>2026-09-30T11:59:59.999Z</x:v>
+      <x:c r="G68" s="20" t="n">
+        <x:v>46295.49999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
-      <x:c r="A69" s="20" t="d">
-        <x:v>2026-09-30T12:00:00.000Z</x:v>
+      <x:c r="A69" s="20" t="n">
+        <x:v>46295.5</x:v>
       </x:c>
       <x:c r="B69" s="8" t="n">
         <x:v>83915.17</x:v>
@@ -2647,13 +2647,13 @@
       <x:c r="F69" s="8" t="n">
         <x:v>228.34394</x:v>
       </x:c>
-      <x:c r="G69" s="20" t="d">
-        <x:v>2026-09-30T12:29:59.999Z</x:v>
+      <x:c r="G69" s="20" t="n">
+        <x:v>46295.52083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
-      <x:c r="A70" s="20" t="d">
-        <x:v>2026-09-30T12:30:00.000Z</x:v>
+      <x:c r="A70" s="20" t="n">
+        <x:v>46295.52083333333</x:v>
       </x:c>
       <x:c r="B70" s="8" t="n">
         <x:v>83939.61</x:v>
@@ -2670,13 +2670,13 @@
       <x:c r="F70" s="8" t="n">
         <x:v>3621.75767</x:v>
       </x:c>
-      <x:c r="G70" s="20" t="d">
-        <x:v>2026-09-30T12:59:59.999Z</x:v>
+      <x:c r="G70" s="20" t="n">
+        <x:v>46295.54166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="42" customHeight="1">
-      <x:c r="A71" s="20" t="d">
-        <x:v>2026-09-30T13:00:00.000Z</x:v>
+      <x:c r="A71" s="20" t="n">
+        <x:v>46295.54166666667</x:v>
       </x:c>
       <x:c r="B71" s="8" t="n">
         <x:v>85290.32</x:v>
@@ -2693,13 +2693,13 @@
       <x:c r="F71" s="8" t="n">
         <x:v>1171.0427</x:v>
       </x:c>
-      <x:c r="G71" s="20" t="d">
-        <x:v>2026-09-30T13:29:59.999Z</x:v>
+      <x:c r="G71" s="20" t="n">
+        <x:v>46295.56249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="42" customHeight="1">
-      <x:c r="A72" s="20" t="d">
-        <x:v>2026-09-30T13:30:00.000Z</x:v>
+      <x:c r="A72" s="20" t="n">
+        <x:v>46295.5625</x:v>
       </x:c>
       <x:c r="B72" s="8" t="n">
         <x:v>85188.01</x:v>
@@ -2716,13 +2716,13 @@
       <x:c r="F72" s="8" t="n">
         <x:v>1212.51829</x:v>
       </x:c>
-      <x:c r="G72" s="20" t="d">
-        <x:v>2026-09-30T13:59:59.999Z</x:v>
+      <x:c r="G72" s="20" t="n">
+        <x:v>46295.58333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
-      <x:c r="A73" s="20" t="d">
-        <x:v>2026-09-30T14:00:00.000Z</x:v>
+      <x:c r="A73" s="20" t="n">
+        <x:v>46295.58333333333</x:v>
       </x:c>
       <x:c r="B73" s="8" t="n">
         <x:v>84637.74</x:v>
@@ -2739,13 +2739,13 @@
       <x:c r="F73" s="8" t="n">
         <x:v>992.54712</x:v>
       </x:c>
-      <x:c r="G73" s="20" t="d">
-        <x:v>2026-09-30T14:29:59.999Z</x:v>
+      <x:c r="G73" s="20" t="n">
+        <x:v>46295.60416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
-      <x:c r="A74" s="20" t="d">
-        <x:v>2026-09-30T14:30:00.000Z</x:v>
+      <x:c r="A74" s="20" t="n">
+        <x:v>46295.60416666667</x:v>
       </x:c>
       <x:c r="B74" s="8" t="n">
         <x:v>83768.38</x:v>
@@ -2762,13 +2762,13 @@
       <x:c r="F74" s="8" t="n">
         <x:v>905.41873</x:v>
       </x:c>
-      <x:c r="G74" s="20" t="d">
-        <x:v>2026-09-30T14:59:59.999Z</x:v>
+      <x:c r="G74" s="20" t="n">
+        <x:v>46295.62499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
-      <x:c r="A75" s="20" t="d">
-        <x:v>2026-09-30T15:00:00.000Z</x:v>
+      <x:c r="A75" s="20" t="n">
+        <x:v>46295.625</x:v>
       </x:c>
       <x:c r="B75" s="8" t="n">
         <x:v>83800.01</x:v>
@@ -2785,13 +2785,13 @@
       <x:c r="F75" s="8" t="n">
         <x:v>441.81278</x:v>
       </x:c>
-      <x:c r="G75" s="20" t="d">
-        <x:v>2026-09-30T15:29:59.999Z</x:v>
+      <x:c r="G75" s="20" t="n">
+        <x:v>46295.64583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
-      <x:c r="A76" s="20" t="d">
-        <x:v>2026-09-30T15:30:00.000Z</x:v>
+      <x:c r="A76" s="20" t="n">
+        <x:v>46295.64583333333</x:v>
       </x:c>
       <x:c r="B76" s="8" t="n">
         <x:v>83895.49</x:v>
@@ -2808,13 +2808,13 @@
       <x:c r="F76" s="8" t="n">
         <x:v>369.17852</x:v>
       </x:c>
-      <x:c r="G76" s="20" t="d">
-        <x:v>2026-09-30T15:59:59.999Z</x:v>
+      <x:c r="G76" s="20" t="n">
+        <x:v>46295.66666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
-      <x:c r="A77" s="20" t="d">
-        <x:v>2026-09-30T16:00:00.000Z</x:v>
+      <x:c r="A77" s="20" t="n">
+        <x:v>46295.66666666667</x:v>
       </x:c>
       <x:c r="B77" s="8" t="n">
         <x:v>84134.43</x:v>
@@ -2831,13 +2831,13 @@
       <x:c r="F77" s="8" t="n">
         <x:v>349.37143</x:v>
       </x:c>
-      <x:c r="G77" s="20" t="d">
-        <x:v>2026-09-30T16:29:59.999Z</x:v>
+      <x:c r="G77" s="20" t="n">
+        <x:v>46295.68749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
-      <x:c r="A78" s="20" t="d">
-        <x:v>2026-09-30T16:30:00.000Z</x:v>
+      <x:c r="A78" s="20" t="n">
+        <x:v>46295.6875</x:v>
       </x:c>
       <x:c r="B78" s="8" t="n">
         <x:v>84294.01</x:v>
@@ -2854,13 +2854,13 @@
       <x:c r="F78" s="8" t="n">
         <x:v>222.4526</x:v>
       </x:c>
-      <x:c r="G78" s="20" t="d">
-        <x:v>2026-09-30T16:59:59.999Z</x:v>
+      <x:c r="G78" s="20" t="n">
+        <x:v>46295.70833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
-      <x:c r="A79" s="20" t="d">
-        <x:v>2026-09-30T17:00:00.000Z</x:v>
+      <x:c r="A79" s="20" t="n">
+        <x:v>46295.70833333333</x:v>
       </x:c>
       <x:c r="B79" s="8" t="n">
         <x:v>84349.44</x:v>
@@ -2877,13 +2877,13 @@
       <x:c r="F79" s="8" t="n">
         <x:v>292.11711</x:v>
       </x:c>
-      <x:c r="G79" s="20" t="d">
-        <x:v>2026-09-30T17:29:59.999Z</x:v>
+      <x:c r="G79" s="20" t="n">
+        <x:v>46295.72916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
-      <x:c r="A80" s="20" t="d">
-        <x:v>2026-09-30T17:30:00.000Z</x:v>
+      <x:c r="A80" s="20" t="n">
+        <x:v>46295.72916666667</x:v>
       </x:c>
       <x:c r="B80" s="8" t="n">
         <x:v>84217.36</x:v>
@@ -2900,13 +2900,13 @@
       <x:c r="F80" s="8" t="n">
         <x:v>300.5586</x:v>
       </x:c>
-      <x:c r="G80" s="20" t="d">
-        <x:v>2026-09-30T17:59:59.999Z</x:v>
+      <x:c r="G80" s="20" t="n">
+        <x:v>46295.74999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
-      <x:c r="A81" s="20" t="d">
-        <x:v>2026-09-30T18:00:00.000Z</x:v>
+      <x:c r="A81" s="20" t="n">
+        <x:v>46295.75</x:v>
       </x:c>
       <x:c r="B81" s="8" t="n">
         <x:v>84031.47</x:v>
@@ -2923,13 +2923,13 @@
       <x:c r="F81" s="8" t="n">
         <x:v>234.44399</x:v>
       </x:c>
-      <x:c r="G81" s="20" t="d">
-        <x:v>2026-09-30T18:29:59.999Z</x:v>
+      <x:c r="G81" s="20" t="n">
+        <x:v>46295.77083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
-      <x:c r="A82" s="20" t="d">
-        <x:v>2026-09-30T18:30:00.000Z</x:v>
+      <x:c r="A82" s="20" t="n">
+        <x:v>46295.77083333333</x:v>
       </x:c>
       <x:c r="B82" s="8" t="n">
         <x:v>83919.81</x:v>
@@ -2946,13 +2946,13 @@
       <x:c r="F82" s="8" t="n">
         <x:v>197.68634</x:v>
       </x:c>
-      <x:c r="G82" s="20" t="d">
-        <x:v>2026-09-30T18:59:59.999Z</x:v>
+      <x:c r="G82" s="20" t="n">
+        <x:v>46295.79166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
-      <x:c r="A83" s="20" t="d">
-        <x:v>2026-09-30T19:00:00.000Z</x:v>
+      <x:c r="A83" s="20" t="n">
+        <x:v>46295.79166666667</x:v>
       </x:c>
       <x:c r="B83" s="8" t="n">
         <x:v>83950.01</x:v>
@@ -2969,13 +2969,13 @@
       <x:c r="F83" s="8" t="n">
         <x:v>220.55144</x:v>
       </x:c>
-      <x:c r="G83" s="20" t="d">
-        <x:v>2026-09-30T19:29:59.999Z</x:v>
+      <x:c r="G83" s="20" t="n">
+        <x:v>46295.81249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="42" customHeight="1">
-      <x:c r="A84" s="20" t="d">
-        <x:v>2026-09-30T19:30:00.000Z</x:v>
+      <x:c r="A84" s="20" t="n">
+        <x:v>46295.8125</x:v>
       </x:c>
       <x:c r="B84" s="8" t="n">
         <x:v>83749.24</x:v>
@@ -2992,13 +2992,13 @@
       <x:c r="F84" s="8" t="n">
         <x:v>281.81786</x:v>
       </x:c>
-      <x:c r="G84" s="20" t="d">
-        <x:v>2026-09-30T19:59:59.999Z</x:v>
+      <x:c r="G84" s="20" t="n">
+        <x:v>46295.83333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
-      <x:c r="A85" s="20" t="d">
-        <x:v>2026-09-30T20:00:00.000Z</x:v>
+      <x:c r="A85" s="20" t="n">
+        <x:v>46295.83333333333</x:v>
       </x:c>
       <x:c r="B85" s="8" t="n">
         <x:v>83603.16</x:v>
@@ -3015,13 +3015,13 @@
       <x:c r="F85" s="8" t="n">
         <x:v>308.79313</x:v>
       </x:c>
-      <x:c r="G85" s="20" t="d">
-        <x:v>2026-09-30T20:29:59.999Z</x:v>
+      <x:c r="G85" s="20" t="n">
+        <x:v>46295.85416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="42" customHeight="1">
-      <x:c r="A86" s="20" t="d">
-        <x:v>2026-09-30T20:30:00.000Z</x:v>
+      <x:c r="A86" s="20" t="n">
+        <x:v>46295.85416666667</x:v>
       </x:c>
       <x:c r="B86" s="8" t="n">
         <x:v>83725.99</x:v>
@@ -3038,13 +3038,13 @@
       <x:c r="F86" s="8" t="n">
         <x:v>111.29607</x:v>
       </x:c>
-      <x:c r="G86" s="20" t="d">
-        <x:v>2026-09-30T20:59:59.999Z</x:v>
+      <x:c r="G86" s="20" t="n">
+        <x:v>46295.87499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="42" customHeight="1">
-      <x:c r="A87" s="20" t="d">
-        <x:v>2026-09-30T21:00:00.000Z</x:v>
+      <x:c r="A87" s="20" t="n">
+        <x:v>46295.875</x:v>
       </x:c>
       <x:c r="B87" s="8" t="n">
         <x:v>83673.99</x:v>
@@ -3061,13 +3061,13 @@
       <x:c r="F87" s="8" t="n">
         <x:v>189.89998</x:v>
       </x:c>
-      <x:c r="G87" s="20" t="d">
-        <x:v>2026-09-30T21:29:59.999Z</x:v>
+      <x:c r="G87" s="20" t="n">
+        <x:v>46295.89583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="42" customHeight="1">
-      <x:c r="A88" s="20" t="d">
-        <x:v>2026-09-30T21:30:00.000Z</x:v>
+      <x:c r="A88" s="20" t="n">
+        <x:v>46295.89583333333</x:v>
       </x:c>
       <x:c r="B88" s="8" t="n">
         <x:v>83726</x:v>
@@ -3084,13 +3084,13 @@
       <x:c r="F88" s="8" t="n">
         <x:v>112.18869</x:v>
       </x:c>
-      <x:c r="G88" s="20" t="d">
-        <x:v>2026-09-30T21:59:59.999Z</x:v>
+      <x:c r="G88" s="20" t="n">
+        <x:v>46295.91666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="42" customHeight="1">
-      <x:c r="A89" s="20" t="d">
-        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      <x:c r="A89" s="20" t="n">
+        <x:v>46295.91666666667</x:v>
       </x:c>
       <x:c r="B89" s="8" t="n">
         <x:v>83757.73</x:v>
@@ -3107,13 +3107,13 @@
       <x:c r="F89" s="8" t="n">
         <x:v>127.62186</x:v>
       </x:c>
-      <x:c r="G89" s="20" t="d">
-        <x:v>2026-09-30T22:29:59.999Z</x:v>
+      <x:c r="G89" s="20" t="n">
+        <x:v>46295.93749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="42" customHeight="1">
-      <x:c r="A90" s="20" t="d">
-        <x:v>2026-09-30T22:30:00.000Z</x:v>
+      <x:c r="A90" s="20" t="n">
+        <x:v>46295.9375</x:v>
       </x:c>
       <x:c r="B90" s="8" t="n">
         <x:v>83824</x:v>
@@ -3130,13 +3130,13 @@
       <x:c r="F90" s="8" t="n">
         <x:v>87.27234</x:v>
       </x:c>
-      <x:c r="G90" s="20" t="d">
-        <x:v>2026-09-30T22:59:59.999Z</x:v>
+      <x:c r="G90" s="20" t="n">
+        <x:v>46295.95833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="42" customHeight="1">
-      <x:c r="A91" s="20" t="d">
-        <x:v>2026-09-30T23:00:00.000Z</x:v>
+      <x:c r="A91" s="20" t="n">
+        <x:v>46295.95833333333</x:v>
       </x:c>
       <x:c r="B91" s="8" t="n">
         <x:v>83685.86</x:v>
@@ -3153,13 +3153,13 @@
       <x:c r="F91" s="8" t="n">
         <x:v>347.94319</x:v>
       </x:c>
-      <x:c r="G91" s="20" t="d">
-        <x:v>2026-09-30T23:29:59.999Z</x:v>
+      <x:c r="G91" s="20" t="n">
+        <x:v>46295.97916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="42" customHeight="1">
-      <x:c r="A92" s="20" t="d">
-        <x:v>2026-09-30T23:30:00.000Z</x:v>
+      <x:c r="A92" s="20" t="n">
+        <x:v>46295.97916666667</x:v>
       </x:c>
       <x:c r="B92" s="8" t="n">
         <x:v>83662</x:v>
@@ -3176,13 +3176,13 @@
       <x:c r="F92" s="8" t="n">
         <x:v>343.32805</x:v>
       </x:c>
-      <x:c r="G92" s="20" t="d">
-        <x:v>2026-09-30T23:59:59.999Z</x:v>
+      <x:c r="G92" s="20" t="n">
+        <x:v>46295.99999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="42" customHeight="1">
-      <x:c r="A93" s="20" t="d">
-        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      <x:c r="A93" s="20" t="n">
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="B93" s="8" t="n">
         <x:v>83623.59</x:v>
@@ -3199,13 +3199,13 @@
       <x:c r="F93" s="8" t="n">
         <x:v>269.18982</x:v>
       </x:c>
-      <x:c r="G93" s="20" t="d">
-        <x:v>2026-10-01T00:29:59.999Z</x:v>
+      <x:c r="G93" s="20" t="n">
+        <x:v>46296.02083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
-      <x:c r="A94" s="20" t="d">
-        <x:v>2026-10-01T00:30:00.000Z</x:v>
+      <x:c r="A94" s="20" t="n">
+        <x:v>46296.02083333333</x:v>
       </x:c>
       <x:c r="B94" s="8" t="n">
         <x:v>83488.01</x:v>
@@ -3222,13 +3222,13 @@
       <x:c r="F94" s="8" t="n">
         <x:v>182.50536</x:v>
       </x:c>
-      <x:c r="G94" s="20" t="d">
-        <x:v>2026-10-01T00:59:59.999Z</x:v>
+      <x:c r="G94" s="20" t="n">
+        <x:v>46296.04166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
-      <x:c r="A95" s="20" t="d">
-        <x:v>2026-10-01T01:00:00.000Z</x:v>
+      <x:c r="A95" s="20" t="n">
+        <x:v>46296.04166666667</x:v>
       </x:c>
       <x:c r="B95" s="8" t="n">
         <x:v>83509.03</x:v>
@@ -3245,13 +3245,13 @@
       <x:c r="F95" s="8" t="n">
         <x:v>212.21309</x:v>
       </x:c>
-      <x:c r="G95" s="20" t="d">
-        <x:v>2026-10-01T01:29:59.999Z</x:v>
+      <x:c r="G95" s="20" t="n">
+        <x:v>46296.06249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="42" customHeight="1">
-      <x:c r="A96" s="20" t="d">
-        <x:v>2026-10-01T01:30:00.000Z</x:v>
+      <x:c r="A96" s="20" t="n">
+        <x:v>46296.0625</x:v>
       </x:c>
       <x:c r="B96" s="8" t="n">
         <x:v>83635.01</x:v>
@@ -3268,13 +3268,13 @@
       <x:c r="F96" s="8" t="n">
         <x:v>131.23431</x:v>
       </x:c>
-      <x:c r="G96" s="20" t="d">
-        <x:v>2026-10-01T01:59:59.999Z</x:v>
+      <x:c r="G96" s="20" t="n">
+        <x:v>46296.08333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
-      <x:c r="A97" s="20" t="d">
-        <x:v>2026-10-01T02:00:00.000Z</x:v>
+      <x:c r="A97" s="20" t="n">
+        <x:v>46296.08333333333</x:v>
       </x:c>
       <x:c r="B97" s="8" t="n">
         <x:v>83518.07</x:v>
@@ -3291,13 +3291,13 @@
       <x:c r="F97" s="8" t="n">
         <x:v>166.25599</x:v>
       </x:c>
-      <x:c r="G97" s="20" t="d">
-        <x:v>2026-10-01T02:29:59.999Z</x:v>
+      <x:c r="G97" s="20" t="n">
+        <x:v>46296.10416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="42" customHeight="1">
-      <x:c r="A98" s="20" t="d">
-        <x:v>2026-10-01T02:30:00.000Z</x:v>
+      <x:c r="A98" s="20" t="n">
+        <x:v>46296.10416666667</x:v>
       </x:c>
       <x:c r="B98" s="8" t="n">
         <x:v>83541.32</x:v>
@@ -3314,13 +3314,13 @@
       <x:c r="F98" s="8" t="n">
         <x:v>195.89096</x:v>
       </x:c>
-      <x:c r="G98" s="20" t="d">
-        <x:v>2026-10-01T02:59:59.999Z</x:v>
+      <x:c r="G98" s="20" t="n">
+        <x:v>46296.12499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
-      <x:c r="A99" s="20" t="d">
-        <x:v>2026-10-01T03:00:00.000Z</x:v>
+      <x:c r="A99" s="20" t="n">
+        <x:v>46296.125</x:v>
       </x:c>
       <x:c r="B99" s="8" t="n">
         <x:v>83490.78</x:v>
@@ -3337,13 +3337,13 @@
       <x:c r="F99" s="8" t="n">
         <x:v>143.23814</x:v>
       </x:c>
-      <x:c r="G99" s="20" t="d">
-        <x:v>2026-10-01T03:29:59.999Z</x:v>
+      <x:c r="G99" s="20" t="n">
+        <x:v>46296.14583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
-      <x:c r="A100" s="20" t="d">
-        <x:v>2026-10-01T03:30:00.000Z</x:v>
+      <x:c r="A100" s="20" t="n">
+        <x:v>46296.14583333333</x:v>
       </x:c>
       <x:c r="B100" s="8" t="n">
         <x:v>83529.32</x:v>
@@ -3360,13 +3360,13 @@
       <x:c r="F100" s="8" t="n">
         <x:v>181.77812</x:v>
       </x:c>
-      <x:c r="G100" s="20" t="d">
-        <x:v>2026-10-01T03:59:59.999Z</x:v>
+      <x:c r="G100" s="20" t="n">
+        <x:v>46296.16666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
-      <x:c r="A101" s="20" t="d">
-        <x:v>2026-10-01T04:00:00.000Z</x:v>
+      <x:c r="A101" s="20" t="n">
+        <x:v>46296.16666666667</x:v>
       </x:c>
       <x:c r="B101" s="8" t="n">
         <x:v>83754.01</x:v>
@@ -3383,13 +3383,13 @@
       <x:c r="F101" s="8" t="n">
         <x:v>239.61354</x:v>
       </x:c>
-      <x:c r="G101" s="20" t="d">
-        <x:v>2026-10-01T04:29:59.999Z</x:v>
+      <x:c r="G101" s="20" t="n">
+        <x:v>46296.18749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
-      <x:c r="A102" s="20" t="d">
-        <x:v>2026-10-01T04:30:00.000Z</x:v>
+      <x:c r="A102" s="20" t="n">
+        <x:v>46296.1875</x:v>
       </x:c>
       <x:c r="B102" s="8" t="n">
         <x:v>83860</x:v>
@@ -3406,13 +3406,13 @@
       <x:c r="F102" s="8" t="n">
         <x:v>275.01468</x:v>
       </x:c>
-      <x:c r="G102" s="20" t="d">
-        <x:v>2026-10-01T04:59:59.999Z</x:v>
+      <x:c r="G102" s="20" t="n">
+        <x:v>46296.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
-      <x:c r="A103" s="20" t="d">
-        <x:v>2026-10-01T05:00:00.000Z</x:v>
+      <x:c r="A103" s="20" t="n">
+        <x:v>46296.20833333333</x:v>
       </x:c>
       <x:c r="B103" s="8" t="n">
         <x:v>84110.01</x:v>
@@ -3429,13 +3429,13 @@
       <x:c r="F103" s="8" t="n">
         <x:v>262.52789</x:v>
       </x:c>
-      <x:c r="G103" s="20" t="d">
-        <x:v>2026-10-01T05:29:59.999Z</x:v>
+      <x:c r="G103" s="20" t="n">
+        <x:v>46296.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="42" customHeight="1">
-      <x:c r="A104" s="20" t="d">
-        <x:v>2026-10-01T05:30:00.000Z</x:v>
+      <x:c r="A104" s="20" t="n">
+        <x:v>46296.22916666667</x:v>
       </x:c>
       <x:c r="B104" s="8" t="n">
         <x:v>84288.21</x:v>
@@ -3452,13 +3452,13 @@
       <x:c r="F104" s="8" t="n">
         <x:v>157.51663</x:v>
       </x:c>
-      <x:c r="G104" s="20" t="d">
-        <x:v>2026-10-01T05:59:59.999Z</x:v>
+      <x:c r="G104" s="20" t="n">
+        <x:v>46296.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
-      <x:c r="A105" s="20" t="d">
-        <x:v>2026-10-01T06:00:00.000Z</x:v>
+      <x:c r="A105" s="20" t="n">
+        <x:v>46296.25</x:v>
       </x:c>
       <x:c r="B105" s="8" t="n">
         <x:v>84291.49</x:v>
@@ -3475,13 +3475,13 @@
       <x:c r="F105" s="8" t="n">
         <x:v>193.09808</x:v>
       </x:c>
-      <x:c r="G105" s="20" t="d">
-        <x:v>2026-10-01T06:29:59.999Z</x:v>
+      <x:c r="G105" s="20" t="n">
+        <x:v>46296.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
-      <x:c r="A106" s="20" t="d">
-        <x:v>2026-10-01T06:30:00.000Z</x:v>
+      <x:c r="A106" s="20" t="n">
+        <x:v>46296.27083333333</x:v>
       </x:c>
       <x:c r="B106" s="8" t="n">
         <x:v>84347.34</x:v>
@@ -3498,13 +3498,13 @@
       <x:c r="F106" s="8" t="n">
         <x:v>205.49655</x:v>
       </x:c>
-      <x:c r="G106" s="20" t="d">
-        <x:v>2026-10-01T06:59:59.999Z</x:v>
+      <x:c r="G106" s="20" t="n">
+        <x:v>46296.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
-      <x:c r="A107" s="20" t="d">
-        <x:v>2026-10-01T07:00:00.000Z</x:v>
+      <x:c r="A107" s="20" t="n">
+        <x:v>46296.29166666667</x:v>
       </x:c>
       <x:c r="B107" s="8" t="n">
         <x:v>84121.45</x:v>
@@ -3521,13 +3521,13 @@
       <x:c r="F107" s="8" t="n">
         <x:v>758.24963</x:v>
       </x:c>
-      <x:c r="G107" s="20" t="d">
-        <x:v>2026-10-01T07:29:59.999Z</x:v>
+      <x:c r="G107" s="20" t="n">
+        <x:v>46296.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="42" customHeight="1">
-      <x:c r="A108" s="20" t="d">
-        <x:v>2026-10-01T07:30:00.000Z</x:v>
+      <x:c r="A108" s="20" t="n">
+        <x:v>46296.3125</x:v>
       </x:c>
       <x:c r="B108" s="8" t="n">
         <x:v>83364.3</x:v>
@@ -3544,13 +3544,13 @@
       <x:c r="F108" s="8" t="n">
         <x:v>675.28424</x:v>
       </x:c>
-      <x:c r="G108" s="20" t="d">
-        <x:v>2026-10-01T07:59:59.999Z</x:v>
+      <x:c r="G108" s="20" t="n">
+        <x:v>46296.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
-      <x:c r="A109" s="20" t="d">
-        <x:v>2026-10-01T08:00:00.000Z</x:v>
+      <x:c r="A109" s="20" t="n">
+        <x:v>46296.33333333333</x:v>
       </x:c>
       <x:c r="B109" s="8" t="n">
         <x:v>83429.93</x:v>
@@ -3567,13 +3567,13 @@
       <x:c r="F109" s="8" t="n">
         <x:v>813.08693</x:v>
       </x:c>
-      <x:c r="G109" s="20" t="d">
-        <x:v>2026-10-01T08:29:59.999Z</x:v>
+      <x:c r="G109" s="20" t="n">
+        <x:v>46296.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="42" customHeight="1">
-      <x:c r="A110" s="20" t="d">
-        <x:v>2026-10-01T08:30:00.000Z</x:v>
+      <x:c r="A110" s="20" t="n">
+        <x:v>46296.35416666667</x:v>
       </x:c>
       <x:c r="B110" s="8" t="n">
         <x:v>83431.3</x:v>
@@ -3590,13 +3590,13 @@
       <x:c r="F110" s="8" t="n">
         <x:v>615.7104</x:v>
       </x:c>
-      <x:c r="G110" s="20" t="d">
-        <x:v>2026-10-01T08:59:59.999Z</x:v>
+      <x:c r="G110" s="20" t="n">
+        <x:v>46296.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="42" customHeight="1">
-      <x:c r="A111" s="20" t="d">
-        <x:v>2026-10-01T09:00:00.000Z</x:v>
+      <x:c r="A111" s="20" t="n">
+        <x:v>46296.375</x:v>
       </x:c>
       <x:c r="B111" s="8" t="n">
         <x:v>83566.98</x:v>
@@ -3613,13 +3613,13 @@
       <x:c r="F111" s="8" t="n">
         <x:v>397.49744</x:v>
       </x:c>
-      <x:c r="G111" s="20" t="d">
-        <x:v>2026-10-01T09:29:59.999Z</x:v>
+      <x:c r="G111" s="20" t="n">
+        <x:v>46296.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="42" customHeight="1">
-      <x:c r="A112" s="20" t="d">
-        <x:v>2026-10-01T09:30:00.000Z</x:v>
+      <x:c r="A112" s="20" t="n">
+        <x:v>46296.39583333333</x:v>
       </x:c>
       <x:c r="B112" s="8" t="n">
         <x:v>83761.88</x:v>
@@ -3636,13 +3636,13 @@
       <x:c r="F112" s="8" t="n">
         <x:v>323.61718</x:v>
       </x:c>
-      <x:c r="G112" s="20" t="d">
-        <x:v>2026-10-01T09:59:59.999Z</x:v>
+      <x:c r="G112" s="20" t="n">
+        <x:v>46296.41666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="42" customHeight="1">
-      <x:c r="A113" s="20" t="d">
-        <x:v>2026-10-01T10:00:00.000Z</x:v>
+      <x:c r="A113" s="20" t="n">
+        <x:v>46296.41666666667</x:v>
       </x:c>
       <x:c r="B113" s="8" t="n">
         <x:v>83782.01</x:v>
@@ -3659,13 +3659,13 @@
       <x:c r="F113" s="8" t="n">
         <x:v>245.55034</x:v>
       </x:c>
-      <x:c r="G113" s="20" t="d">
-        <x:v>2026-10-01T10:29:59.999Z</x:v>
+      <x:c r="G113" s="20" t="n">
+        <x:v>46296.43749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="42" customHeight="1">
-      <x:c r="A114" s="20" t="d">
-        <x:v>2026-10-01T10:30:00.000Z</x:v>
+      <x:c r="A114" s="20" t="n">
+        <x:v>46296.4375</x:v>
       </x:c>
       <x:c r="B114" s="8" t="n">
         <x:v>83686.64</x:v>
@@ -3682,13 +3682,13 @@
       <x:c r="F114" s="8" t="n">
         <x:v>220.13596</x:v>
       </x:c>
-      <x:c r="G114" s="20" t="d">
-        <x:v>2026-10-01T10:59:59.999Z</x:v>
+      <x:c r="G114" s="20" t="n">
+        <x:v>46296.45833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="42" customHeight="1">
-      <x:c r="A115" s="20" t="d">
-        <x:v>2026-10-01T11:00:00.000Z</x:v>
+      <x:c r="A115" s="20" t="n">
+        <x:v>46296.45833333333</x:v>
       </x:c>
       <x:c r="B115" s="8" t="n">
         <x:v>83966.27</x:v>
@@ -3705,13 +3705,13 @@
       <x:c r="F115" s="8" t="n">
         <x:v>158.80986</x:v>
       </x:c>
-      <x:c r="G115" s="20" t="d">
-        <x:v>2026-10-01T11:29:59.999Z</x:v>
+      <x:c r="G115" s="20" t="n">
+        <x:v>46296.47916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="42" customHeight="1">
-      <x:c r="A116" s="20" t="d">
-        <x:v>2026-10-01T11:30:00.000Z</x:v>
+      <x:c r="A116" s="20" t="n">
+        <x:v>46296.47916666667</x:v>
       </x:c>
       <x:c r="B116" s="8" t="n">
         <x:v>83874.01</x:v>
@@ -3728,13 +3728,13 @@
       <x:c r="F116" s="8" t="n">
         <x:v>265.20874</x:v>
       </x:c>
-      <x:c r="G116" s="20" t="d">
-        <x:v>2026-10-01T11:59:59.999Z</x:v>
+      <x:c r="G116" s="20" t="n">
+        <x:v>46296.49999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="42" customHeight="1">
-      <x:c r="A117" s="20" t="d">
-        <x:v>2026-10-01T12:00:00.000Z</x:v>
+      <x:c r="A117" s="20" t="n">
+        <x:v>46296.5</x:v>
       </x:c>
       <x:c r="B117" s="8" t="n">
         <x:v>83905.76</x:v>
@@ -3751,13 +3751,13 @@
       <x:c r="F117" s="8" t="n">
         <x:v>196.6013</x:v>
       </x:c>
-      <x:c r="G117" s="20" t="d">
-        <x:v>2026-10-01T12:29:59.999Z</x:v>
+      <x:c r="G117" s="20" t="n">
+        <x:v>46296.52083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="42" customHeight="1">
-      <x:c r="A118" s="20" t="d">
-        <x:v>2026-10-01T12:30:00.000Z</x:v>
+      <x:c r="A118" s="20" t="n">
+        <x:v>46296.52083333333</x:v>
       </x:c>
       <x:c r="B118" s="8" t="n">
         <x:v>83912.01</x:v>
@@ -3774,13 +3774,13 @@
       <x:c r="F118" s="8" t="n">
         <x:v>214.27946</x:v>
       </x:c>
-      <x:c r="G118" s="20" t="d">
-        <x:v>2026-10-01T12:59:59.999Z</x:v>
+      <x:c r="G118" s="20" t="n">
+        <x:v>46296.54166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="42" customHeight="1">
-      <x:c r="A119" s="20" t="d">
-        <x:v>2026-10-01T13:00:00.000Z</x:v>
+      <x:c r="A119" s="20" t="n">
+        <x:v>46296.54166666667</x:v>
       </x:c>
       <x:c r="B119" s="8" t="n">
         <x:v>83736.02</x:v>
@@ -3797,13 +3797,13 @@
       <x:c r="F119" s="8" t="n">
         <x:v>374.42677</x:v>
       </x:c>
-      <x:c r="G119" s="20" t="d">
-        <x:v>2026-10-01T13:29:59.999Z</x:v>
+      <x:c r="G119" s="20" t="n">
+        <x:v>46296.56249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="42" customHeight="1">
-      <x:c r="A120" s="20" t="d">
-        <x:v>2026-10-01T13:30:00.000Z</x:v>
+      <x:c r="A120" s="20" t="n">
+        <x:v>46296.5625</x:v>
       </x:c>
       <x:c r="B120" s="8" t="n">
         <x:v>83476.04</x:v>
@@ -3820,13 +3820,13 @@
       <x:c r="F120" s="8" t="n">
         <x:v>623.90601</x:v>
       </x:c>
-      <x:c r="G120" s="20" t="d">
-        <x:v>2026-10-01T13:59:59.999Z</x:v>
+      <x:c r="G120" s="20" t="n">
+        <x:v>46296.58333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="42" customHeight="1">
-      <x:c r="A121" s="20" t="d">
-        <x:v>2026-10-01T14:00:00.000Z</x:v>
+      <x:c r="A121" s="20" t="n">
+        <x:v>46296.58333333333</x:v>
       </x:c>
       <x:c r="B121" s="8" t="n">
         <x:v>83938.6</x:v>
@@ -3843,13 +3843,13 @@
       <x:c r="F121" s="8" t="n">
         <x:v>605.03551</x:v>
       </x:c>
-      <x:c r="G121" s="20" t="d">
-        <x:v>2026-10-01T14:29:59.999Z</x:v>
+      <x:c r="G121" s="20" t="n">
+        <x:v>46296.60416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="42" customHeight="1">
-      <x:c r="A122" s="20" t="d">
-        <x:v>2026-10-01T14:30:00.000Z</x:v>
+      <x:c r="A122" s="20" t="n">
+        <x:v>46296.60416666667</x:v>
       </x:c>
       <x:c r="B122" s="8" t="n">
         <x:v>84120</x:v>
@@ -3866,13 +3866,13 @@
       <x:c r="F122" s="8" t="n">
         <x:v>538.39969</x:v>
       </x:c>
-      <x:c r="G122" s="20" t="d">
-        <x:v>2026-10-01T14:59:59.999Z</x:v>
+      <x:c r="G122" s="20" t="n">
+        <x:v>46296.62499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="42" customHeight="1">
-      <x:c r="A123" s="20" t="d">
-        <x:v>2026-10-01T15:00:00.000Z</x:v>
+      <x:c r="A123" s="20" t="n">
+        <x:v>46296.625</x:v>
       </x:c>
       <x:c r="B123" s="8" t="n">
         <x:v>84050.65</x:v>
@@ -3889,13 +3889,13 @@
       <x:c r="F123" s="8" t="n">
         <x:v>1760.94094</x:v>
       </x:c>
-      <x:c r="G123" s="20" t="d">
-        <x:v>2026-10-01T15:29:59.999Z</x:v>
+      <x:c r="G123" s="20" t="n">
+        <x:v>46296.64583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="42" customHeight="1">
-      <x:c r="A124" s="20" t="d">
-        <x:v>2026-10-01T15:30:00.000Z</x:v>
+      <x:c r="A124" s="20" t="n">
+        <x:v>46296.64583333333</x:v>
       </x:c>
       <x:c r="B124" s="8" t="n">
         <x:v>84094.27</x:v>
@@ -3912,13 +3912,13 @@
       <x:c r="F124" s="8" t="n">
         <x:v>474.99122</x:v>
       </x:c>
-      <x:c r="G124" s="20" t="d">
-        <x:v>2026-10-01T15:59:59.999Z</x:v>
+      <x:c r="G124" s="20" t="n">
+        <x:v>46296.66666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="42" customHeight="1">
-      <x:c r="A125" s="20" t="d">
-        <x:v>2026-10-01T16:00:00.000Z</x:v>
+      <x:c r="A125" s="20" t="n">
+        <x:v>46296.66666666667</x:v>
       </x:c>
       <x:c r="B125" s="8" t="n">
         <x:v>84162.66</x:v>
@@ -3935,13 +3935,13 @@
       <x:c r="F125" s="8" t="n">
         <x:v>373.30165</x:v>
       </x:c>
-      <x:c r="G125" s="20" t="d">
-        <x:v>2026-10-01T16:29:59.999Z</x:v>
+      <x:c r="G125" s="20" t="n">
+        <x:v>46296.68749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="42" customHeight="1">
-      <x:c r="A126" s="20" t="d">
-        <x:v>2026-10-01T16:30:00.000Z</x:v>
+      <x:c r="A126" s="20" t="n">
+        <x:v>46296.6875</x:v>
       </x:c>
       <x:c r="B126" s="8" t="n">
         <x:v>84305.49</x:v>
@@ -3958,13 +3958,13 @@
       <x:c r="F126" s="8" t="n">
         <x:v>378.43659</x:v>
       </x:c>
-      <x:c r="G126" s="20" t="d">
-        <x:v>2026-10-01T16:59:59.999Z</x:v>
+      <x:c r="G126" s="20" t="n">
+        <x:v>46296.70833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="42" customHeight="1">
-      <x:c r="A127" s="20" t="d">
-        <x:v>2026-10-01T17:00:00.000Z</x:v>
+      <x:c r="A127" s="20" t="n">
+        <x:v>46296.70833333333</x:v>
       </x:c>
       <x:c r="B127" s="8" t="n">
         <x:v>84202</x:v>
@@ -3981,13 +3981,13 @@
       <x:c r="F127" s="8" t="n">
         <x:v>441.2965</x:v>
       </x:c>
-      <x:c r="G127" s="20" t="d">
-        <x:v>2026-10-01T17:29:59.999Z</x:v>
+      <x:c r="G127" s="20" t="n">
+        <x:v>46296.72916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="42" customHeight="1">
-      <x:c r="A128" s="20" t="d">
-        <x:v>2026-10-01T17:30:00.000Z</x:v>
+      <x:c r="A128" s="20" t="n">
+        <x:v>46296.72916666667</x:v>
       </x:c>
       <x:c r="B128" s="8" t="n">
         <x:v>84919.18</x:v>
@@ -4004,13 +4004,13 @@
       <x:c r="F128" s="8" t="n">
         <x:v>719.84584</x:v>
       </x:c>
-      <x:c r="G128" s="20" t="d">
-        <x:v>2026-10-01T17:59:59.999Z</x:v>
+      <x:c r="G128" s="20" t="n">
+        <x:v>46296.74999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="42" customHeight="1">
-      <x:c r="A129" s="20" t="d">
-        <x:v>2026-10-01T18:00:00.000Z</x:v>
+      <x:c r="A129" s="20" t="n">
+        <x:v>46296.75</x:v>
       </x:c>
       <x:c r="B129" s="8" t="n">
         <x:v>84908</x:v>
@@ -4027,13 +4027,13 @@
       <x:c r="F129" s="8" t="n">
         <x:v>322.5103</x:v>
       </x:c>
-      <x:c r="G129" s="20" t="d">
-        <x:v>2026-10-01T18:29:59.999Z</x:v>
+      <x:c r="G129" s="20" t="n">
+        <x:v>46296.77083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="42" customHeight="1">
-      <x:c r="A130" s="20" t="d">
-        <x:v>2026-10-01T18:30:00.000Z</x:v>
+      <x:c r="A130" s="20" t="n">
+        <x:v>46296.77083333333</x:v>
       </x:c>
       <x:c r="B130" s="8" t="n">
         <x:v>84802.95</x:v>
@@ -4050,13 +4050,13 @@
       <x:c r="F130" s="8" t="n">
         <x:v>500.64485</x:v>
       </x:c>
-      <x:c r="G130" s="20" t="d">
-        <x:v>2026-10-01T18:59:59.999Z</x:v>
+      <x:c r="G130" s="20" t="n">
+        <x:v>46296.79166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="42" customHeight="1">
-      <x:c r="A131" s="20" t="d">
-        <x:v>2026-10-01T19:00:00.000Z</x:v>
+      <x:c r="A131" s="20" t="n">
+        <x:v>46296.79166666667</x:v>
       </x:c>
       <x:c r="B131" s="8" t="n">
         <x:v>84802.02</x:v>
@@ -4073,13 +4073,13 @@
       <x:c r="F131" s="8" t="n">
         <x:v>217.92788</x:v>
       </x:c>
-      <x:c r="G131" s="20" t="d">
-        <x:v>2026-10-01T19:29:59.999Z</x:v>
+      <x:c r="G131" s="20" t="n">
+        <x:v>46296.81249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="42" customHeight="1">
-      <x:c r="A132" s="20" t="d">
-        <x:v>2026-10-01T19:30:00.000Z</x:v>
+      <x:c r="A132" s="20" t="n">
+        <x:v>46296.8125</x:v>
       </x:c>
       <x:c r="B132" s="8" t="n">
         <x:v>84612</x:v>
@@ -4096,13 +4096,13 @@
       <x:c r="F132" s="8" t="n">
         <x:v>249.51896</x:v>
       </x:c>
-      <x:c r="G132" s="20" t="d">
-        <x:v>2026-10-01T19:59:59.999Z</x:v>
+      <x:c r="G132" s="20" t="n">
+        <x:v>46296.83333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="42" customHeight="1">
-      <x:c r="A133" s="20" t="d">
-        <x:v>2026-10-01T20:00:00.000Z</x:v>
+      <x:c r="A133" s="20" t="n">
+        <x:v>46296.83333333333</x:v>
       </x:c>
       <x:c r="B133" s="8" t="n">
         <x:v>84675.36</x:v>
@@ -4119,13 +4119,13 @@
       <x:c r="F133" s="8" t="n">
         <x:v>232.54576</x:v>
       </x:c>
-      <x:c r="G133" s="20" t="d">
-        <x:v>2026-10-01T20:29:59.999Z</x:v>
+      <x:c r="G133" s="20" t="n">
+        <x:v>46296.85416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="42" customHeight="1">
-      <x:c r="A134" s="20" t="d">
-        <x:v>2026-10-01T20:30:00.000Z</x:v>
+      <x:c r="A134" s="20" t="n">
+        <x:v>46296.85416666667</x:v>
       </x:c>
       <x:c r="B134" s="8" t="n">
         <x:v>84766.66</x:v>
@@ -4142,13 +4142,13 @@
       <x:c r="F134" s="8" t="n">
         <x:v>161.81779</x:v>
       </x:c>
-      <x:c r="G134" s="20" t="d">
-        <x:v>2026-10-01T20:59:59.999Z</x:v>
+      <x:c r="G134" s="20" t="n">
+        <x:v>46296.87499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="42" customHeight="1">
-      <x:c r="A135" s="20" t="d">
-        <x:v>2026-10-01T21:00:00.000Z</x:v>
+      <x:c r="A135" s="20" t="n">
+        <x:v>46296.875</x:v>
       </x:c>
       <x:c r="B135" s="8" t="n">
         <x:v>84634.01</x:v>
@@ -4165,13 +4165,13 @@
       <x:c r="F135" s="8" t="n">
         <x:v>135.94005</x:v>
       </x:c>
-      <x:c r="G135" s="20" t="d">
-        <x:v>2026-10-01T21:29:59.999Z</x:v>
+      <x:c r="G135" s="20" t="n">
+        <x:v>46296.89583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="42" customHeight="1">
-      <x:c r="A136" s="20" t="d">
-        <x:v>2026-10-01T21:30:00.000Z</x:v>
+      <x:c r="A136" s="20" t="n">
+        <x:v>46296.89583333333</x:v>
       </x:c>
       <x:c r="B136" s="8" t="n">
         <x:v>84591.34</x:v>
@@ -4188,13 +4188,13 @@
       <x:c r="F136" s="8" t="n">
         <x:v>166.73128</x:v>
       </x:c>
-      <x:c r="G136" s="20" t="d">
-        <x:v>2026-10-01T21:59:59.999Z</x:v>
+      <x:c r="G136" s="20" t="n">
+        <x:v>46296.91666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="42" customHeight="1">
-      <x:c r="A137" s="20" t="d">
-        <x:v>2026-10-02T00:00:00.000Z</x:v>
+      <x:c r="A137" s="20" t="n">
+        <x:v>46296.91666666667</x:v>
       </x:c>
       <x:c r="B137" s="8" t="n">
         <x:v>84544.99</x:v>
@@ -4211,13 +4211,13 @@
       <x:c r="F137" s="8" t="n">
         <x:v>159.74256</x:v>
       </x:c>
-      <x:c r="G137" s="20" t="d">
-        <x:v>2026-10-01T22:29:59.999Z</x:v>
+      <x:c r="G137" s="20" t="n">
+        <x:v>46296.93749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="42" customHeight="1">
-      <x:c r="A138" s="20" t="d">
-        <x:v>2026-10-01T22:30:00.000Z</x:v>
+      <x:c r="A138" s="20" t="n">
+        <x:v>46296.9375</x:v>
       </x:c>
       <x:c r="B138" s="8" t="n">
         <x:v>84702.34</x:v>
@@ -4234,13 +4234,13 @@
       <x:c r="F138" s="8" t="n">
         <x:v>294.22513</x:v>
       </x:c>
-      <x:c r="G138" s="20" t="d">
-        <x:v>2026-10-01T22:59:59.999Z</x:v>
+      <x:c r="G138" s="20" t="n">
+        <x:v>46296.95833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="42" customHeight="1">
-      <x:c r="A139" s="20" t="d">
-        <x:v>2026-10-01T23:00:00.000Z</x:v>
+      <x:c r="A139" s="20" t="n">
+        <x:v>46296.95833333333</x:v>
       </x:c>
       <x:c r="B139" s="8" t="n">
         <x:v>84749.74</x:v>
@@ -4257,13 +4257,13 @@
       <x:c r="F139" s="8" t="n">
         <x:v>159.92409</x:v>
       </x:c>
-      <x:c r="G139" s="20" t="d">
-        <x:v>2026-10-01T23:29:59.999Z</x:v>
+      <x:c r="G139" s="20" t="n">
+        <x:v>46296.97916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="42" customHeight="1">
-      <x:c r="A140" s="20" t="d">
-        <x:v>2026-10-01T23:30:00.000Z</x:v>
+      <x:c r="A140" s="20" t="n">
+        <x:v>46296.97916666667</x:v>
       </x:c>
       <x:c r="B140" s="8" t="n">
         <x:v>84729.99</x:v>
@@ -4280,13 +4280,13 @@
       <x:c r="F140" s="8" t="n">
         <x:v>174.34274</x:v>
       </x:c>
-      <x:c r="G140" s="20" t="d">
-        <x:v>2026-10-01T23:59:59.999Z</x:v>
+      <x:c r="G140" s="20" t="n">
+        <x:v>46296.99999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="42" customHeight="1">
-      <x:c r="A141" s="20" t="d">
-        <x:v>2026-10-02T00:00:00.000Z</x:v>
+      <x:c r="A141" s="20" t="n">
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="B141" s="8" t="n">
         <x:v>84880.05</x:v>
@@ -4303,13 +4303,13 @@
       <x:c r="F141" s="8" t="n">
         <x:v>622.90257</x:v>
       </x:c>
-      <x:c r="G141" s="20" t="d">
-        <x:v>2026-10-02T00:29:59.999Z</x:v>
+      <x:c r="G141" s="20" t="n">
+        <x:v>46297.02083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="42" customHeight="1">
-      <x:c r="A142" s="20" t="d">
-        <x:v>2026-10-02T00:30:00.000Z</x:v>
+      <x:c r="A142" s="20" t="n">
+        <x:v>46297.02083333333</x:v>
       </x:c>
       <x:c r="B142" s="8" t="n">
         <x:v>84802.02</x:v>
@@ -4326,13 +4326,13 @@
       <x:c r="F142" s="8" t="n">
         <x:v>178.48007</x:v>
       </x:c>
-      <x:c r="G142" s="20" t="d">
-        <x:v>2026-10-02T00:59:59.999Z</x:v>
+      <x:c r="G142" s="20" t="n">
+        <x:v>46297.04166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="42" customHeight="1">
-      <x:c r="A143" s="20" t="d">
-        <x:v>2026-10-02T01:00:00.000Z</x:v>
+      <x:c r="A143" s="20" t="n">
+        <x:v>46297.04166666667</x:v>
       </x:c>
       <x:c r="B143" s="8" t="n">
         <x:v>84784.89</x:v>
@@ -4349,13 +4349,13 @@
       <x:c r="F143" s="8" t="n">
         <x:v>160.12674</x:v>
       </x:c>
-      <x:c r="G143" s="20" t="d">
-        <x:v>2026-10-02T01:29:59.999Z</x:v>
+      <x:c r="G143" s="20" t="n">
+        <x:v>46297.06249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="42" customHeight="1">
-      <x:c r="A144" s="20" t="d">
-        <x:v>2026-10-02T01:30:00.000Z</x:v>
+      <x:c r="A144" s="20" t="n">
+        <x:v>46297.0625</x:v>
       </x:c>
       <x:c r="B144" s="8" t="n">
         <x:v>84614</x:v>
@@ -4372,13 +4372,13 @@
       <x:c r="F144" s="8" t="n">
         <x:v>212.58963</x:v>
       </x:c>
-      <x:c r="G144" s="20" t="d">
-        <x:v>2026-10-02T01:59:59.999Z</x:v>
+      <x:c r="G144" s="20" t="n">
+        <x:v>46297.08333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="42" customHeight="1">
-      <x:c r="A145" s="20" t="d">
-        <x:v>2026-10-02T02:00:00.000Z</x:v>
+      <x:c r="A145" s="20" t="n">
+        <x:v>46297.08333333333</x:v>
       </x:c>
       <x:c r="B145" s="8" t="n">
         <x:v>84910.01</x:v>
@@ -4395,13 +4395,13 @@
       <x:c r="F145" s="8" t="n">
         <x:v>352.65682</x:v>
       </x:c>
-      <x:c r="G145" s="20" t="d">
-        <x:v>2026-10-02T02:29:59.999Z</x:v>
+      <x:c r="G145" s="20" t="n">
+        <x:v>46297.10416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="42" customHeight="1">
-      <x:c r="A146" s="20" t="d">
-        <x:v>2026-10-02T02:30:00.000Z</x:v>
+      <x:c r="A146" s="20" t="n">
+        <x:v>46297.10416666667</x:v>
       </x:c>
       <x:c r="B146" s="8" t="n">
         <x:v>84934</x:v>
@@ -4418,13 +4418,13 @@
       <x:c r="F146" s="8" t="n">
         <x:v>289.17094</x:v>
       </x:c>
-      <x:c r="G146" s="20" t="d">
-        <x:v>2026-10-02T02:59:59.999Z</x:v>
+      <x:c r="G146" s="20" t="n">
+        <x:v>46297.12499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="42" customHeight="1">
-      <x:c r="A147" s="20" t="d">
-        <x:v>2026-10-02T03:00:00.000Z</x:v>
+      <x:c r="A147" s="20" t="n">
+        <x:v>46297.125</x:v>
       </x:c>
       <x:c r="B147" s="8" t="n">
         <x:v>85187.99</x:v>
@@ -4441,13 +4441,13 @@
       <x:c r="F147" s="8" t="n">
         <x:v>500.33295</x:v>
       </x:c>
-      <x:c r="G147" s="20" t="d">
-        <x:v>2026-10-02T03:29:59.999Z</x:v>
+      <x:c r="G147" s="20" t="n">
+        <x:v>46297.14583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="42" customHeight="1">
-      <x:c r="A148" s="20" t="d">
-        <x:v>2026-10-02T03:30:00.000Z</x:v>
+      <x:c r="A148" s="20" t="n">
+        <x:v>46297.14583333333</x:v>
       </x:c>
       <x:c r="B148" s="8" t="n">
         <x:v>85280.94</x:v>
@@ -4464,13 +4464,13 @@
       <x:c r="F148" s="8" t="n">
         <x:v>279.22948</x:v>
       </x:c>
-      <x:c r="G148" s="20" t="d">
-        <x:v>2026-10-02T03:59:59.999Z</x:v>
+      <x:c r="G148" s="20" t="n">
+        <x:v>46297.16666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="42" customHeight="1">
-      <x:c r="A149" s="20" t="d">
-        <x:v>2026-10-02T04:00:00.000Z</x:v>
+      <x:c r="A149" s="20" t="n">
+        <x:v>46297.16666666667</x:v>
       </x:c>
       <x:c r="B149" s="8" t="n">
         <x:v>85512.89</x:v>
@@ -4487,13 +4487,13 @@
       <x:c r="F149" s="8" t="n">
         <x:v>1561.38524</x:v>
       </x:c>
-      <x:c r="G149" s="20" t="d">
-        <x:v>2026-10-02T04:29:59.999Z</x:v>
+      <x:c r="G149" s="20" t="n">
+        <x:v>46297.18749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="42" customHeight="1">
-      <x:c r="A150" s="20" t="d">
-        <x:v>2026-10-02T04:30:00.000Z</x:v>
+      <x:c r="A150" s="20" t="n">
+        <x:v>46297.1875</x:v>
       </x:c>
       <x:c r="B150" s="8" t="n">
         <x:v>86788.12</x:v>
@@ -4510,13 +4510,13 @@
       <x:c r="F150" s="8" t="n">
         <x:v>1116.16024</x:v>
       </x:c>
-      <x:c r="G150" s="20" t="d">
-        <x:v>2026-10-02T04:59:59.999Z</x:v>
+      <x:c r="G150" s="20" t="n">
+        <x:v>46297.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="42" customHeight="1">
-      <x:c r="A151" s="20" t="d">
-        <x:v>2026-10-02T05:00:00.000Z</x:v>
+      <x:c r="A151" s="20" t="n">
+        <x:v>46297.20833333333</x:v>
       </x:c>
       <x:c r="B151" s="8" t="n">
         <x:v>86652.12</x:v>
@@ -4533,13 +4533,13 @@
       <x:c r="F151" s="8" t="n">
         <x:v>462.75417</x:v>
       </x:c>
-      <x:c r="G151" s="20" t="d">
-        <x:v>2026-10-02T05:29:59.999Z</x:v>
+      <x:c r="G151" s="20" t="n">
+        <x:v>46297.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="42" customHeight="1">
-      <x:c r="A152" s="20" t="d">
-        <x:v>2026-10-02T05:30:00.000Z</x:v>
+      <x:c r="A152" s="20" t="n">
+        <x:v>46297.22916666667</x:v>
       </x:c>
       <x:c r="B152" s="8" t="n">
         <x:v>86346.52</x:v>
@@ -4556,13 +4556,13 @@
       <x:c r="F152" s="8" t="n">
         <x:v>417.28616</x:v>
       </x:c>
-      <x:c r="G152" s="20" t="d">
-        <x:v>2026-10-02T05:59:59.999Z</x:v>
+      <x:c r="G152" s="20" t="n">
+        <x:v>46297.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="42" customHeight="1">
-      <x:c r="A153" s="20" t="d">
-        <x:v>2026-10-02T06:00:00.000Z</x:v>
+      <x:c r="A153" s="20" t="n">
+        <x:v>46297.25</x:v>
       </x:c>
       <x:c r="B153" s="8" t="n">
         <x:v>86002.01</x:v>
@@ -4579,13 +4579,13 @@
       <x:c r="F153" s="8" t="n">
         <x:v>530.16657</x:v>
       </x:c>
-      <x:c r="G153" s="20" t="d">
-        <x:v>2026-10-02T06:29:59.999Z</x:v>
+      <x:c r="G153" s="20" t="n">
+        <x:v>46297.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="42" customHeight="1">
-      <x:c r="A154" s="20" t="d">
-        <x:v>2026-10-02T06:30:00.000Z</x:v>
+      <x:c r="A154" s="20" t="n">
+        <x:v>46297.27083333333</x:v>
       </x:c>
       <x:c r="B154" s="8" t="n">
         <x:v>86025.97</x:v>
@@ -4602,13 +4602,13 @@
       <x:c r="F154" s="8" t="n">
         <x:v>296.98844</x:v>
       </x:c>
-      <x:c r="G154" s="20" t="d">
-        <x:v>2026-10-02T06:59:59.999Z</x:v>
+      <x:c r="G154" s="20" t="n">
+        <x:v>46297.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="42" customHeight="1">
-      <x:c r="A155" s="20" t="d">
-        <x:v>2026-10-02T07:00:00.000Z</x:v>
+      <x:c r="A155" s="20" t="n">
+        <x:v>46297.29166666667</x:v>
       </x:c>
       <x:c r="B155" s="8" t="n">
         <x:v>85992.96</x:v>
@@ -4625,13 +4625,13 @@
       <x:c r="F155" s="8" t="n">
         <x:v>320.76261</x:v>
       </x:c>
-      <x:c r="G155" s="20" t="d">
-        <x:v>2026-10-02T07:29:59.999Z</x:v>
+      <x:c r="G155" s="20" t="n">
+        <x:v>46297.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="42" customHeight="1">
-      <x:c r="A156" s="20" t="d">
-        <x:v>2026-10-02T07:30:00.000Z</x:v>
+      <x:c r="A156" s="20" t="n">
+        <x:v>46297.3125</x:v>
       </x:c>
       <x:c r="B156" s="8" t="n">
         <x:v>85956.01</x:v>
@@ -4648,13 +4648,13 @@
       <x:c r="F156" s="8" t="n">
         <x:v>899.97717</x:v>
       </x:c>
-      <x:c r="G156" s="20" t="d">
-        <x:v>2026-10-02T07:59:59.999Z</x:v>
+      <x:c r="G156" s="20" t="n">
+        <x:v>46297.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="42" customHeight="1">
-      <x:c r="A157" s="20" t="d">
-        <x:v>2026-10-02T08:00:00.000Z</x:v>
+      <x:c r="A157" s="20" t="n">
+        <x:v>46297.33333333333</x:v>
       </x:c>
       <x:c r="B157" s="8" t="n">
         <x:v>86089.64</x:v>
@@ -4671,13 +4671,13 @@
       <x:c r="F157" s="8" t="n">
         <x:v>483.49577</x:v>
       </x:c>
-      <x:c r="G157" s="20" t="d">
-        <x:v>2026-10-02T08:29:59.999Z</x:v>
+      <x:c r="G157" s="20" t="n">
+        <x:v>46297.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="42" customHeight="1">
-      <x:c r="A158" s="20" t="d">
-        <x:v>2026-10-02T08:30:00.000Z</x:v>
+      <x:c r="A158" s="20" t="n">
+        <x:v>46297.35416666667</x:v>
       </x:c>
       <x:c r="B158" s="8" t="n">
         <x:v>86400</x:v>
@@ -4694,13 +4694,13 @@
       <x:c r="F158" s="8" t="n">
         <x:v>253.46268</x:v>
       </x:c>
-      <x:c r="G158" s="20" t="d">
-        <x:v>2026-10-02T08:59:59.999Z</x:v>
+      <x:c r="G158" s="20" t="n">
+        <x:v>46297.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="42" customHeight="1">
-      <x:c r="A159" s="20" t="d">
-        <x:v>2026-10-02T09:00:00.000Z</x:v>
+      <x:c r="A159" s="20" t="n">
+        <x:v>46297.375</x:v>
       </x:c>
       <x:c r="B159" s="8" t="n">
         <x:v>86236.01</x:v>
@@ -4717,13 +4717,13 @@
       <x:c r="F159" s="8" t="n">
         <x:v>1127.23131</x:v>
       </x:c>
-      <x:c r="G159" s="20" t="d">
-        <x:v>2026-10-02T09:29:59.999Z</x:v>
+      <x:c r="G159" s="20" t="n">
+        <x:v>46297.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="42" customHeight="1">
-      <x:c r="A160" s="20" t="d">
-        <x:v>2026-10-02T09:30:00.000Z</x:v>
+      <x:c r="A160" s="20" t="n">
+        <x:v>46297.39583333333</x:v>
       </x:c>
       <x:c r="B160" s="8" t="n">
         <x:v>86209.08</x:v>
@@ -4740,13 +4740,13 @@
       <x:c r="F160" s="8" t="n">
         <x:v>314.07023</x:v>
       </x:c>
-      <x:c r="G160" s="20" t="d">
-        <x:v>2026-10-02T09:59:59.999Z</x:v>
+      <x:c r="G160" s="20" t="n">
+        <x:v>46297.41666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="42" customHeight="1">
-      <x:c r="A161" s="20" t="d">
-        <x:v>2026-10-02T10:00:00.000Z</x:v>
+      <x:c r="A161" s="20" t="n">
+        <x:v>46297.41666666667</x:v>
       </x:c>
       <x:c r="B161" s="8" t="n">
         <x:v>86364.01</x:v>
@@ -4763,13 +4763,13 @@
       <x:c r="F161" s="8" t="n">
         <x:v>253.77706</x:v>
       </x:c>
-      <x:c r="G161" s="20" t="d">
-        <x:v>2026-10-02T10:29:59.999Z</x:v>
+      <x:c r="G161" s="20" t="n">
+        <x:v>46297.43749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="42" customHeight="1">
-      <x:c r="A162" s="20" t="d">
-        <x:v>2026-10-02T10:30:00.000Z</x:v>
+      <x:c r="A162" s="20" t="n">
+        <x:v>46297.4375</x:v>
       </x:c>
       <x:c r="B162" s="8" t="n">
         <x:v>86408.18</x:v>
@@ -4786,13 +4786,13 @@
       <x:c r="F162" s="8" t="n">
         <x:v>198.7484</x:v>
       </x:c>
-      <x:c r="G162" s="20" t="d">
-        <x:v>2026-10-02T10:59:59.999Z</x:v>
+      <x:c r="G162" s="20" t="n">
+        <x:v>46297.45833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="42" customHeight="1">
-      <x:c r="A163" s="20" t="d">
-        <x:v>2026-10-02T11:00:00.000Z</x:v>
+      <x:c r="A163" s="20" t="n">
+        <x:v>46297.45833333333</x:v>
       </x:c>
       <x:c r="B163" s="8" t="n">
         <x:v>86297.6</x:v>
@@ -4809,13 +4809,13 @@
       <x:c r="F163" s="8" t="n">
         <x:v>202.75491</x:v>
       </x:c>
-      <x:c r="G163" s="20" t="d">
-        <x:v>2026-10-02T11:29:59.999Z</x:v>
+      <x:c r="G163" s="20" t="n">
+        <x:v>46297.47916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="42" customHeight="1">
-      <x:c r="A164" s="20" t="d">
-        <x:v>2026-10-02T11:30:00.000Z</x:v>
+      <x:c r="A164" s="20" t="n">
+        <x:v>46297.47916666667</x:v>
       </x:c>
       <x:c r="B164" s="8" t="n">
         <x:v>86431.34</x:v>
@@ -4832,13 +4832,13 @@
       <x:c r="F164" s="8" t="n">
         <x:v>266.95933</x:v>
       </x:c>
-      <x:c r="G164" s="20" t="d">
-        <x:v>2026-10-02T11:59:59.999Z</x:v>
+      <x:c r="G164" s="20" t="n">
+        <x:v>46297.49999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="42" customHeight="1">
-      <x:c r="A165" s="20" t="d">
-        <x:v>2026-10-02T12:00:00.000Z</x:v>
+      <x:c r="A165" s="20" t="n">
+        <x:v>46297.5</x:v>
       </x:c>
       <x:c r="B165" s="8" t="n">
         <x:v>86424.85</x:v>
@@ -4855,13 +4855,13 @@
       <x:c r="F165" s="8" t="n">
         <x:v>350.41719</x:v>
       </x:c>
-      <x:c r="G165" s="20" t="d">
-        <x:v>2026-10-02T12:29:59.999Z</x:v>
+      <x:c r="G165" s="20" t="n">
+        <x:v>46297.52083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="42" customHeight="1">
-      <x:c r="A166" s="20" t="d">
-        <x:v>2026-10-02T12:30:00.000Z</x:v>
+      <x:c r="A166" s="20" t="n">
+        <x:v>46297.52083333333</x:v>
       </x:c>
       <x:c r="B166" s="8" t="n">
         <x:v>86616.35</x:v>
@@ -4878,13 +4878,13 @@
       <x:c r="F166" s="8" t="n">
         <x:v>1631.30354</x:v>
       </x:c>
-      <x:c r="G166" s="20" t="d">
-        <x:v>2026-10-02T12:59:59.999Z</x:v>
+      <x:c r="G166" s="20" t="n">
+        <x:v>46297.54166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="42" customHeight="1">
-      <x:c r="A167" s="20" t="d">
-        <x:v>2026-10-02T13:00:00.000Z</x:v>
+      <x:c r="A167" s="20" t="n">
+        <x:v>46297.54166666667</x:v>
       </x:c>
       <x:c r="B167" s="8" t="n">
         <x:v>86810.01</x:v>
@@ -4901,13 +4901,13 @@
       <x:c r="F167" s="8" t="n">
         <x:v>345.01546</x:v>
       </x:c>
-      <x:c r="G167" s="20" t="d">
-        <x:v>2026-10-02T13:29:59.999Z</x:v>
+      <x:c r="G167" s="20" t="n">
+        <x:v>46297.56249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="42" customHeight="1">
-      <x:c r="A168" s="20" t="d">
-        <x:v>2026-10-02T13:30:00.000Z</x:v>
+      <x:c r="A168" s="20" t="n">
+        <x:v>46297.5625</x:v>
       </x:c>
       <x:c r="B168" s="8" t="n">
         <x:v>86606.58</x:v>
@@ -4924,13 +4924,13 @@
       <x:c r="F168" s="8" t="n">
         <x:v>909.06752</x:v>
       </x:c>
-      <x:c r="G168" s="20" t="d">
-        <x:v>2026-10-02T13:59:59.999Z</x:v>
+      <x:c r="G168" s="20" t="n">
+        <x:v>46297.58333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="42" customHeight="1">
-      <x:c r="A169" s="20" t="d">
-        <x:v>2026-10-02T14:00:00.000Z</x:v>
+      <x:c r="A169" s="20" t="n">
+        <x:v>46297.58333333333</x:v>
       </x:c>
       <x:c r="B169" s="8" t="n">
         <x:v>86565.06</x:v>
@@ -4947,13 +4947,13 @@
       <x:c r="F169" s="8" t="n">
         <x:v>950.1803</x:v>
       </x:c>
-      <x:c r="G169" s="20" t="d">
-        <x:v>2026-10-02T14:29:59.999Z</x:v>
+      <x:c r="G169" s="20" t="n">
+        <x:v>46297.60416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="42" customHeight="1">
-      <x:c r="A170" s="20" t="d">
-        <x:v>2026-10-02T14:30:00.000Z</x:v>
+      <x:c r="A170" s="20" t="n">
+        <x:v>46297.60416666667</x:v>
       </x:c>
       <x:c r="B170" s="8" t="n">
         <x:v>86081.86</x:v>
@@ -4970,13 +4970,13 @@
       <x:c r="F170" s="8" t="n">
         <x:v>1210.82755</x:v>
       </x:c>
-      <x:c r="G170" s="20" t="d">
-        <x:v>2026-10-02T14:59:59.999Z</x:v>
+      <x:c r="G170" s="20" t="n">
+        <x:v>46297.62499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="42" customHeight="1">
-      <x:c r="A171" s="20" t="d">
-        <x:v>2026-10-02T15:00:00.000Z</x:v>
+      <x:c r="A171" s="20" t="n">
+        <x:v>46297.625</x:v>
       </x:c>
       <x:c r="B171" s="8" t="n">
         <x:v>85686.93</x:v>
@@ -4993,13 +4993,13 @@
       <x:c r="F171" s="8" t="n">
         <x:v>681.36168</x:v>
       </x:c>
-      <x:c r="G171" s="20" t="d">
-        <x:v>2026-10-02T15:29:59.999Z</x:v>
+      <x:c r="G171" s="20" t="n">
+        <x:v>46297.64583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="42" customHeight="1">
-      <x:c r="A172" s="20" t="d">
-        <x:v>2026-10-02T15:30:00.000Z</x:v>
+      <x:c r="A172" s="20" t="n">
+        <x:v>46297.64583333333</x:v>
       </x:c>
       <x:c r="B172" s="8" t="n">
         <x:v>85484</x:v>
@@ -5016,13 +5016,13 @@
       <x:c r="F172" s="8" t="n">
         <x:v>499.41624</x:v>
       </x:c>
-      <x:c r="G172" s="20" t="d">
-        <x:v>2026-10-02T15:59:59.999Z</x:v>
+      <x:c r="G172" s="20" t="n">
+        <x:v>46297.66666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="42" customHeight="1">
-      <x:c r="A173" s="20" t="d">
-        <x:v>2026-10-02T16:00:00.000Z</x:v>
+      <x:c r="A173" s="20" t="n">
+        <x:v>46297.66666666667</x:v>
       </x:c>
       <x:c r="B173" s="8" t="n">
         <x:v>85326</x:v>
@@ -5039,13 +5039,13 @@
       <x:c r="F173" s="8" t="n">
         <x:v>379.19709</x:v>
       </x:c>
-      <x:c r="G173" s="20" t="d">
-        <x:v>2026-10-02T16:29:59.999Z</x:v>
+      <x:c r="G173" s="20" t="n">
+        <x:v>46297.68749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="42" customHeight="1">
-      <x:c r="A174" s="20" t="d">
-        <x:v>2026-10-02T16:30:00.000Z</x:v>
+      <x:c r="A174" s="20" t="n">
+        <x:v>46297.6875</x:v>
       </x:c>
       <x:c r="B174" s="8" t="n">
         <x:v>85178.69</x:v>
@@ -5062,13 +5062,13 @@
       <x:c r="F174" s="8" t="n">
         <x:v>295.55204</x:v>
       </x:c>
-      <x:c r="G174" s="20" t="d">
-        <x:v>2026-10-02T16:59:59.999Z</x:v>
+      <x:c r="G174" s="20" t="n">
+        <x:v>46297.70833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="42" customHeight="1">
-      <x:c r="A175" s="20" t="d">
-        <x:v>2026-10-02T17:00:00.000Z</x:v>
+      <x:c r="A175" s="20" t="n">
+        <x:v>46297.70833333333</x:v>
       </x:c>
       <x:c r="B175" s="8" t="n">
         <x:v>85160</x:v>
@@ -5085,13 +5085,13 @@
       <x:c r="F175" s="8" t="n">
         <x:v>1968.76186</x:v>
       </x:c>
-      <x:c r="G175" s="20" t="d">
-        <x:v>2026-10-02T17:29:59.999Z</x:v>
+      <x:c r="G175" s="20" t="n">
+        <x:v>46297.72916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="42" customHeight="1">
-      <x:c r="A176" s="20" t="d">
-        <x:v>2026-10-02T17:30:00.000Z</x:v>
+      <x:c r="A176" s="20" t="n">
+        <x:v>46297.72916666667</x:v>
       </x:c>
       <x:c r="B176" s="8" t="n">
         <x:v>84584.75</x:v>
@@ -5108,13 +5108,13 @@
       <x:c r="F176" s="8" t="n">
         <x:v>1658.77458</x:v>
       </x:c>
-      <x:c r="G176" s="20" t="d">
-        <x:v>2026-10-02T17:59:59.999Z</x:v>
+      <x:c r="G176" s="20" t="n">
+        <x:v>46297.74999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="42" customHeight="1">
-      <x:c r="A177" s="20" t="d">
-        <x:v>2026-10-02T18:00:00.000Z</x:v>
+      <x:c r="A177" s="20" t="n">
+        <x:v>46297.75</x:v>
       </x:c>
       <x:c r="B177" s="8" t="n">
         <x:v>84774.75</x:v>
@@ -5131,13 +5131,13 @@
       <x:c r="F177" s="8" t="n">
         <x:v>377.99743</x:v>
       </x:c>
-      <x:c r="G177" s="20" t="d">
-        <x:v>2026-10-02T18:29:59.999Z</x:v>
+      <x:c r="G177" s="20" t="n">
+        <x:v>46297.77083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="42" customHeight="1">
-      <x:c r="A178" s="20" t="d">
-        <x:v>2026-10-02T18:30:00.000Z</x:v>
+      <x:c r="A178" s="20" t="n">
+        <x:v>46297.77083333333</x:v>
       </x:c>
       <x:c r="B178" s="8" t="n">
         <x:v>84621.25</x:v>
@@ -5154,13 +5154,13 @@
       <x:c r="F178" s="8" t="n">
         <x:v>790.56392</x:v>
       </x:c>
-      <x:c r="G178" s="20" t="d">
-        <x:v>2026-10-02T18:59:59.999Z</x:v>
+      <x:c r="G178" s="20" t="n">
+        <x:v>46297.79166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="42" customHeight="1">
-      <x:c r="A179" s="20" t="d">
-        <x:v>2026-10-02T19:00:00.000Z</x:v>
+      <x:c r="A179" s="20" t="n">
+        <x:v>46297.79166666667</x:v>
       </x:c>
       <x:c r="B179" s="8" t="n">
         <x:v>84262.01</x:v>
@@ -5177,13 +5177,13 @@
       <x:c r="F179" s="8" t="n">
         <x:v>483.91332</x:v>
       </x:c>
-      <x:c r="G179" s="20" t="d">
-        <x:v>2026-10-02T19:29:59.999Z</x:v>
+      <x:c r="G179" s="20" t="n">
+        <x:v>46297.81249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="42" customHeight="1">
-      <x:c r="A180" s="20" t="d">
-        <x:v>2026-10-02T19:30:00.000Z</x:v>
+      <x:c r="A180" s="20" t="n">
+        <x:v>46297.8125</x:v>
       </x:c>
       <x:c r="B180" s="8" t="n">
         <x:v>84141.01</x:v>
@@ -5200,13 +5200,13 @@
       <x:c r="F180" s="8" t="n">
         <x:v>631.45183</x:v>
       </x:c>
-      <x:c r="G180" s="20" t="d">
-        <x:v>2026-10-02T19:59:59.999Z</x:v>
+      <x:c r="G180" s="20" t="n">
+        <x:v>46297.83333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="42" customHeight="1">
-      <x:c r="A181" s="20" t="d">
-        <x:v>2026-10-02T20:00:00.000Z</x:v>
+      <x:c r="A181" s="20" t="n">
+        <x:v>46297.83333333333</x:v>
       </x:c>
       <x:c r="B181" s="8" t="n">
         <x:v>84315.27</x:v>
@@ -5223,13 +5223,13 @@
       <x:c r="F181" s="8" t="n">
         <x:v>313.10449</x:v>
       </x:c>
-      <x:c r="G181" s="20" t="d">
-        <x:v>2026-10-02T20:29:59.999Z</x:v>
+      <x:c r="G181" s="20" t="n">
+        <x:v>46297.85416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="42" customHeight="1">
-      <x:c r="A182" s="20" t="d">
-        <x:v>2026-10-02T20:30:00.000Z</x:v>
+      <x:c r="A182" s="20" t="n">
+        <x:v>46297.85416666667</x:v>
       </x:c>
       <x:c r="B182" s="8" t="n">
         <x:v>84348</x:v>
@@ -5246,13 +5246,13 @@
       <x:c r="F182" s="8" t="n">
         <x:v>289.48483</x:v>
       </x:c>
-      <x:c r="G182" s="20" t="d">
-        <x:v>2026-10-02T20:59:59.999Z</x:v>
+      <x:c r="G182" s="20" t="n">
+        <x:v>46297.87499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="42" customHeight="1">
-      <x:c r="A183" s="20" t="d">
-        <x:v>2026-10-02T21:00:00.000Z</x:v>
+      <x:c r="A183" s="20" t="n">
+        <x:v>46297.875</x:v>
       </x:c>
       <x:c r="B183" s="8" t="n">
         <x:v>84459.04</x:v>
@@ -5269,13 +5269,13 @@
       <x:c r="F183" s="8" t="n">
         <x:v>159.45867</x:v>
       </x:c>
-      <x:c r="G183" s="20" t="d">
-        <x:v>2026-10-02T21:29:59.999Z</x:v>
+      <x:c r="G183" s="20" t="n">
+        <x:v>46297.89583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="42" customHeight="1">
-      <x:c r="A184" s="20" t="d">
-        <x:v>2026-10-02T21:30:00.000Z</x:v>
+      <x:c r="A184" s="20" t="n">
+        <x:v>46297.89583333333</x:v>
       </x:c>
       <x:c r="B184" s="8" t="n">
         <x:v>84434</x:v>
@@ -5292,13 +5292,13 @@
       <x:c r="F184" s="8" t="n">
         <x:v>180.46799</x:v>
       </x:c>
-      <x:c r="G184" s="20" t="d">
-        <x:v>2026-10-02T21:59:59.999Z</x:v>
+      <x:c r="G184" s="20" t="n">
+        <x:v>46297.91666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="42" customHeight="1">
-      <x:c r="A185" s="20" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      <x:c r="A185" s="20" t="n">
+        <x:v>46297.91666666667</x:v>
       </x:c>
       <x:c r="B185" s="8" t="n">
         <x:v>84531.68</x:v>
@@ -5315,13 +5315,13 @@
       <x:c r="F185" s="8" t="n">
         <x:v>367.08922</x:v>
       </x:c>
-      <x:c r="G185" s="20" t="d">
-        <x:v>2026-10-02T22:29:59.999Z</x:v>
+      <x:c r="G185" s="20" t="n">
+        <x:v>46297.93749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="42" customHeight="1">
-      <x:c r="A186" s="20" t="d">
-        <x:v>2026-10-02T22:30:00.000Z</x:v>
+      <x:c r="A186" s="20" t="n">
+        <x:v>46297.9375</x:v>
       </x:c>
       <x:c r="B186" s="8" t="n">
         <x:v>84525.02</x:v>
@@ -5338,13 +5338,13 @@
       <x:c r="F186" s="8" t="n">
         <x:v>297.57487</x:v>
       </x:c>
-      <x:c r="G186" s="20" t="d">
-        <x:v>2026-10-02T22:59:59.999Z</x:v>
+      <x:c r="G186" s="20" t="n">
+        <x:v>46297.95833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="42" customHeight="1">
-      <x:c r="A187" s="20" t="d">
-        <x:v>2026-10-02T23:00:00.000Z</x:v>
+      <x:c r="A187" s="20" t="n">
+        <x:v>46297.95833333333</x:v>
       </x:c>
       <x:c r="B187" s="8" t="n">
         <x:v>84559.99</x:v>
@@ -5361,13 +5361,13 @@
       <x:c r="F187" s="8" t="n">
         <x:v>93.36216</x:v>
       </x:c>
-      <x:c r="G187" s="20" t="d">
-        <x:v>2026-10-02T23:29:59.999Z</x:v>
+      <x:c r="G187" s="20" t="n">
+        <x:v>46297.97916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="42" customHeight="1">
-      <x:c r="A188" s="20" t="d">
-        <x:v>2026-10-02T23:30:00.000Z</x:v>
+      <x:c r="A188" s="20" t="n">
+        <x:v>46297.97916666667</x:v>
       </x:c>
       <x:c r="B188" s="8" t="n">
         <x:v>84566.01</x:v>
@@ -5384,13 +5384,13 @@
       <x:c r="F188" s="8" t="n">
         <x:v>332.10627</x:v>
       </x:c>
-      <x:c r="G188" s="20" t="d">
-        <x:v>2026-10-02T23:59:59.999Z</x:v>
+      <x:c r="G188" s="20" t="n">
+        <x:v>46297.99999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="42" customHeight="1">
-      <x:c r="A189" s="20" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      <x:c r="A189" s="20" t="n">
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="B189" s="8" t="n">
         <x:v>84518</x:v>
@@ -5407,13 +5407,13 @@
       <x:c r="F189" s="8" t="n">
         <x:v>164.38288</x:v>
       </x:c>
-      <x:c r="G189" s="20" t="d">
-        <x:v>2026-10-03T00:29:59.999Z</x:v>
+      <x:c r="G189" s="20" t="n">
+        <x:v>46298.02083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="42" customHeight="1">
-      <x:c r="A190" s="20" t="d">
-        <x:v>2026-10-03T00:30:00.000Z</x:v>
+      <x:c r="A190" s="20" t="n">
+        <x:v>46298.02083333333</x:v>
       </x:c>
       <x:c r="B190" s="8" t="n">
         <x:v>84558.68</x:v>
@@ -5430,13 +5430,13 @@
       <x:c r="F190" s="8" t="n">
         <x:v>148.46316</x:v>
       </x:c>
-      <x:c r="G190" s="20" t="d">
-        <x:v>2026-10-03T00:59:59.999Z</x:v>
+      <x:c r="G190" s="20" t="n">
+        <x:v>46298.04166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="42" customHeight="1">
-      <x:c r="A191" s="20" t="d">
-        <x:v>2026-10-03T01:00:00.000Z</x:v>
+      <x:c r="A191" s="20" t="n">
+        <x:v>46298.04166666667</x:v>
       </x:c>
       <x:c r="B191" s="8" t="n">
         <x:v>84660.11</x:v>
@@ -5453,13 +5453,13 @@
       <x:c r="F191" s="8" t="n">
         <x:v>140.19768</x:v>
       </x:c>
-      <x:c r="G191" s="20" t="d">
-        <x:v>2026-10-03T01:29:59.999Z</x:v>
+      <x:c r="G191" s="20" t="n">
+        <x:v>46298.06249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="42" customHeight="1">
-      <x:c r="A192" s="20" t="d">
-        <x:v>2026-10-03T01:30:00.000Z</x:v>
+      <x:c r="A192" s="20" t="n">
+        <x:v>46298.0625</x:v>
       </x:c>
       <x:c r="B192" s="8" t="n">
         <x:v>84614.6</x:v>
@@ -5476,13 +5476,13 @@
       <x:c r="F192" s="8" t="n">
         <x:v>98.55533</x:v>
       </x:c>
-      <x:c r="G192" s="20" t="d">
-        <x:v>2026-10-03T01:59:59.999Z</x:v>
+      <x:c r="G192" s="20" t="n">
+        <x:v>46298.08333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="42" customHeight="1">
-      <x:c r="A193" s="20" t="d">
-        <x:v>2026-10-03T02:00:00.000Z</x:v>
+      <x:c r="A193" s="20" t="n">
+        <x:v>46298.08333333333</x:v>
       </x:c>
       <x:c r="B193" s="8" t="n">
         <x:v>84640.01</x:v>
@@ -5499,13 +5499,13 @@
       <x:c r="F193" s="8" t="n">
         <x:v>103.26676</x:v>
       </x:c>
-      <x:c r="G193" s="20" t="d">
-        <x:v>2026-10-03T02:29:59.999Z</x:v>
+      <x:c r="G193" s="20" t="n">
+        <x:v>46298.10416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="42" customHeight="1">
-      <x:c r="A194" s="20" t="d">
-        <x:v>2026-10-03T02:30:00.000Z</x:v>
+      <x:c r="A194" s="20" t="n">
+        <x:v>46298.10416666667</x:v>
       </x:c>
       <x:c r="B194" s="8" t="n">
         <x:v>84641.52</x:v>
@@ -5522,13 +5522,13 @@
       <x:c r="F194" s="8" t="n">
         <x:v>119.9708</x:v>
       </x:c>
-      <x:c r="G194" s="20" t="d">
-        <x:v>2026-10-03T02:59:59.999Z</x:v>
+      <x:c r="G194" s="20" t="n">
+        <x:v>46298.12499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="42" customHeight="1">
-      <x:c r="A195" s="20" t="d">
-        <x:v>2026-10-03T03:00:00.000Z</x:v>
+      <x:c r="A195" s="20" t="n">
+        <x:v>46298.125</x:v>
       </x:c>
       <x:c r="B195" s="8" t="n">
         <x:v>84600.01</x:v>
@@ -5545,13 +5545,13 @@
       <x:c r="F195" s="8" t="n">
         <x:v>108.05245</x:v>
       </x:c>
-      <x:c r="G195" s="20" t="d">
-        <x:v>2026-10-03T03:29:59.999Z</x:v>
+      <x:c r="G195" s="20" t="n">
+        <x:v>46298.14583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="42" customHeight="1">
-      <x:c r="A196" s="20" t="d">
-        <x:v>2026-10-03T03:30:00.000Z</x:v>
+      <x:c r="A196" s="20" t="n">
+        <x:v>46298.14583333333</x:v>
       </x:c>
       <x:c r="B196" s="8" t="n">
         <x:v>84594.01</x:v>
@@ -5568,13 +5568,13 @@
       <x:c r="F196" s="8" t="n">
         <x:v>102.77798</x:v>
       </x:c>
-      <x:c r="G196" s="20" t="d">
-        <x:v>2026-10-03T03:59:59.999Z</x:v>
+      <x:c r="G196" s="20" t="n">
+        <x:v>46298.16666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="42" customHeight="1">
-      <x:c r="A197" s="20" t="d">
-        <x:v>2026-10-03T04:00:00.000Z</x:v>
+      <x:c r="A197" s="20" t="n">
+        <x:v>46298.16666666667</x:v>
       </x:c>
       <x:c r="B197" s="8" t="n">
         <x:v>84699.56</x:v>
@@ -5591,13 +5591,13 @@
       <x:c r="F197" s="8" t="n">
         <x:v>74.8054</x:v>
       </x:c>
-      <x:c r="G197" s="20" t="d">
-        <x:v>2026-10-03T04:29:59.999Z</x:v>
+      <x:c r="G197" s="20" t="n">
+        <x:v>46298.18749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="42" customHeight="1">
-      <x:c r="A198" s="20" t="d">
-        <x:v>2026-10-03T04:30:00.000Z</x:v>
+      <x:c r="A198" s="20" t="n">
+        <x:v>46298.1875</x:v>
       </x:c>
       <x:c r="B198" s="8" t="n">
         <x:v>84528</x:v>
@@ -5614,13 +5614,13 @@
       <x:c r="F198" s="8" t="n">
         <x:v>77.37001</x:v>
       </x:c>
-      <x:c r="G198" s="20" t="d">
-        <x:v>2026-10-03T04:59:59.999Z</x:v>
+      <x:c r="G198" s="20" t="n">
+        <x:v>46298.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="42" customHeight="1">
-      <x:c r="A199" s="20" t="d">
-        <x:v>2026-10-03T05:00:00.000Z</x:v>
+      <x:c r="A199" s="20" t="n">
+        <x:v>46298.20833333333</x:v>
       </x:c>
       <x:c r="B199" s="8" t="n">
         <x:v>84577.23</x:v>
@@ -5637,13 +5637,13 @@
       <x:c r="F199" s="8" t="n">
         <x:v>66.94835</x:v>
       </x:c>
-      <x:c r="G199" s="20" t="d">
-        <x:v>2026-10-03T05:29:59.999Z</x:v>
+      <x:c r="G199" s="20" t="n">
+        <x:v>46298.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="42" customHeight="1">
-      <x:c r="A200" s="20" t="d">
-        <x:v>2026-10-03T05:30:00.000Z</x:v>
+      <x:c r="A200" s="20" t="n">
+        <x:v>46298.22916666667</x:v>
       </x:c>
       <x:c r="B200" s="8" t="n">
         <x:v>84619.64</x:v>
@@ -5660,13 +5660,13 @@
       <x:c r="F200" s="8" t="n">
         <x:v>80.99262</x:v>
       </x:c>
-      <x:c r="G200" s="20" t="d">
-        <x:v>2026-10-03T05:59:59.999Z</x:v>
+      <x:c r="G200" s="20" t="n">
+        <x:v>46298.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="42" customHeight="1">
-      <x:c r="A201" s="20" t="d">
-        <x:v>2026-10-03T06:00:00.000Z</x:v>
+      <x:c r="A201" s="20" t="n">
+        <x:v>46298.25</x:v>
       </x:c>
       <x:c r="B201" s="8" t="n">
         <x:v>84652.09</x:v>
@@ -5683,13 +5683,13 @@
       <x:c r="F201" s="8" t="n">
         <x:v>97.62475</x:v>
       </x:c>
-      <x:c r="G201" s="20" t="d">
-        <x:v>2026-10-03T06:29:59.999Z</x:v>
+      <x:c r="G201" s="20" t="n">
+        <x:v>46298.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="42" customHeight="1">
-      <x:c r="A202" s="20" t="d">
-        <x:v>2026-10-03T06:30:00.000Z</x:v>
+      <x:c r="A202" s="20" t="n">
+        <x:v>46298.27083333333</x:v>
       </x:c>
       <x:c r="B202" s="8" t="n">
         <x:v>84649.55</x:v>
@@ -5706,13 +5706,13 @@
       <x:c r="F202" s="8" t="n">
         <x:v>174.68638</x:v>
       </x:c>
-      <x:c r="G202" s="20" t="d">
-        <x:v>2026-10-03T06:59:59.999Z</x:v>
+      <x:c r="G202" s="20" t="n">
+        <x:v>46298.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="42" customHeight="1">
-      <x:c r="A203" s="20" t="d">
-        <x:v>2026-10-03T07:00:00.000Z</x:v>
+      <x:c r="A203" s="20" t="n">
+        <x:v>46298.29166666667</x:v>
       </x:c>
       <x:c r="B203" s="8" t="n">
         <x:v>84586.01</x:v>
@@ -5729,13 +5729,13 @@
       <x:c r="F203" s="8" t="n">
         <x:v>191.74844</x:v>
       </x:c>
-      <x:c r="G203" s="20" t="d">
-        <x:v>2026-10-03T07:29:59.999Z</x:v>
+      <x:c r="G203" s="20" t="n">
+        <x:v>46298.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="42" customHeight="1">
-      <x:c r="A204" s="20" t="d">
-        <x:v>2026-10-03T07:30:00.000Z</x:v>
+      <x:c r="A204" s="20" t="n">
+        <x:v>46298.3125</x:v>
       </x:c>
       <x:c r="B204" s="8" t="n">
         <x:v>84629.66</x:v>
@@ -5752,13 +5752,13 @@
       <x:c r="F204" s="8" t="n">
         <x:v>184.27305</x:v>
       </x:c>
-      <x:c r="G204" s="20" t="d">
-        <x:v>2026-10-03T07:59:59.999Z</x:v>
+      <x:c r="G204" s="20" t="n">
+        <x:v>46298.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="42" customHeight="1">
-      <x:c r="A205" s="20" t="d">
-        <x:v>2026-10-03T08:00:00.000Z</x:v>
+      <x:c r="A205" s="20" t="n">
+        <x:v>46298.33333333333</x:v>
       </x:c>
       <x:c r="B205" s="8" t="n">
         <x:v>84560</x:v>
@@ -5775,13 +5775,13 @@
       <x:c r="F205" s="8" t="n">
         <x:v>134.21643</x:v>
       </x:c>
-      <x:c r="G205" s="20" t="d">
-        <x:v>2026-10-03T08:29:59.999Z</x:v>
+      <x:c r="G205" s="20" t="n">
+        <x:v>46298.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="42" customHeight="1">
-      <x:c r="A206" s="20" t="d">
-        <x:v>2026-10-03T08:30:00.000Z</x:v>
+      <x:c r="A206" s="20" t="n">
+        <x:v>46298.35416666667</x:v>
       </x:c>
       <x:c r="B206" s="8" t="n">
         <x:v>84589.86</x:v>
@@ -5798,13 +5798,13 @@
       <x:c r="F206" s="8" t="n">
         <x:v>109.86405</x:v>
       </x:c>
-      <x:c r="G206" s="20" t="d">
-        <x:v>2026-10-03T08:59:59.999Z</x:v>
+      <x:c r="G206" s="20" t="n">
+        <x:v>46298.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="42" customHeight="1">
-      <x:c r="A207" s="20" t="d">
-        <x:v>2026-10-03T09:00:00.000Z</x:v>
+      <x:c r="A207" s="20" t="n">
+        <x:v>46298.375</x:v>
       </x:c>
       <x:c r="B207" s="8" t="n">
         <x:v>84616.02</x:v>
@@ -5821,13 +5821,13 @@
       <x:c r="F207" s="8" t="n">
         <x:v>76.48482</x:v>
       </x:c>
-      <x:c r="G207" s="20" t="d">
-        <x:v>2026-10-03T09:29:59.999Z</x:v>
+      <x:c r="G207" s="20" t="n">
+        <x:v>46298.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="42" customHeight="1">
-      <x:c r="A208" s="20" t="d">
-        <x:v>2026-10-03T09:30:00.000Z</x:v>
+      <x:c r="A208" s="20" t="n">
+        <x:v>46298.39583333333</x:v>
       </x:c>
       <x:c r="B208" s="8" t="n">
         <x:v>84598.06</x:v>
@@ -5844,13 +5844,13 @@
       <x:c r="F208" s="8" t="n">
         <x:v>95.22217</x:v>
       </x:c>
-      <x:c r="G208" s="20" t="d">
-        <x:v>2026-10-03T09:59:59.999Z</x:v>
+      <x:c r="G208" s="20" t="n">
+        <x:v>46298.41666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="42" customHeight="1">
-      <x:c r="A209" s="20" t="d">
-        <x:v>2026-10-03T10:00:00.000Z</x:v>
+      <x:c r="A209" s="20" t="n">
+        <x:v>46298.41666666667</x:v>
       </x:c>
       <x:c r="B209" s="8" t="n">
         <x:v>84600</x:v>
@@ -5867,13 +5867,13 @@
       <x:c r="F209" s="8" t="n">
         <x:v>239.26878</x:v>
       </x:c>
-      <x:c r="G209" s="20" t="d">
-        <x:v>2026-10-03T10:29:59.999Z</x:v>
+      <x:c r="G209" s="20" t="n">
+        <x:v>46298.43749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="42" customHeight="1">
-      <x:c r="A210" s="20" t="d">
-        <x:v>2026-10-03T10:30:00.000Z</x:v>
+      <x:c r="A210" s="20" t="n">
+        <x:v>46298.4375</x:v>
       </x:c>
       <x:c r="B210" s="8" t="n">
         <x:v>84586.24</x:v>
@@ -5890,13 +5890,13 @@
       <x:c r="F210" s="8" t="n">
         <x:v>101.33666</x:v>
       </x:c>
-      <x:c r="G210" s="20" t="d">
-        <x:v>2026-10-03T10:59:59.999Z</x:v>
+      <x:c r="G210" s="20" t="n">
+        <x:v>46298.45833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="42" customHeight="1">
-      <x:c r="A211" s="20" t="d">
-        <x:v>2026-10-03T11:00:00.000Z</x:v>
+      <x:c r="A211" s="20" t="n">
+        <x:v>46298.45833333333</x:v>
       </x:c>
       <x:c r="B211" s="8" t="n">
         <x:v>84636.13</x:v>
@@ -5913,13 +5913,13 @@
       <x:c r="F211" s="8" t="n">
         <x:v>110.59741</x:v>
       </x:c>
-      <x:c r="G211" s="20" t="d">
-        <x:v>2026-10-03T11:29:59.999Z</x:v>
+      <x:c r="G211" s="20" t="n">
+        <x:v>46298.47916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="42" customHeight="1">
-      <x:c r="A212" s="20" t="d">
-        <x:v>2026-10-03T11:30:00.000Z</x:v>
+      <x:c r="A212" s="20" t="n">
+        <x:v>46298.47916666667</x:v>
       </x:c>
       <x:c r="B212" s="8" t="n">
         <x:v>84651.22</x:v>
@@ -5936,13 +5936,13 @@
       <x:c r="F212" s="8" t="n">
         <x:v>77.44086</x:v>
       </x:c>
-      <x:c r="G212" s="20" t="d">
-        <x:v>2026-10-03T11:59:59.999Z</x:v>
+      <x:c r="G212" s="20" t="n">
+        <x:v>46298.49999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="42" customHeight="1">
-      <x:c r="A213" s="20" t="d">
-        <x:v>2026-10-03T12:00:00.000Z</x:v>
+      <x:c r="A213" s="20" t="n">
+        <x:v>46298.5</x:v>
       </x:c>
       <x:c r="B213" s="8" t="n">
         <x:v>84672.01</x:v>
@@ -5959,13 +5959,13 @@
       <x:c r="F213" s="8" t="n">
         <x:v>220.64237</x:v>
       </x:c>
-      <x:c r="G213" s="20" t="d">
-        <x:v>2026-10-03T12:29:59.999Z</x:v>
+      <x:c r="G213" s="20" t="n">
+        <x:v>46298.52083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="42" customHeight="1">
-      <x:c r="A214" s="20" t="d">
-        <x:v>2026-10-03T12:30:00.000Z</x:v>
+      <x:c r="A214" s="20" t="n">
+        <x:v>46298.52083333333</x:v>
       </x:c>
       <x:c r="B214" s="8" t="n">
         <x:v>84861.41</x:v>
@@ -5982,13 +5982,13 @@
       <x:c r="F214" s="8" t="n">
         <x:v>165.76108</x:v>
       </x:c>
-      <x:c r="G214" s="20" t="d">
-        <x:v>2026-10-03T12:59:59.999Z</x:v>
+      <x:c r="G214" s="20" t="n">
+        <x:v>46298.54166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="42" customHeight="1">
-      <x:c r="A215" s="20" t="d">
-        <x:v>2026-10-03T13:00:00.000Z</x:v>
+      <x:c r="A215" s="20" t="n">
+        <x:v>46298.54166666667</x:v>
       </x:c>
       <x:c r="B215" s="8" t="n">
         <x:v>84888.02</x:v>
@@ -6005,13 +6005,13 @@
       <x:c r="F215" s="8" t="n">
         <x:v>135.15733</x:v>
       </x:c>
-      <x:c r="G215" s="20" t="d">
-        <x:v>2026-10-03T13:29:59.999Z</x:v>
+      <x:c r="G215" s="20" t="n">
+        <x:v>46298.56249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="42" customHeight="1">
-      <x:c r="A216" s="20" t="d">
-        <x:v>2026-10-03T13:30:00.000Z</x:v>
+      <x:c r="A216" s="20" t="n">
+        <x:v>46298.5625</x:v>
       </x:c>
       <x:c r="B216" s="8" t="n">
         <x:v>84812.01</x:v>
@@ -6028,13 +6028,13 @@
       <x:c r="F216" s="8" t="n">
         <x:v>114.84176</x:v>
       </x:c>
-      <x:c r="G216" s="20" t="d">
-        <x:v>2026-10-03T13:59:59.999Z</x:v>
+      <x:c r="G216" s="20" t="n">
+        <x:v>46298.58333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="42" customHeight="1">
-      <x:c r="A217" s="20" t="d">
-        <x:v>2026-10-03T14:00:00.000Z</x:v>
+      <x:c r="A217" s="20" t="n">
+        <x:v>46298.58333333333</x:v>
       </x:c>
       <x:c r="B217" s="8" t="n">
         <x:v>84870.03</x:v>
@@ -6051,13 +6051,13 @@
       <x:c r="F217" s="8" t="n">
         <x:v>105.07909</x:v>
       </x:c>
-      <x:c r="G217" s="20" t="d">
-        <x:v>2026-10-03T14:29:59.999Z</x:v>
+      <x:c r="G217" s="20" t="n">
+        <x:v>46298.60416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="42" customHeight="1">
-      <x:c r="A218" s="20" t="d">
-        <x:v>2026-10-03T14:30:00.000Z</x:v>
+      <x:c r="A218" s="20" t="n">
+        <x:v>46298.60416666667</x:v>
       </x:c>
       <x:c r="B218" s="8" t="n">
         <x:v>84826.01</x:v>
@@ -6074,13 +6074,13 @@
       <x:c r="F218" s="8" t="n">
         <x:v>120.48959</x:v>
       </x:c>
-      <x:c r="G218" s="20" t="d">
-        <x:v>2026-10-03T14:59:59.999Z</x:v>
+      <x:c r="G218" s="20" t="n">
+        <x:v>46298.62499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="42" customHeight="1">
-      <x:c r="A219" s="20" t="d">
-        <x:v>2026-10-03T15:00:00.000Z</x:v>
+      <x:c r="A219" s="20" t="n">
+        <x:v>46298.625</x:v>
       </x:c>
       <x:c r="B219" s="8" t="n">
         <x:v>84856.01</x:v>
@@ -6097,13 +6097,13 @@
       <x:c r="F219" s="8" t="n">
         <x:v>147.45501</x:v>
       </x:c>
-      <x:c r="G219" s="20" t="d">
-        <x:v>2026-10-03T15:29:59.999Z</x:v>
+      <x:c r="G219" s="20" t="n">
+        <x:v>46298.64583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="42" customHeight="1">
-      <x:c r="A220" s="20" t="d">
-        <x:v>2026-10-03T15:30:00.000Z</x:v>
+      <x:c r="A220" s="20" t="n">
+        <x:v>46298.64583333333</x:v>
       </x:c>
       <x:c r="B220" s="8" t="n">
         <x:v>84838.66</x:v>
@@ -6120,13 +6120,13 @@
       <x:c r="F220" s="8" t="n">
         <x:v>218.74819</x:v>
       </x:c>
-      <x:c r="G220" s="20" t="d">
-        <x:v>2026-10-03T15:59:59.999Z</x:v>
+      <x:c r="G220" s="20" t="n">
+        <x:v>46298.66666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="42" customHeight="1">
-      <x:c r="A221" s="20" t="d">
-        <x:v>2026-10-03T16:00:00.000Z</x:v>
+      <x:c r="A221" s="20" t="n">
+        <x:v>46298.66666666667</x:v>
       </x:c>
       <x:c r="B221" s="8" t="n">
         <x:v>84867.27</x:v>
@@ -6143,13 +6143,13 @@
       <x:c r="F221" s="8" t="n">
         <x:v>92.91586</x:v>
       </x:c>
-      <x:c r="G221" s="20" t="d">
-        <x:v>2026-10-03T16:29:59.999Z</x:v>
+      <x:c r="G221" s="20" t="n">
+        <x:v>46298.68749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="42" customHeight="1">
-      <x:c r="A222" s="20" t="d">
-        <x:v>2026-10-03T16:30:00.000Z</x:v>
+      <x:c r="A222" s="20" t="n">
+        <x:v>46298.6875</x:v>
       </x:c>
       <x:c r="B222" s="8" t="n">
         <x:v>84813.23</x:v>
@@ -6166,13 +6166,13 @@
       <x:c r="F222" s="8" t="n">
         <x:v>122.22504</x:v>
       </x:c>
-      <x:c r="G222" s="20" t="d">
-        <x:v>2026-10-03T16:59:59.999Z</x:v>
+      <x:c r="G222" s="20" t="n">
+        <x:v>46298.70833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="42" customHeight="1">
-      <x:c r="A223" s="20" t="d">
-        <x:v>2026-10-03T17:00:00.000Z</x:v>
+      <x:c r="A223" s="20" t="n">
+        <x:v>46298.70833333333</x:v>
       </x:c>
       <x:c r="B223" s="8" t="n">
         <x:v>84868.02</x:v>
@@ -6189,13 +6189,13 @@
       <x:c r="F223" s="8" t="n">
         <x:v>129.73584</x:v>
       </x:c>
-      <x:c r="G223" s="20" t="d">
-        <x:v>2026-10-03T17:29:59.999Z</x:v>
+      <x:c r="G223" s="20" t="n">
+        <x:v>46298.72916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="42" customHeight="1">
-      <x:c r="A224" s="20" t="d">
-        <x:v>2026-10-03T17:30:00.000Z</x:v>
+      <x:c r="A224" s="20" t="n">
+        <x:v>46298.72916666667</x:v>
       </x:c>
       <x:c r="B224" s="8" t="n">
         <x:v>84894.01</x:v>
@@ -6212,13 +6212,13 @@
       <x:c r="F224" s="8" t="n">
         <x:v>202.10661</x:v>
       </x:c>
-      <x:c r="G224" s="20" t="d">
-        <x:v>2026-10-03T17:59:59.999Z</x:v>
+      <x:c r="G224" s="20" t="n">
+        <x:v>46298.74999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="42" customHeight="1">
-      <x:c r="A225" s="20" t="d">
-        <x:v>2026-10-03T18:00:00.000Z</x:v>
+      <x:c r="A225" s="20" t="n">
+        <x:v>46298.75</x:v>
       </x:c>
       <x:c r="B225" s="8" t="n">
         <x:v>85012.01</x:v>
@@ -6235,13 +6235,13 @@
       <x:c r="F225" s="8" t="n">
         <x:v>133.73013</x:v>
       </x:c>
-      <x:c r="G225" s="20" t="d">
-        <x:v>2026-10-03T18:29:59.999Z</x:v>
+      <x:c r="G225" s="20" t="n">
+        <x:v>46298.77083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="42" customHeight="1">
-      <x:c r="A226" s="20" t="d">
-        <x:v>2026-10-03T18:30:00.000Z</x:v>
+      <x:c r="A226" s="20" t="n">
+        <x:v>46298.77083333333</x:v>
       </x:c>
       <x:c r="B226" s="8" t="n">
         <x:v>84995.78</x:v>
@@ -6258,13 +6258,13 @@
       <x:c r="F226" s="8" t="n">
         <x:v>81.05253</x:v>
       </x:c>
-      <x:c r="G226" s="20" t="d">
-        <x:v>2026-10-03T18:59:59.999Z</x:v>
+      <x:c r="G226" s="20" t="n">
+        <x:v>46298.79166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="42" customHeight="1">
-      <x:c r="A227" s="20" t="d">
-        <x:v>2026-10-03T19:00:00.000Z</x:v>
+      <x:c r="A227" s="20" t="n">
+        <x:v>46298.79166666667</x:v>
       </x:c>
       <x:c r="B227" s="8" t="n">
         <x:v>84950</x:v>
@@ -6281,13 +6281,13 @@
       <x:c r="F227" s="8" t="n">
         <x:v>107.042</x:v>
       </x:c>
-      <x:c r="G227" s="20" t="d">
-        <x:v>2026-10-03T19:29:59.999Z</x:v>
+      <x:c r="G227" s="20" t="n">
+        <x:v>46298.81249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="42" customHeight="1">
-      <x:c r="A228" s="20" t="d">
-        <x:v>2026-10-03T19:30:00.000Z</x:v>
+      <x:c r="A228" s="20" t="n">
+        <x:v>46298.8125</x:v>
       </x:c>
       <x:c r="B228" s="8" t="n">
         <x:v>84828.1</x:v>
@@ -6304,13 +6304,13 @@
       <x:c r="F228" s="8" t="n">
         <x:v>128.28067</x:v>
       </x:c>
-      <x:c r="G228" s="20" t="d">
-        <x:v>2026-10-03T19:59:59.999Z</x:v>
+      <x:c r="G228" s="20" t="n">
+        <x:v>46298.83333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="42" customHeight="1">
-      <x:c r="A229" s="20" t="d">
-        <x:v>2026-10-03T20:00:00.000Z</x:v>
+      <x:c r="A229" s="20" t="n">
+        <x:v>46298.83333333333</x:v>
       </x:c>
       <x:c r="B229" s="8" t="n">
         <x:v>84842.5</x:v>
@@ -6327,13 +6327,13 @@
       <x:c r="F229" s="8" t="n">
         <x:v>88.20696</x:v>
       </x:c>
-      <x:c r="G229" s="20" t="d">
-        <x:v>2026-10-03T20:29:59.999Z</x:v>
+      <x:c r="G229" s="20" t="n">
+        <x:v>46298.85416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="42" customHeight="1">
-      <x:c r="A230" s="20" t="d">
-        <x:v>2026-10-03T20:30:00.000Z</x:v>
+      <x:c r="A230" s="20" t="n">
+        <x:v>46298.85416666667</x:v>
       </x:c>
       <x:c r="B230" s="8" t="n">
         <x:v>84889.16</x:v>
@@ -6350,13 +6350,13 @@
       <x:c r="F230" s="8" t="n">
         <x:v>107.14799</x:v>
       </x:c>
-      <x:c r="G230" s="20" t="d">
-        <x:v>2026-10-03T20:59:59.999Z</x:v>
+      <x:c r="G230" s="20" t="n">
+        <x:v>46298.87499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="42" customHeight="1">
-      <x:c r="A231" s="20" t="d">
-        <x:v>2026-10-03T21:00:00.000Z</x:v>
+      <x:c r="A231" s="20" t="n">
+        <x:v>46298.875</x:v>
       </x:c>
       <x:c r="B231" s="8" t="n">
         <x:v>84749.76</x:v>
@@ -6373,13 +6373,13 @@
       <x:c r="F231" s="8" t="n">
         <x:v>206.28642</x:v>
       </x:c>
-      <x:c r="G231" s="20" t="d">
-        <x:v>2026-10-03T21:29:59.999Z</x:v>
+      <x:c r="G231" s="20" t="n">
+        <x:v>46298.89583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="42" customHeight="1">
-      <x:c r="A232" s="20" t="d">
-        <x:v>2026-10-03T21:30:00.000Z</x:v>
+      <x:c r="A232" s="20" t="n">
+        <x:v>46298.89583333333</x:v>
       </x:c>
       <x:c r="B232" s="8" t="n">
         <x:v>84710.69</x:v>
@@ -6396,13 +6396,13 @@
       <x:c r="F232" s="8" t="n">
         <x:v>82.4274</x:v>
       </x:c>
-      <x:c r="G232" s="20" t="d">
-        <x:v>2026-10-03T21:59:59.999Z</x:v>
+      <x:c r="G232" s="20" t="n">
+        <x:v>46298.91666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="42" customHeight="1">
-      <x:c r="A233" s="20" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      <x:c r="A233" s="20" t="n">
+        <x:v>46298.91666666667</x:v>
       </x:c>
       <x:c r="B233" s="8" t="n">
         <x:v>84715.15</x:v>
@@ -6419,13 +6419,13 @@
       <x:c r="F233" s="8" t="n">
         <x:v>284.53489</x:v>
       </x:c>
-      <x:c r="G233" s="20" t="d">
-        <x:v>2026-10-03T22:29:59.999Z</x:v>
+      <x:c r="G233" s="20" t="n">
+        <x:v>46298.93749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="42" customHeight="1">
-      <x:c r="A234" s="20" t="d">
-        <x:v>2026-10-03T22:30:00.000Z</x:v>
+      <x:c r="A234" s="20" t="n">
+        <x:v>46298.9375</x:v>
       </x:c>
       <x:c r="B234" s="8" t="n">
         <x:v>84784.01</x:v>
@@ -6442,13 +6442,13 @@
       <x:c r="F234" s="8" t="n">
         <x:v>97.74391</x:v>
       </x:c>
-      <x:c r="G234" s="20" t="d">
-        <x:v>2026-10-03T22:59:59.999Z</x:v>
+      <x:c r="G234" s="20" t="n">
+        <x:v>46298.95833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="42" customHeight="1">
-      <x:c r="A235" s="20" t="d">
-        <x:v>2026-10-03T23:00:00.000Z</x:v>
+      <x:c r="A235" s="20" t="n">
+        <x:v>46298.95833333333</x:v>
       </x:c>
       <x:c r="B235" s="8" t="n">
         <x:v>84776.02</x:v>
@@ -6465,13 +6465,13 @@
       <x:c r="F235" s="8" t="n">
         <x:v>441.21859</x:v>
       </x:c>
-      <x:c r="G235" s="20" t="d">
-        <x:v>2026-10-03T23:29:59.999Z</x:v>
+      <x:c r="G235" s="20" t="n">
+        <x:v>46298.97916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="42" customHeight="1">
-      <x:c r="A236" s="20" t="d">
-        <x:v>2026-10-03T23:30:00.000Z</x:v>
+      <x:c r="A236" s="20" t="n">
+        <x:v>46298.97916666667</x:v>
       </x:c>
       <x:c r="B236" s="8" t="n">
         <x:v>84738</x:v>
@@ -6488,13 +6488,13 @@
       <x:c r="F236" s="8" t="n">
         <x:v>478.25975</x:v>
       </x:c>
-      <x:c r="G236" s="20" t="d">
-        <x:v>2026-10-03T23:59:59.999Z</x:v>
+      <x:c r="G236" s="20" t="n">
+        <x:v>46298.99999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="42" customHeight="1">
-      <x:c r="A237" s="20" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      <x:c r="A237" s="20" t="n">
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="B237" s="8" t="n">
         <x:v>84753.57</x:v>
@@ -6511,13 +6511,13 @@
       <x:c r="F237" s="8" t="n">
         <x:v>107.23775</x:v>
       </x:c>
-      <x:c r="G237" s="20" t="d">
-        <x:v>2026-10-04T00:29:59.999Z</x:v>
+      <x:c r="G237" s="20" t="n">
+        <x:v>46299.02083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="42" customHeight="1">
-      <x:c r="A238" s="20" t="d">
-        <x:v>2026-10-04T00:30:00.000Z</x:v>
+      <x:c r="A238" s="20" t="n">
+        <x:v>46299.02083333333</x:v>
       </x:c>
       <x:c r="B238" s="8" t="n">
         <x:v>84808.93</x:v>
@@ -6534,13 +6534,13 @@
       <x:c r="F238" s="8" t="n">
         <x:v>277.79517</x:v>
       </x:c>
-      <x:c r="G238" s="20" t="d">
-        <x:v>2026-10-04T00:59:59.999Z</x:v>
+      <x:c r="G238" s="20" t="n">
+        <x:v>46299.04166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="42" customHeight="1">
-      <x:c r="A239" s="20" t="d">
-        <x:v>2026-10-04T01:00:00.000Z</x:v>
+      <x:c r="A239" s="20" t="n">
+        <x:v>46299.04166666667</x:v>
       </x:c>
       <x:c r="B239" s="8" t="n">
         <x:v>84790</x:v>
@@ -6557,13 +6557,13 @@
       <x:c r="F239" s="8" t="n">
         <x:v>100.65991</x:v>
       </x:c>
-      <x:c r="G239" s="20" t="d">
-        <x:v>2026-10-04T01:29:59.999Z</x:v>
+      <x:c r="G239" s="20" t="n">
+        <x:v>46299.06249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="42" customHeight="1">
-      <x:c r="A240" s="20" t="d">
-        <x:v>2026-10-04T01:30:00.000Z</x:v>
+      <x:c r="A240" s="20" t="n">
+        <x:v>46299.0625</x:v>
       </x:c>
       <x:c r="B240" s="8" t="n">
         <x:v>84747.51</x:v>
@@ -6580,13 +6580,13 @@
       <x:c r="F240" s="8" t="n">
         <x:v>90.75519</x:v>
       </x:c>
-      <x:c r="G240" s="20" t="d">
-        <x:v>2026-10-04T01:59:59.999Z</x:v>
+      <x:c r="G240" s="20" t="n">
+        <x:v>46299.08333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="42" customHeight="1">
-      <x:c r="A241" s="20" t="d">
-        <x:v>2026-10-04T02:00:00.000Z</x:v>
+      <x:c r="A241" s="20" t="n">
+        <x:v>46299.08333333333</x:v>
       </x:c>
       <x:c r="B241" s="8" t="n">
         <x:v>84802.6</x:v>
@@ -6603,13 +6603,13 @@
       <x:c r="F241" s="8" t="n">
         <x:v>158.07561</x:v>
       </x:c>
-      <x:c r="G241" s="20" t="d">
-        <x:v>2026-10-04T02:29:59.999Z</x:v>
+      <x:c r="G241" s="20" t="n">
+        <x:v>46299.10416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="42" customHeight="1">
-      <x:c r="A242" s="20" t="d">
-        <x:v>2026-10-04T02:30:00.000Z</x:v>
+      <x:c r="A242" s="20" t="n">
+        <x:v>46299.10416666667</x:v>
       </x:c>
       <x:c r="B242" s="8" t="n">
         <x:v>84836</x:v>
@@ -6626,13 +6626,13 @@
       <x:c r="F242" s="8" t="n">
         <x:v>120.06465</x:v>
       </x:c>
-      <x:c r="G242" s="20" t="d">
-        <x:v>2026-10-04T02:59:59.999Z</x:v>
+      <x:c r="G242" s="20" t="n">
+        <x:v>46299.12499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="42" customHeight="1">
-      <x:c r="A243" s="20" t="d">
-        <x:v>2026-10-04T03:00:00.000Z</x:v>
+      <x:c r="A243" s="20" t="n">
+        <x:v>46299.125</x:v>
       </x:c>
       <x:c r="B243" s="8" t="n">
         <x:v>84802.17</x:v>
@@ -6649,13 +6649,13 @@
       <x:c r="F243" s="8" t="n">
         <x:v>130.33814</x:v>
       </x:c>
-      <x:c r="G243" s="20" t="d">
-        <x:v>2026-10-04T03:29:59.999Z</x:v>
+      <x:c r="G243" s="20" t="n">
+        <x:v>46299.14583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="42" customHeight="1">
-      <x:c r="A244" s="20" t="d">
-        <x:v>2026-10-04T03:30:00.000Z</x:v>
+      <x:c r="A244" s="20" t="n">
+        <x:v>46299.14583333333</x:v>
       </x:c>
       <x:c r="B244" s="8" t="n">
         <x:v>84796.42</x:v>
@@ -6672,13 +6672,13 @@
       <x:c r="F244" s="8" t="n">
         <x:v>96.44657</x:v>
       </x:c>
-      <x:c r="G244" s="20" t="d">
-        <x:v>2026-10-04T03:59:59.999Z</x:v>
+      <x:c r="G244" s="20" t="n">
+        <x:v>46299.16666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="42" customHeight="1">
-      <x:c r="A245" s="20" t="d">
-        <x:v>2026-10-04T04:00:00.000Z</x:v>
+      <x:c r="A245" s="20" t="n">
+        <x:v>46299.16666666667</x:v>
       </x:c>
       <x:c r="B245" s="8" t="n">
         <x:v>84840.88</x:v>
@@ -6695,13 +6695,13 @@
       <x:c r="F245" s="8" t="n">
         <x:v>44.73612</x:v>
       </x:c>
-      <x:c r="G245" s="20" t="d">
-        <x:v>2026-10-04T04:29:59.999Z</x:v>
+      <x:c r="G245" s="20" t="n">
+        <x:v>46299.18749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="42" customHeight="1">
-      <x:c r="A246" s="20" t="d">
-        <x:v>2026-10-04T04:30:00.000Z</x:v>
+      <x:c r="A246" s="20" t="n">
+        <x:v>46299.1875</x:v>
       </x:c>
       <x:c r="B246" s="8" t="n">
         <x:v>84812</x:v>
@@ -6718,13 +6718,13 @@
       <x:c r="F246" s="8" t="n">
         <x:v>31.17726</x:v>
       </x:c>
-      <x:c r="G246" s="20" t="d">
-        <x:v>2026-10-04T04:59:59.999Z</x:v>
+      <x:c r="G246" s="20" t="n">
+        <x:v>46299.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="42" customHeight="1">
-      <x:c r="A247" s="20" t="d">
-        <x:v>2026-10-04T05:00:00.000Z</x:v>
+      <x:c r="A247" s="20" t="n">
+        <x:v>46299.20833333333</x:v>
       </x:c>
       <x:c r="B247" s="8" t="n">
         <x:v>84811.94</x:v>
@@ -6741,13 +6741,13 @@
       <x:c r="F247" s="8" t="n">
         <x:v>154.47794</x:v>
       </x:c>
-      <x:c r="G247" s="20" t="d">
-        <x:v>2026-10-04T05:29:59.999Z</x:v>
+      <x:c r="G247" s="20" t="n">
+        <x:v>46299.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="42" customHeight="1">
-      <x:c r="A248" s="20" t="d">
-        <x:v>2026-10-04T05:30:00.000Z</x:v>
+      <x:c r="A248" s="20" t="n">
+        <x:v>46299.22916666667</x:v>
       </x:c>
       <x:c r="B248" s="8" t="n">
         <x:v>84861.34</x:v>
@@ -6764,13 +6764,13 @@
       <x:c r="F248" s="8" t="n">
         <x:v>72.29586</x:v>
       </x:c>
-      <x:c r="G248" s="20" t="d">
-        <x:v>2026-10-04T05:59:59.999Z</x:v>
+      <x:c r="G248" s="20" t="n">
+        <x:v>46299.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="42" customHeight="1">
-      <x:c r="A249" s="20" t="d">
-        <x:v>2026-10-04T06:00:00.000Z</x:v>
+      <x:c r="A249" s="20" t="n">
+        <x:v>46299.25</x:v>
       </x:c>
       <x:c r="B249" s="8" t="n">
         <x:v>84912.01</x:v>
@@ -6787,13 +6787,13 @@
       <x:c r="F249" s="8" t="n">
         <x:v>178.07501</x:v>
       </x:c>
-      <x:c r="G249" s="20" t="d">
-        <x:v>2026-10-04T06:29:59.999Z</x:v>
+      <x:c r="G249" s="20" t="n">
+        <x:v>46299.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="42" customHeight="1">
-      <x:c r="A250" s="20" t="d">
-        <x:v>2026-10-04T06:30:00.000Z</x:v>
+      <x:c r="A250" s="20" t="n">
+        <x:v>46299.27083333333</x:v>
       </x:c>
       <x:c r="B250" s="8" t="n">
         <x:v>84947.62</x:v>
@@ -6810,13 +6810,13 @@
       <x:c r="F250" s="8" t="n">
         <x:v>117.64474</x:v>
       </x:c>
-      <x:c r="G250" s="20" t="d">
-        <x:v>2026-10-04T06:59:59.999Z</x:v>
+      <x:c r="G250" s="20" t="n">
+        <x:v>46299.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="42" customHeight="1">
-      <x:c r="A251" s="20" t="d">
-        <x:v>2026-10-04T07:00:00.000Z</x:v>
+      <x:c r="A251" s="20" t="n">
+        <x:v>46299.29166666667</x:v>
       </x:c>
       <x:c r="B251" s="8" t="n">
         <x:v>85031.74</x:v>
@@ -6833,13 +6833,13 @@
       <x:c r="F251" s="8" t="n">
         <x:v>83.44219</x:v>
       </x:c>
-      <x:c r="G251" s="20" t="d">
-        <x:v>2026-10-04T07:29:59.999Z</x:v>
+      <x:c r="G251" s="20" t="n">
+        <x:v>46299.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="42" customHeight="1">
-      <x:c r="A252" s="20" t="d">
-        <x:v>2026-10-04T07:30:00.000Z</x:v>
+      <x:c r="A252" s="20" t="n">
+        <x:v>46299.3125</x:v>
       </x:c>
       <x:c r="B252" s="8" t="n">
         <x:v>84972.73</x:v>
@@ -6856,13 +6856,13 @@
       <x:c r="F252" s="8" t="n">
         <x:v>161.03147</x:v>
       </x:c>
-      <x:c r="G252" s="20" t="d">
-        <x:v>2026-10-04T07:59:59.999Z</x:v>
+      <x:c r="G252" s="20" t="n">
+        <x:v>46299.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="42" customHeight="1">
-      <x:c r="A253" s="20" t="d">
-        <x:v>2026-10-04T08:00:00.000Z</x:v>
+      <x:c r="A253" s="20" t="n">
+        <x:v>46299.33333333333</x:v>
       </x:c>
       <x:c r="B253" s="8" t="n">
         <x:v>85106.01</x:v>
@@ -6879,13 +6879,13 @@
       <x:c r="F253" s="8" t="n">
         <x:v>162.85915</x:v>
       </x:c>
-      <x:c r="G253" s="20" t="d">
-        <x:v>2026-10-04T08:29:59.999Z</x:v>
+      <x:c r="G253" s="20" t="n">
+        <x:v>46299.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="42" customHeight="1">
-      <x:c r="A254" s="20" t="d">
-        <x:v>2026-10-04T08:30:00.000Z</x:v>
+      <x:c r="A254" s="20" t="n">
+        <x:v>46299.35416666667</x:v>
       </x:c>
       <x:c r="B254" s="8" t="n">
         <x:v>85137.99</x:v>
@@ -6902,13 +6902,13 @@
       <x:c r="F254" s="8" t="n">
         <x:v>158.21671</x:v>
       </x:c>
-      <x:c r="G254" s="20" t="d">
-        <x:v>2026-10-04T08:59:59.999Z</x:v>
+      <x:c r="G254" s="20" t="n">
+        <x:v>46299.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="42" customHeight="1">
-      <x:c r="A255" s="20" t="d">
-        <x:v>2026-10-04T09:00:00.000Z</x:v>
+      <x:c r="A255" s="20" t="n">
+        <x:v>46299.375</x:v>
       </x:c>
       <x:c r="B255" s="8" t="n">
         <x:v>85106.48</x:v>
@@ -6925,13 +6925,13 @@
       <x:c r="F255" s="8" t="n">
         <x:v>141.35143</x:v>
       </x:c>
-      <x:c r="G255" s="20" t="d">
-        <x:v>2026-10-04T09:29:59.999Z</x:v>
+      <x:c r="G255" s="20" t="n">
+        <x:v>46299.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="42" customHeight="1">
-      <x:c r="A256" s="20" t="d">
-        <x:v>2026-10-04T09:30:00.000Z</x:v>
+      <x:c r="A256" s="20" t="n">
+        <x:v>46299.39583333333</x:v>
       </x:c>
       <x:c r="B256" s="8" t="n">
         <x:v>85264.08</x:v>
@@ -6948,13 +6948,13 @@
       <x:c r="F256" s="8" t="n">
         <x:v>193.96162</x:v>
       </x:c>
-      <x:c r="G256" s="20" t="d">
-        <x:v>2026-10-04T09:59:59.999Z</x:v>
+      <x:c r="G256" s="20" t="n">
+        <x:v>46299.41666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="42" customHeight="1">
-      <x:c r="A257" s="20" t="d">
-        <x:v>2026-10-04T10:00:00.000Z</x:v>
+      <x:c r="A257" s="20" t="n">
+        <x:v>46299.41666666667</x:v>
       </x:c>
       <x:c r="B257" s="8" t="n">
         <x:v>85233.84</x:v>
@@ -6971,13 +6971,13 @@
       <x:c r="F257" s="8" t="n">
         <x:v>177.63549</x:v>
       </x:c>
-      <x:c r="G257" s="20" t="d">
-        <x:v>2026-10-04T10:29:59.999Z</x:v>
+      <x:c r="G257" s="20" t="n">
+        <x:v>46299.43749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="42" customHeight="1">
-      <x:c r="A258" s="20" t="d">
-        <x:v>2026-10-04T10:30:00.000Z</x:v>
+      <x:c r="A258" s="20" t="n">
+        <x:v>46299.4375</x:v>
       </x:c>
       <x:c r="B258" s="8" t="n">
         <x:v>85375.07</x:v>
@@ -6994,13 +6994,13 @@
       <x:c r="F258" s="8" t="n">
         <x:v>158.38399</x:v>
       </x:c>
-      <x:c r="G258" s="20" t="d">
-        <x:v>2026-10-04T10:59:59.999Z</x:v>
+      <x:c r="G258" s="20" t="n">
+        <x:v>46299.45833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="42" customHeight="1">
-      <x:c r="A259" s="20" t="d">
-        <x:v>2026-10-04T11:00:00.000Z</x:v>
+      <x:c r="A259" s="20" t="n">
+        <x:v>46299.45833333333</x:v>
       </x:c>
       <x:c r="B259" s="8" t="n">
         <x:v>85264.01</x:v>
@@ -7017,13 +7017,13 @@
       <x:c r="F259" s="8" t="n">
         <x:v>109.90582</x:v>
       </x:c>
-      <x:c r="G259" s="20" t="d">
-        <x:v>2026-10-04T11:29:59.999Z</x:v>
+      <x:c r="G259" s="20" t="n">
+        <x:v>46299.47916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="42" customHeight="1">
-      <x:c r="A260" s="20" t="d">
-        <x:v>2026-10-04T11:30:00.000Z</x:v>
+      <x:c r="A260" s="20" t="n">
+        <x:v>46299.47916666667</x:v>
       </x:c>
       <x:c r="B260" s="8" t="n">
         <x:v>85312</x:v>
@@ -7040,13 +7040,13 @@
       <x:c r="F260" s="8" t="n">
         <x:v>141.89841</x:v>
       </x:c>
-      <x:c r="G260" s="20" t="d">
-        <x:v>2026-10-04T11:59:59.999Z</x:v>
+      <x:c r="G260" s="20" t="n">
+        <x:v>46299.49999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="42" customHeight="1">
-      <x:c r="A261" s="20" t="d">
-        <x:v>2026-10-04T12:00:00.000Z</x:v>
+      <x:c r="A261" s="20" t="n">
+        <x:v>46299.5</x:v>
       </x:c>
       <x:c r="B261" s="8" t="n">
         <x:v>85309.47</x:v>
@@ -7063,13 +7063,13 @@
       <x:c r="F261" s="8" t="n">
         <x:v>235.56749</x:v>
       </x:c>
-      <x:c r="G261" s="20" t="d">
-        <x:v>2026-10-04T12:29:59.999Z</x:v>
+      <x:c r="G261" s="20" t="n">
+        <x:v>46299.52083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="42" customHeight="1">
-      <x:c r="A262" s="20" t="d">
-        <x:v>2026-10-04T12:30:00.000Z</x:v>
+      <x:c r="A262" s="20" t="n">
+        <x:v>46299.52083333333</x:v>
       </x:c>
       <x:c r="B262" s="8" t="n">
         <x:v>85276.01</x:v>
@@ -7086,13 +7086,13 @@
       <x:c r="F262" s="8" t="n">
         <x:v>123.72216</x:v>
       </x:c>
-      <x:c r="G262" s="20" t="d">
-        <x:v>2026-10-04T12:59:59.999Z</x:v>
+      <x:c r="G262" s="20" t="n">
+        <x:v>46299.54166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="42" customHeight="1">
-      <x:c r="A263" s="20" t="d">
-        <x:v>2026-10-04T13:00:00.000Z</x:v>
+      <x:c r="A263" s="20" t="n">
+        <x:v>46299.54166666667</x:v>
       </x:c>
       <x:c r="B263" s="8" t="n">
         <x:v>85127.94</x:v>
@@ -7109,13 +7109,13 @@
       <x:c r="F263" s="8" t="n">
         <x:v>97.11108</x:v>
       </x:c>
-      <x:c r="G263" s="20" t="d">
-        <x:v>2026-10-04T13:29:59.999Z</x:v>
+      <x:c r="G263" s="20" t="n">
+        <x:v>46299.56249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="42" customHeight="1">
-      <x:c r="A264" s="20" t="d">
-        <x:v>2026-10-04T13:30:00.000Z</x:v>
+      <x:c r="A264" s="20" t="n">
+        <x:v>46299.5625</x:v>
       </x:c>
       <x:c r="B264" s="8" t="n">
         <x:v>85226.01</x:v>
@@ -7132,13 +7132,13 @@
       <x:c r="F264" s="8" t="n">
         <x:v>121.66984</x:v>
       </x:c>
-      <x:c r="G264" s="20" t="d">
-        <x:v>2026-10-04T13:59:59.999Z</x:v>
+      <x:c r="G264" s="20" t="n">
+        <x:v>46299.58333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="42" customHeight="1">
-      <x:c r="A265" s="20" t="d">
-        <x:v>2026-10-04T14:00:00.000Z</x:v>
+      <x:c r="A265" s="20" t="n">
+        <x:v>46299.58333333333</x:v>
       </x:c>
       <x:c r="B265" s="8" t="n">
         <x:v>85241.15</x:v>
@@ -7155,13 +7155,13 @@
       <x:c r="F265" s="8" t="n">
         <x:v>100.30642</x:v>
       </x:c>
-      <x:c r="G265" s="20" t="d">
-        <x:v>2026-10-04T14:29:59.999Z</x:v>
+      <x:c r="G265" s="20" t="n">
+        <x:v>46299.60416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="42" customHeight="1">
-      <x:c r="A266" s="20" t="d">
-        <x:v>2026-10-04T14:30:00.000Z</x:v>
+      <x:c r="A266" s="20" t="n">
+        <x:v>46299.60416666667</x:v>
       </x:c>
       <x:c r="B266" s="8" t="n">
         <x:v>85187.78</x:v>
@@ -7178,13 +7178,13 @@
       <x:c r="F266" s="8" t="n">
         <x:v>159.20478</x:v>
       </x:c>
-      <x:c r="G266" s="20" t="d">
-        <x:v>2026-10-04T14:59:59.999Z</x:v>
+      <x:c r="G266" s="20" t="n">
+        <x:v>46299.62499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="42" customHeight="1">
-      <x:c r="A267" s="20" t="d">
-        <x:v>2026-10-04T15:00:00.000Z</x:v>
+      <x:c r="A267" s="20" t="n">
+        <x:v>46299.625</x:v>
       </x:c>
       <x:c r="B267" s="8" t="n">
         <x:v>85278.45</x:v>
@@ -7201,13 +7201,13 @@
       <x:c r="F267" s="8" t="n">
         <x:v>196.05642</x:v>
       </x:c>
-      <x:c r="G267" s="20" t="d">
-        <x:v>2026-10-04T15:29:59.999Z</x:v>
+      <x:c r="G267" s="20" t="n">
+        <x:v>46299.64583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="42" customHeight="1">
-      <x:c r="A268" s="20" t="d">
-        <x:v>2026-10-04T15:30:00.000Z</x:v>
+      <x:c r="A268" s="20" t="n">
+        <x:v>46299.64583333333</x:v>
       </x:c>
       <x:c r="B268" s="8" t="n">
         <x:v>85320.01</x:v>
@@ -7224,13 +7224,13 @@
       <x:c r="F268" s="8" t="n">
         <x:v>91.7774</x:v>
       </x:c>
-      <x:c r="G268" s="20" t="d">
-        <x:v>2026-10-04T15:59:59.999Z</x:v>
+      <x:c r="G268" s="20" t="n">
+        <x:v>46299.66666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="42" customHeight="1">
-      <x:c r="A269" s="20" t="d">
-        <x:v>2026-10-04T16:00:00.000Z</x:v>
+      <x:c r="A269" s="20" t="n">
+        <x:v>46299.66666666667</x:v>
       </x:c>
       <x:c r="B269" s="8" t="n">
         <x:v>85256.01</x:v>
@@ -7247,13 +7247,13 @@
       <x:c r="F269" s="8" t="n">
         <x:v>111.99659</x:v>
       </x:c>
-      <x:c r="G269" s="20" t="d">
-        <x:v>2026-10-04T16:29:59.999Z</x:v>
+      <x:c r="G269" s="20" t="n">
+        <x:v>46299.68749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="42" customHeight="1">
-      <x:c r="A270" s="20" t="d">
-        <x:v>2026-10-04T16:30:00.000Z</x:v>
+      <x:c r="A270" s="20" t="n">
+        <x:v>46299.6875</x:v>
       </x:c>
       <x:c r="B270" s="8" t="n">
         <x:v>85243.7</x:v>
@@ -7270,13 +7270,13 @@
       <x:c r="F270" s="8" t="n">
         <x:v>83.75293</x:v>
       </x:c>
-      <x:c r="G270" s="20" t="d">
-        <x:v>2026-10-04T16:59:59.999Z</x:v>
+      <x:c r="G270" s="20" t="n">
+        <x:v>46299.70833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="42" customHeight="1">
-      <x:c r="A271" s="20" t="d">
-        <x:v>2026-10-04T17:00:00.000Z</x:v>
+      <x:c r="A271" s="20" t="n">
+        <x:v>46299.70833333333</x:v>
       </x:c>
       <x:c r="B271" s="8" t="n">
         <x:v>85374</x:v>
@@ -7293,13 +7293,13 @@
       <x:c r="F271" s="8" t="n">
         <x:v>72.10749</x:v>
       </x:c>
-      <x:c r="G271" s="20" t="d">
-        <x:v>2026-10-04T17:29:59.999Z</x:v>
+      <x:c r="G271" s="20" t="n">
+        <x:v>46299.72916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="42" customHeight="1">
-      <x:c r="A272" s="20" t="d">
-        <x:v>2026-10-04T17:30:00.000Z</x:v>
+      <x:c r="A272" s="20" t="n">
+        <x:v>46299.72916666667</x:v>
       </x:c>
       <x:c r="B272" s="8" t="n">
         <x:v>85386</x:v>
@@ -7316,13 +7316,13 @@
       <x:c r="F272" s="8" t="n">
         <x:v>86.97996</x:v>
       </x:c>
-      <x:c r="G272" s="20" t="d">
-        <x:v>2026-10-04T17:59:59.999Z</x:v>
+      <x:c r="G272" s="20" t="n">
+        <x:v>46299.74999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="42" customHeight="1">
-      <x:c r="A273" s="20" t="d">
-        <x:v>2026-10-04T18:00:00.000Z</x:v>
+      <x:c r="A273" s="20" t="n">
+        <x:v>46299.75</x:v>
       </x:c>
       <x:c r="B273" s="8" t="n">
         <x:v>85319.54</x:v>
@@ -7339,13 +7339,13 @@
       <x:c r="F273" s="8" t="n">
         <x:v>48.07145</x:v>
       </x:c>
-      <x:c r="G273" s="20" t="d">
-        <x:v>2026-10-04T18:29:59.999Z</x:v>
+      <x:c r="G273" s="20" t="n">
+        <x:v>46299.77083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="42" customHeight="1">
-      <x:c r="A274" s="20" t="d">
-        <x:v>2026-10-04T18:30:00.000Z</x:v>
+      <x:c r="A274" s="20" t="n">
+        <x:v>46299.77083333333</x:v>
       </x:c>
       <x:c r="B274" s="8" t="n">
         <x:v>85325.97</x:v>
@@ -7362,13 +7362,13 @@
       <x:c r="F274" s="8" t="n">
         <x:v>86.10494</x:v>
       </x:c>
-      <x:c r="G274" s="20" t="d">
-        <x:v>2026-10-04T18:59:59.999Z</x:v>
+      <x:c r="G274" s="20" t="n">
+        <x:v>46299.79166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="42" customHeight="1">
-      <x:c r="A275" s="20" t="d">
-        <x:v>2026-10-04T19:00:00.000Z</x:v>
+      <x:c r="A275" s="20" t="n">
+        <x:v>46299.79166666667</x:v>
       </x:c>
       <x:c r="B275" s="8" t="n">
         <x:v>85338.84</x:v>
@@ -7385,13 +7385,13 @@
       <x:c r="F275" s="8" t="n">
         <x:v>93.70418</x:v>
       </x:c>
-      <x:c r="G275" s="20" t="d">
-        <x:v>2026-10-04T19:29:59.999Z</x:v>
+      <x:c r="G275" s="20" t="n">
+        <x:v>46299.81249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="42" customHeight="1">
-      <x:c r="A276" s="20" t="d">
-        <x:v>2026-10-04T19:30:00.000Z</x:v>
+      <x:c r="A276" s="20" t="n">
+        <x:v>46299.8125</x:v>
       </x:c>
       <x:c r="B276" s="8" t="n">
         <x:v>85462.5</x:v>
@@ -7408,13 +7408,13 @@
       <x:c r="F276" s="8" t="n">
         <x:v>165.2471</x:v>
       </x:c>
-      <x:c r="G276" s="20" t="d">
-        <x:v>2026-10-04T19:59:59.999Z</x:v>
+      <x:c r="G276" s="20" t="n">
+        <x:v>46299.83333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="42" customHeight="1">
-      <x:c r="A277" s="20" t="d">
-        <x:v>2026-10-04T20:00:00.000Z</x:v>
+      <x:c r="A277" s="20" t="n">
+        <x:v>46299.83333333333</x:v>
       </x:c>
       <x:c r="B277" s="8" t="n">
         <x:v>85428</x:v>
@@ -7431,13 +7431,13 @@
       <x:c r="F277" s="8" t="n">
         <x:v>85.8441</x:v>
       </x:c>
-      <x:c r="G277" s="20" t="d">
-        <x:v>2026-10-04T20:29:59.999Z</x:v>
+      <x:c r="G277" s="20" t="n">
+        <x:v>46299.85416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="42" customHeight="1">
-      <x:c r="A278" s="20" t="d">
-        <x:v>2026-10-04T20:30:00.000Z</x:v>
+      <x:c r="A278" s="20" t="n">
+        <x:v>46299.85416666667</x:v>
       </x:c>
       <x:c r="B278" s="8" t="n">
         <x:v>85474.3</x:v>
@@ -7454,13 +7454,13 @@
       <x:c r="F278" s="8" t="n">
         <x:v>292.28174</x:v>
       </x:c>
-      <x:c r="G278" s="20" t="d">
-        <x:v>2026-10-04T20:59:59.999Z</x:v>
+      <x:c r="G278" s="20" t="n">
+        <x:v>46299.87499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="42" customHeight="1">
-      <x:c r="A279" s="20" t="d">
-        <x:v>2026-10-04T21:00:00.000Z</x:v>
+      <x:c r="A279" s="20" t="n">
+        <x:v>46299.875</x:v>
       </x:c>
       <x:c r="B279" s="8" t="n">
         <x:v>85824.45</x:v>
@@ -7477,13 +7477,13 @@
       <x:c r="F279" s="8" t="n">
         <x:v>373.19666</x:v>
       </x:c>
-      <x:c r="G279" s="20" t="d">
-        <x:v>2026-10-04T21:29:59.999Z</x:v>
+      <x:c r="G279" s="20" t="n">
+        <x:v>46299.89583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="42" customHeight="1">
-      <x:c r="A280" s="20" t="d">
-        <x:v>2026-10-04T21:30:00.000Z</x:v>
+      <x:c r="A280" s="20" t="n">
+        <x:v>46299.89583333333</x:v>
       </x:c>
       <x:c r="B280" s="8" t="n">
         <x:v>85827.34</x:v>
@@ -7500,13 +7500,13 @@
       <x:c r="F280" s="8" t="n">
         <x:v>165.08027</x:v>
       </x:c>
-      <x:c r="G280" s="20" t="d">
-        <x:v>2026-10-04T21:59:59.999Z</x:v>
+      <x:c r="G280" s="20" t="n">
+        <x:v>46299.91666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="42" customHeight="1">
-      <x:c r="A281" s="20" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      <x:c r="A281" s="20" t="n">
+        <x:v>46299.91666666667</x:v>
       </x:c>
       <x:c r="B281" s="8" t="n">
         <x:v>85865.43</x:v>
@@ -7523,13 +7523,13 @@
       <x:c r="F281" s="8" t="n">
         <x:v>932.86205</x:v>
       </x:c>
-      <x:c r="G281" s="20" t="d">
-        <x:v>2026-10-04T22:29:59.999Z</x:v>
+      <x:c r="G281" s="20" t="n">
+        <x:v>46299.93749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="42" customHeight="1">
-      <x:c r="A282" s="20" t="d">
-        <x:v>2026-10-04T22:30:00.000Z</x:v>
+      <x:c r="A282" s="20" t="n">
+        <x:v>46299.9375</x:v>
       </x:c>
       <x:c r="B282" s="8" t="n">
         <x:v>86244.83</x:v>
@@ -7546,13 +7546,13 @@
       <x:c r="F282" s="8" t="n">
         <x:v>286.01471</x:v>
       </x:c>
-      <x:c r="G282" s="20" t="d">
-        <x:v>2026-10-04T22:59:59.999Z</x:v>
+      <x:c r="G282" s="20" t="n">
+        <x:v>46299.95833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="42" customHeight="1">
-      <x:c r="A283" s="20" t="d">
-        <x:v>2026-10-04T23:00:00.000Z</x:v>
+      <x:c r="A283" s="20" t="n">
+        <x:v>46299.95833333333</x:v>
       </x:c>
       <x:c r="B283" s="8" t="n">
         <x:v>86428.01</x:v>
@@ -7569,13 +7569,13 @@
       <x:c r="F283" s="8" t="n">
         <x:v>476.44018</x:v>
       </x:c>
-      <x:c r="G283" s="20" t="d">
-        <x:v>2026-10-04T23:29:59.999Z</x:v>
+      <x:c r="G283" s="20" t="n">
+        <x:v>46299.97916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="42" customHeight="1">
-      <x:c r="A284" s="20" t="d">
-        <x:v>2026-10-04T23:30:00.000Z</x:v>
+      <x:c r="A284" s="20" t="n">
+        <x:v>46299.97916666667</x:v>
       </x:c>
       <x:c r="B284" s="8" t="n">
         <x:v>86688</x:v>
@@ -7592,13 +7592,13 @@
       <x:c r="F284" s="8" t="n">
         <x:v>339.54781</x:v>
       </x:c>
-      <x:c r="G284" s="20" t="d">
-        <x:v>2026-10-04T23:59:59.999Z</x:v>
+      <x:c r="G284" s="20" t="n">
+        <x:v>46299.99999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="42" customHeight="1">
-      <x:c r="A285" s="20" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      <x:c r="A285" s="20" t="n">
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="B285" s="8" t="n">
         <x:v>86530</x:v>
@@ -7615,13 +7615,13 @@
       <x:c r="F285" s="8" t="n">
         <x:v>389.46898</x:v>
       </x:c>
-      <x:c r="G285" s="20" t="d">
-        <x:v>2026-10-05T00:29:59.999Z</x:v>
+      <x:c r="G285" s="20" t="n">
+        <x:v>46300.02083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="42" customHeight="1">
-      <x:c r="A286" s="20" t="d">
-        <x:v>2026-10-05T00:30:00.000Z</x:v>
+      <x:c r="A286" s="20" t="n">
+        <x:v>46300.02083333333</x:v>
       </x:c>
       <x:c r="B286" s="8" t="n">
         <x:v>86274.01</x:v>
@@ -7638,13 +7638,13 @@
       <x:c r="F286" s="8" t="n">
         <x:v>296.58574</x:v>
       </x:c>
-      <x:c r="G286" s="20" t="d">
-        <x:v>2026-10-05T00:59:59.999Z</x:v>
+      <x:c r="G286" s="20" t="n">
+        <x:v>46300.04166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="42" customHeight="1">
-      <x:c r="A287" s="20" t="d">
-        <x:v>2026-10-05T01:00:00.000Z</x:v>
+      <x:c r="A287" s="20" t="n">
+        <x:v>46300.04166666667</x:v>
       </x:c>
       <x:c r="B287" s="8" t="n">
         <x:v>86652.45</x:v>
@@ -7661,13 +7661,13 @@
       <x:c r="F287" s="8" t="n">
         <x:v>905.31574</x:v>
       </x:c>
-      <x:c r="G287" s="20" t="d">
-        <x:v>2026-10-05T01:29:59.999Z</x:v>
+      <x:c r="G287" s="20" t="n">
+        <x:v>46300.06249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="42" customHeight="1">
-      <x:c r="A288" s="20" t="d">
-        <x:v>2026-10-05T01:30:00.000Z</x:v>
+      <x:c r="A288" s="20" t="n">
+        <x:v>46300.0625</x:v>
       </x:c>
       <x:c r="B288" s="8" t="n">
         <x:v>86944.68</x:v>
@@ -7684,13 +7684,13 @@
       <x:c r="F288" s="8" t="n">
         <x:v>251.96284</x:v>
       </x:c>
-      <x:c r="G288" s="20" t="d">
-        <x:v>2026-10-05T01:59:59.999Z</x:v>
+      <x:c r="G288" s="20" t="n">
+        <x:v>46300.08333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="42" customHeight="1">
-      <x:c r="A289" s="20" t="d">
-        <x:v>2026-10-05T02:00:00.000Z</x:v>
+      <x:c r="A289" s="20" t="n">
+        <x:v>46300.08333333333</x:v>
       </x:c>
       <x:c r="B289" s="8" t="n">
         <x:v>86615.31</x:v>
@@ -7707,13 +7707,13 @@
       <x:c r="F289" s="8" t="n">
         <x:v>474.21142</x:v>
       </x:c>
-      <x:c r="G289" s="20" t="d">
-        <x:v>2026-10-05T02:29:59.999Z</x:v>
+      <x:c r="G289" s="20" t="n">
+        <x:v>46300.10416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="42" customHeight="1">
-      <x:c r="A290" s="20" t="d">
-        <x:v>2026-10-05T02:30:00.000Z</x:v>
+      <x:c r="A290" s="20" t="n">
+        <x:v>46300.10416666667</x:v>
       </x:c>
       <x:c r="B290" s="8" t="n">
         <x:v>86511.79</x:v>
@@ -7730,13 +7730,13 @@
       <x:c r="F290" s="8" t="n">
         <x:v>273.07538</x:v>
       </x:c>
-      <x:c r="G290" s="20" t="d">
-        <x:v>2026-10-05T02:59:59.999Z</x:v>
+      <x:c r="G290" s="20" t="n">
+        <x:v>46300.12499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="42" customHeight="1">
-      <x:c r="A291" s="20" t="d">
-        <x:v>2026-10-05T03:00:00.000Z</x:v>
+      <x:c r="A291" s="20" t="n">
+        <x:v>46300.125</x:v>
       </x:c>
       <x:c r="B291" s="8" t="n">
         <x:v>86522.01</x:v>
@@ -7753,13 +7753,13 @@
       <x:c r="F291" s="8" t="n">
         <x:v>263.59012</x:v>
       </x:c>
-      <x:c r="G291" s="20" t="d">
-        <x:v>2026-10-05T03:29:59.999Z</x:v>
+      <x:c r="G291" s="20" t="n">
+        <x:v>46300.14583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="42" customHeight="1">
-      <x:c r="A292" s="20" t="d">
-        <x:v>2026-10-05T03:30:00.000Z</x:v>
+      <x:c r="A292" s="20" t="n">
+        <x:v>46300.14583333333</x:v>
       </x:c>
       <x:c r="B292" s="8" t="n">
         <x:v>86454</x:v>
@@ -7776,13 +7776,13 @@
       <x:c r="F292" s="8" t="n">
         <x:v>231.16755</x:v>
       </x:c>
-      <x:c r="G292" s="20" t="d">
-        <x:v>2026-10-05T03:59:59.999Z</x:v>
+      <x:c r="G292" s="20" t="n">
+        <x:v>46300.16666665509</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="42" customHeight="1">
-      <x:c r="A293" s="20" t="d">
-        <x:v>2026-10-05T04:00:00.000Z</x:v>
+      <x:c r="A293" s="20" t="n">
+        <x:v>46300.16666666667</x:v>
       </x:c>
       <x:c r="B293" s="8" t="n">
         <x:v>86085.02</x:v>
@@ -7799,13 +7799,13 @@
       <x:c r="F293" s="8" t="n">
         <x:v>564.88243</x:v>
       </x:c>
-      <x:c r="G293" s="20" t="d">
-        <x:v>2026-10-05T04:29:59.999Z</x:v>
+      <x:c r="G293" s="20" t="n">
+        <x:v>46300.18749998843</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="42" customHeight="1">
-      <x:c r="A294" s="20" t="d">
-        <x:v>2026-10-05T04:30:00.000Z</x:v>
+      <x:c r="A294" s="20" t="n">
+        <x:v>46300.1875</x:v>
       </x:c>
       <x:c r="B294" s="8" t="n">
         <x:v>85778.99</x:v>
@@ -7822,13 +7822,13 @@
       <x:c r="F294" s="8" t="n">
         <x:v>332.03314</x:v>
       </x:c>
-      <x:c r="G294" s="20" t="d">
-        <x:v>2026-10-05T04:59:59.999Z</x:v>
+      <x:c r="G294" s="20" t="n">
+        <x:v>46300.20833332176</x:v>
       </x:c>
     </x:row>
     <x:row r="295" ht="42" customHeight="1">
-      <x:c r="A295" s="20" t="d">
-        <x:v>2026-10-05T05:00:00.000Z</x:v>
+      <x:c r="A295" s="20" t="n">
+        <x:v>46300.20833333333</x:v>
       </x:c>
       <x:c r="B295" s="8" t="n">
         <x:v>85538.02</x:v>
@@ -7845,13 +7845,13 @@
       <x:c r="F295" s="8" t="n">
         <x:v>358.53739</x:v>
       </x:c>
-      <x:c r="G295" s="20" t="d">
-        <x:v>2026-10-05T05:29:59.999Z</x:v>
+      <x:c r="G295" s="20" t="n">
+        <x:v>46300.22916665509</x:v>
       </x:c>
     </x:row>
     <x:row r="296" ht="42" customHeight="1">
-      <x:c r="A296" s="20" t="d">
-        <x:v>2026-10-05T05:30:00.000Z</x:v>
+      <x:c r="A296" s="20" t="n">
+        <x:v>46300.22916666667</x:v>
       </x:c>
       <x:c r="B296" s="8" t="n">
         <x:v>85542.03</x:v>
@@ -7868,13 +7868,13 @@
       <x:c r="F296" s="8" t="n">
         <x:v>314.5134</x:v>
       </x:c>
-      <x:c r="G296" s="20" t="d">
-        <x:v>2026-10-05T05:59:59.999Z</x:v>
+      <x:c r="G296" s="20" t="n">
+        <x:v>46300.24999998843</x:v>
       </x:c>
     </x:row>
     <x:row r="297" ht="42" customHeight="1">
-      <x:c r="A297" s="20" t="d">
-        <x:v>2026-10-05T06:00:00.000Z</x:v>
+      <x:c r="A297" s="20" t="n">
+        <x:v>46300.25</x:v>
       </x:c>
       <x:c r="B297" s="8" t="n">
         <x:v>85767.58</x:v>
@@ -7891,13 +7891,13 @@
       <x:c r="F297" s="8" t="n">
         <x:v>326.85984</x:v>
       </x:c>
-      <x:c r="G297" s="20" t="d">
-        <x:v>2026-10-05T06:29:59.999Z</x:v>
+      <x:c r="G297" s="20" t="n">
+        <x:v>46300.27083332176</x:v>
       </x:c>
     </x:row>
     <x:row r="298" ht="42" customHeight="1">
-      <x:c r="A298" s="20" t="d">
-        <x:v>2026-10-05T06:30:00.000Z</x:v>
+      <x:c r="A298" s="20" t="n">
+        <x:v>46300.27083333333</x:v>
       </x:c>
       <x:c r="B298" s="8" t="n">
         <x:v>85880.01</x:v>
@@ -7914,13 +7914,13 @@
       <x:c r="F298" s="8" t="n">
         <x:v>292.22482</x:v>
       </x:c>
-      <x:c r="G298" s="20" t="d">
-        <x:v>2026-10-05T06:59:59.999Z</x:v>
+      <x:c r="G298" s="20" t="n">
+        <x:v>46300.29166665509</x:v>
       </x:c>
     </x:row>
     <x:row r="299" ht="42" customHeight="1">
-      <x:c r="A299" s="20" t="d">
-        <x:v>2026-10-05T07:00:00.000Z</x:v>
+      <x:c r="A299" s="20" t="n">
+        <x:v>46300.29166666667</x:v>
       </x:c>
       <x:c r="B299" s="8" t="n">
         <x:v>86260.01</x:v>
@@ -7937,13 +7937,13 @@
       <x:c r="F299" s="8" t="n">
         <x:v>356.06423</x:v>
       </x:c>
-      <x:c r="G299" s="20" t="d">
-        <x:v>2026-10-05T07:29:59.999Z</x:v>
+      <x:c r="G299" s="20" t="n">
+        <x:v>46300.31249998843</x:v>
       </x:c>
     </x:row>
     <x:row r="300" ht="42" customHeight="1">
-      <x:c r="A300" s="20" t="d">
-        <x:v>2026-10-05T07:30:00.000Z</x:v>
+      <x:c r="A300" s="20" t="n">
+        <x:v>46300.3125</x:v>
       </x:c>
       <x:c r="B300" s="8" t="n">
         <x:v>86290.01</x:v>
@@ -7960,13 +7960,13 @@
       <x:c r="F300" s="8" t="n">
         <x:v>344.86077</x:v>
       </x:c>
-      <x:c r="G300" s="20" t="d">
-        <x:v>2026-10-05T07:59:59.999Z</x:v>
+      <x:c r="G300" s="20" t="n">
+        <x:v>46300.33333332176</x:v>
       </x:c>
     </x:row>
     <x:row r="301" ht="42" customHeight="1">
-      <x:c r="A301" s="20" t="d">
-        <x:v>2026-10-05T08:00:00.000Z</x:v>
+      <x:c r="A301" s="20" t="n">
+        <x:v>46300.33333333333</x:v>
       </x:c>
       <x:c r="B301" s="8" t="n">
         <x:v>86252.76</x:v>
@@ -7983,13 +7983,13 @@
       <x:c r="F301" s="8" t="n">
         <x:v>225.81586</x:v>
       </x:c>
-      <x:c r="G301" s="20" t="d">
-        <x:v>2026-10-05T08:29:59.999Z</x:v>
+      <x:c r="G301" s="20" t="n">
+        <x:v>46300.35416665509</x:v>
       </x:c>
     </x:row>
     <x:row r="302" ht="42" customHeight="1">
-      <x:c r="A302" s="20" t="d">
-        <x:v>2026-10-05T08:30:00.000Z</x:v>
+      <x:c r="A302" s="20" t="n">
+        <x:v>46300.35416666667</x:v>
       </x:c>
       <x:c r="B302" s="8" t="n">
         <x:v>86431.63</x:v>
@@ -8006,13 +8006,13 @@
       <x:c r="F302" s="8" t="n">
         <x:v>350.18313</x:v>
       </x:c>
-      <x:c r="G302" s="20" t="d">
-        <x:v>2026-10-05T08:59:59.999Z</x:v>
+      <x:c r="G302" s="20" t="n">
+        <x:v>46300.37499998843</x:v>
       </x:c>
     </x:row>
     <x:row r="303" ht="42" customHeight="1">
-      <x:c r="A303" s="20" t="d">
-        <x:v>2026-10-05T09:00:00.000Z</x:v>
+      <x:c r="A303" s="20" t="n">
+        <x:v>46300.375</x:v>
       </x:c>
       <x:c r="B303" s="8" t="n">
         <x:v>86211</x:v>
@@ -8029,13 +8029,13 @@
       <x:c r="F303" s="8" t="n">
         <x:v>685.85246</x:v>
       </x:c>
-      <x:c r="G303" s="20" t="d">
-        <x:v>2026-10-05T09:29:59.999Z</x:v>
+      <x:c r="G303" s="20" t="n">
+        <x:v>46300.39583332176</x:v>
       </x:c>
     </x:row>
     <x:row r="304" ht="42" customHeight="1">
-      <x:c r="A304" s="20" t="d">
-        <x:v>2026-10-05T09:30:00.000Z</x:v>
+      <x:c r="A304" s="20" t="n">
+        <x:v>46300.39583333333</x:v>
       </x:c>
       <x:c r="B304" s="8" t="n">
         <x:v>85874</x:v>
@@ -8052,8 +8052,8 @@
       <x:c r="F304" s="8" t="n">
         <x:v>217.64989</x:v>
       </x:c>
-      <x:c r="G304" s="20" t="d">
-        <x:v>2026-10-05T09:59:59.999Z</x:v>
+      <x:c r="G304" s="20" t="n">
+        <x:v>46300.41666665509</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
